--- a/Task-1/mock_data/client_summary.xlsx
+++ b/Task-1/mock_data/client_summary.xlsx
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>65000</v>
+        <v>64086</v>
       </c>
       <c r="G2" t="n">
-        <v>9750</v>
+        <v>9612</v>
       </c>
       <c r="H2" t="n">
-        <v>55250</v>
+        <v>54474</v>
       </c>
     </row>
     <row r="3">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>65000</v>
+        <v>66015</v>
       </c>
       <c r="G3" t="n">
-        <v>9750</v>
+        <v>9902</v>
       </c>
       <c r="H3" t="n">
-        <v>55250</v>
+        <v>56113</v>
       </c>
     </row>
     <row r="4">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>65000</v>
+        <v>74997</v>
       </c>
       <c r="G4" t="n">
-        <v>9750</v>
+        <v>11249</v>
       </c>
       <c r="H4" t="n">
-        <v>55250</v>
+        <v>63748</v>
       </c>
     </row>
     <row r="5">
@@ -584,22 +584,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>May 2019</t>
+          <t>Apr 2019</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>65000</v>
+        <v>65010</v>
       </c>
       <c r="G5" t="n">
-        <v>9750</v>
+        <v>9751</v>
       </c>
       <c r="H5" t="n">
-        <v>55250</v>
+        <v>55259</v>
       </c>
     </row>
     <row r="6">
@@ -620,22 +620,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jun 2019</t>
+          <t>May 2019</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>65000</v>
+        <v>63932</v>
       </c>
       <c r="G6" t="n">
-        <v>9750</v>
+        <v>9589</v>
       </c>
       <c r="H6" t="n">
-        <v>55250</v>
+        <v>54343</v>
       </c>
     </row>
     <row r="7">
@@ -656,22 +656,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jul 2019</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65000</v>
+        <v>79033</v>
       </c>
       <c r="G7" t="n">
-        <v>9750</v>
+        <v>11854</v>
       </c>
       <c r="H7" t="n">
-        <v>55250</v>
+        <v>67179</v>
       </c>
     </row>
     <row r="8">
@@ -692,22 +692,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aug 2019</t>
+          <t>Jul 2019</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>65000</v>
+        <v>63903</v>
       </c>
       <c r="G8" t="n">
-        <v>9750</v>
+        <v>9585</v>
       </c>
       <c r="H8" t="n">
-        <v>55250</v>
+        <v>54318</v>
       </c>
     </row>
     <row r="9">
@@ -728,22 +728,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oct 2019</t>
+          <t>Aug 2019</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>65000</v>
+        <v>63797</v>
       </c>
       <c r="G9" t="n">
-        <v>9750</v>
+        <v>9569</v>
       </c>
       <c r="H9" t="n">
-        <v>55250</v>
+        <v>54228</v>
       </c>
     </row>
     <row r="10">
@@ -764,22 +764,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nov 2019</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>65000</v>
+        <v>81057</v>
       </c>
       <c r="G10" t="n">
-        <v>9750</v>
+        <v>12158</v>
       </c>
       <c r="H10" t="n">
-        <v>55250</v>
+        <v>68899</v>
       </c>
     </row>
     <row r="11">
@@ -800,22 +800,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>Oct 2019</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>65000</v>
+        <v>66271</v>
       </c>
       <c r="G11" t="n">
-        <v>9750</v>
+        <v>9940</v>
       </c>
       <c r="H11" t="n">
-        <v>55250</v>
+        <v>56331</v>
       </c>
     </row>
     <row r="12">
@@ -836,22 +836,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jan 2020</t>
+          <t>Nov 2019</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>68250</v>
+        <v>64630</v>
       </c>
       <c r="G12" t="n">
-        <v>10237</v>
+        <v>9694</v>
       </c>
       <c r="H12" t="n">
-        <v>58013</v>
+        <v>54936</v>
       </c>
     </row>
     <row r="13">
@@ -872,22 +872,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Feb 2020</t>
+          <t>Dec 2019</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>68250</v>
+        <v>108635</v>
       </c>
       <c r="G13" t="n">
-        <v>10237</v>
+        <v>16295</v>
       </c>
       <c r="H13" t="n">
-        <v>58013</v>
+        <v>92340</v>
       </c>
     </row>
     <row r="14">
@@ -908,22 +908,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>68250</v>
+        <v>65537</v>
       </c>
       <c r="G14" t="n">
-        <v>10237</v>
+        <v>9830</v>
       </c>
       <c r="H14" t="n">
-        <v>58013</v>
+        <v>55707</v>
       </c>
     </row>
     <row r="15">
@@ -944,22 +944,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Apr 2020</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>68250</v>
+        <v>77991</v>
       </c>
       <c r="G15" t="n">
-        <v>10237</v>
+        <v>11698</v>
       </c>
       <c r="H15" t="n">
-        <v>58013</v>
+        <v>66293</v>
       </c>
     </row>
     <row r="16">
@@ -980,22 +980,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>68250</v>
+        <v>64824</v>
       </c>
       <c r="G16" t="n">
-        <v>10237</v>
+        <v>9723</v>
       </c>
       <c r="H16" t="n">
-        <v>58013</v>
+        <v>55101</v>
       </c>
     </row>
     <row r="17">
@@ -1016,22 +1016,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>May 2020</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>68250</v>
+        <v>63875</v>
       </c>
       <c r="G17" t="n">
-        <v>10237</v>
+        <v>9581</v>
       </c>
       <c r="H17" t="n">
-        <v>58013</v>
+        <v>54294</v>
       </c>
     </row>
     <row r="18">
@@ -1052,22 +1052,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>68250</v>
+        <v>65736</v>
       </c>
       <c r="G18" t="n">
-        <v>10237</v>
+        <v>9860</v>
       </c>
       <c r="H18" t="n">
-        <v>58013</v>
+        <v>55876</v>
       </c>
     </row>
     <row r="19">
@@ -1088,22 +1088,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Aug 2020</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>68250</v>
+        <v>64635</v>
       </c>
       <c r="G19" t="n">
-        <v>10237</v>
+        <v>9695</v>
       </c>
       <c r="H19" t="n">
-        <v>58013</v>
+        <v>54940</v>
       </c>
     </row>
     <row r="20">
@@ -1124,22 +1124,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oct 2020</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>68250</v>
+        <v>82356</v>
       </c>
       <c r="G20" t="n">
-        <v>10237</v>
+        <v>12353</v>
       </c>
       <c r="H20" t="n">
-        <v>58013</v>
+        <v>70003</v>
       </c>
     </row>
     <row r="21">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nov 2020</t>
+          <t>Oct 2020</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>68250</v>
+        <v>64837</v>
       </c>
       <c r="G21" t="n">
-        <v>10237</v>
+        <v>9725</v>
       </c>
       <c r="H21" t="n">
-        <v>58013</v>
+        <v>55112</v>
       </c>
     </row>
     <row r="22">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>68250</v>
+        <v>124239</v>
       </c>
       <c r="G22" t="n">
-        <v>10237</v>
+        <v>18635</v>
       </c>
       <c r="H22" t="n">
-        <v>58013</v>
+        <v>105604</v>
       </c>
     </row>
     <row r="23">
@@ -1241,13 +1241,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>71662</v>
+        <v>64483</v>
       </c>
       <c r="G23" t="n">
-        <v>10749</v>
+        <v>9672</v>
       </c>
       <c r="H23" t="n">
-        <v>60913</v>
+        <v>54811</v>
       </c>
     </row>
     <row r="24">
@@ -1277,13 +1277,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>71662</v>
+        <v>66137</v>
       </c>
       <c r="G24" t="n">
-        <v>10749</v>
+        <v>9920</v>
       </c>
       <c r="H24" t="n">
-        <v>60913</v>
+        <v>56217</v>
       </c>
     </row>
     <row r="25">
@@ -1313,13 +1313,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>71662</v>
+        <v>81840</v>
       </c>
       <c r="G25" t="n">
-        <v>10749</v>
+        <v>12276</v>
       </c>
       <c r="H25" t="n">
-        <v>60913</v>
+        <v>69564</v>
       </c>
     </row>
     <row r="26">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>71662</v>
+        <v>65029</v>
       </c>
       <c r="G26" t="n">
-        <v>10749</v>
+        <v>9754</v>
       </c>
       <c r="H26" t="n">
-        <v>60913</v>
+        <v>55275</v>
       </c>
     </row>
     <row r="27">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>71662</v>
+        <v>82960</v>
       </c>
       <c r="G27" t="n">
-        <v>10749</v>
+        <v>12444</v>
       </c>
       <c r="H27" t="n">
-        <v>60913</v>
+        <v>70516</v>
       </c>
     </row>
     <row r="28">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>71662</v>
+        <v>66189</v>
       </c>
       <c r="G28" t="n">
-        <v>10749</v>
+        <v>9928</v>
       </c>
       <c r="H28" t="n">
-        <v>60913</v>
+        <v>56261</v>
       </c>
     </row>
     <row r="29">
@@ -1448,22 +1448,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aug 2021</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>71662</v>
+        <v>83186</v>
       </c>
       <c r="G29" t="n">
-        <v>10749</v>
+        <v>12477</v>
       </c>
       <c r="H29" t="n">
-        <v>60913</v>
+        <v>70709</v>
       </c>
     </row>
     <row r="30">
@@ -1484,22 +1484,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>71662</v>
+        <v>64009</v>
       </c>
       <c r="G30" t="n">
-        <v>10749</v>
+        <v>9601</v>
       </c>
       <c r="H30" t="n">
-        <v>60913</v>
+        <v>54408</v>
       </c>
     </row>
     <row r="31">
@@ -1520,22 +1520,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>Jan 2022</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>71662</v>
+        <v>64152</v>
       </c>
       <c r="G31" t="n">
-        <v>10749</v>
+        <v>9622</v>
       </c>
       <c r="H31" t="n">
-        <v>60913</v>
+        <v>54530</v>
       </c>
     </row>
     <row r="32">
@@ -1556,22 +1556,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>Feb 2022</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>71662</v>
+        <v>65883</v>
       </c>
       <c r="G32" t="n">
-        <v>10749</v>
+        <v>9882</v>
       </c>
       <c r="H32" t="n">
-        <v>60913</v>
+        <v>56001</v>
       </c>
     </row>
     <row r="33">
@@ -1592,22 +1592,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jan 2022</t>
+          <t>Mar 2022</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>75245</v>
+        <v>75297</v>
       </c>
       <c r="G33" t="n">
-        <v>11286</v>
+        <v>11294</v>
       </c>
       <c r="H33" t="n">
-        <v>63959</v>
+        <v>64003</v>
       </c>
     </row>
     <row r="34">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mar 2022</t>
+          <t>Apr 2022</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>75245</v>
+        <v>63804</v>
       </c>
       <c r="G34" t="n">
-        <v>11286</v>
+        <v>9570</v>
       </c>
       <c r="H34" t="n">
-        <v>63959</v>
+        <v>54234</v>
       </c>
     </row>
     <row r="35">
@@ -1664,22 +1664,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Apr 2022</t>
+          <t>May 2022</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>75245</v>
+        <v>64054</v>
       </c>
       <c r="G35" t="n">
-        <v>11286</v>
+        <v>9608</v>
       </c>
       <c r="H35" t="n">
-        <v>63959</v>
+        <v>54446</v>
       </c>
     </row>
     <row r="36">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>75245</v>
+        <v>77664</v>
       </c>
       <c r="G36" t="n">
-        <v>11286</v>
+        <v>11649</v>
       </c>
       <c r="H36" t="n">
-        <v>63959</v>
+        <v>66015</v>
       </c>
     </row>
     <row r="37">
@@ -1736,22 +1736,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>Jul 2022</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>75245</v>
+        <v>64676</v>
       </c>
       <c r="G37" t="n">
-        <v>11286</v>
+        <v>9701</v>
       </c>
       <c r="H37" t="n">
-        <v>63959</v>
+        <v>54975</v>
       </c>
     </row>
     <row r="38">
@@ -1772,22 +1772,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Aug 2022</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>75245</v>
+        <v>64584</v>
       </c>
       <c r="G38" t="n">
-        <v>11286</v>
+        <v>9687</v>
       </c>
       <c r="H38" t="n">
-        <v>63959</v>
+        <v>54897</v>
       </c>
     </row>
     <row r="39">
@@ -1808,22 +1808,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>75245</v>
+        <v>79531</v>
       </c>
       <c r="G39" t="n">
-        <v>11286</v>
+        <v>11929</v>
       </c>
       <c r="H39" t="n">
-        <v>63959</v>
+        <v>67602</v>
       </c>
     </row>
     <row r="40">
@@ -1844,22 +1844,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nov 2022</t>
+          <t>Oct 2022</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>75245</v>
+        <v>64111</v>
       </c>
       <c r="G40" t="n">
-        <v>11286</v>
+        <v>9616</v>
       </c>
       <c r="H40" t="n">
-        <v>63959</v>
+        <v>54495</v>
       </c>
     </row>
     <row r="41">
@@ -1880,22 +1880,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dec 2022</t>
+          <t>Nov 2022</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>75245</v>
+        <v>66074</v>
       </c>
       <c r="G41" t="n">
-        <v>11286</v>
+        <v>9911</v>
       </c>
       <c r="H41" t="n">
-        <v>63959</v>
+        <v>56163</v>
       </c>
     </row>
     <row r="42">
@@ -1916,22 +1916,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jan 2023</t>
+          <t>Dec 2022</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>79007</v>
+        <v>107483</v>
       </c>
       <c r="G42" t="n">
-        <v>11851</v>
+        <v>16122</v>
       </c>
       <c r="H42" t="n">
-        <v>67156</v>
+        <v>91361</v>
       </c>
     </row>
     <row r="43">
@@ -1952,22 +1952,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>Mar 2023</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>79007</v>
+        <v>79132</v>
       </c>
       <c r="G43" t="n">
-        <v>11851</v>
+        <v>11869</v>
       </c>
       <c r="H43" t="n">
-        <v>67156</v>
+        <v>67263</v>
       </c>
     </row>
     <row r="44">
@@ -1988,22 +1988,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mar 2023</t>
+          <t>Apr 2023</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>79007</v>
+        <v>64095</v>
       </c>
       <c r="G44" t="n">
-        <v>11851</v>
+        <v>9614</v>
       </c>
       <c r="H44" t="n">
-        <v>67156</v>
+        <v>54481</v>
       </c>
     </row>
     <row r="45">
@@ -2024,22 +2024,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Apr 2023</t>
+          <t>May 2023</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>79007</v>
+        <v>65776</v>
       </c>
       <c r="G45" t="n">
-        <v>11851</v>
+        <v>9866</v>
       </c>
       <c r="H45" t="n">
-        <v>67156</v>
+        <v>55910</v>
       </c>
     </row>
     <row r="46">
@@ -2060,22 +2060,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>79007</v>
+        <v>76699</v>
       </c>
       <c r="G46" t="n">
-        <v>11851</v>
+        <v>11504</v>
       </c>
       <c r="H46" t="n">
-        <v>67156</v>
+        <v>65195</v>
       </c>
     </row>
     <row r="47">
@@ -2096,22 +2096,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>Aug 2023</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>79007</v>
+        <v>65410</v>
       </c>
       <c r="G47" t="n">
-        <v>11851</v>
+        <v>9811</v>
       </c>
       <c r="H47" t="n">
-        <v>67156</v>
+        <v>55599</v>
       </c>
     </row>
     <row r="48">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>Sep 2023</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>79007</v>
+        <v>77063</v>
       </c>
       <c r="G48" t="n">
-        <v>11851</v>
+        <v>11559</v>
       </c>
       <c r="H48" t="n">
-        <v>67156</v>
+        <v>65504</v>
       </c>
     </row>
     <row r="49">
@@ -2168,22 +2168,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aug 2023</t>
+          <t>Oct 2023</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>79007</v>
+        <v>64173</v>
       </c>
       <c r="G49" t="n">
-        <v>11851</v>
+        <v>9625</v>
       </c>
       <c r="H49" t="n">
-        <v>67156</v>
+        <v>54548</v>
       </c>
     </row>
     <row r="50">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>Nov 2023</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>79007</v>
+        <v>65112</v>
       </c>
       <c r="G50" t="n">
-        <v>11851</v>
+        <v>9766</v>
       </c>
       <c r="H50" t="n">
-        <v>67156</v>
+        <v>55346</v>
       </c>
     </row>
     <row r="51">
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>79007</v>
+        <v>109990</v>
       </c>
       <c r="G51" t="n">
-        <v>11851</v>
+        <v>16498</v>
       </c>
       <c r="H51" t="n">
-        <v>67156</v>
+        <v>93492</v>
       </c>
     </row>
     <row r="52">
@@ -2276,22 +2276,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jan 2019</t>
+          <t>Mar 2019</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>85000</v>
+        <v>102077</v>
       </c>
       <c r="G52" t="n">
-        <v>12750</v>
+        <v>15311</v>
       </c>
       <c r="H52" t="n">
-        <v>72250</v>
+        <v>86766</v>
       </c>
     </row>
     <row r="53">
@@ -2312,22 +2312,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Feb 2019</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>85000</v>
+        <v>99411</v>
       </c>
       <c r="G53" t="n">
-        <v>12750</v>
+        <v>14911</v>
       </c>
       <c r="H53" t="n">
-        <v>72250</v>
+        <v>84500</v>
       </c>
     </row>
     <row r="54">
@@ -2348,22 +2348,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>May 2019</t>
+          <t>Jul 2019</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>85000</v>
+        <v>84868</v>
       </c>
       <c r="G54" t="n">
-        <v>12750</v>
+        <v>12730</v>
       </c>
       <c r="H54" t="n">
-        <v>72250</v>
+        <v>72138</v>
       </c>
     </row>
     <row r="55">
@@ -2384,22 +2384,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Jun 2019</t>
+          <t>Aug 2019</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>85000</v>
+        <v>84065</v>
       </c>
       <c r="G55" t="n">
-        <v>12750</v>
+        <v>12609</v>
       </c>
       <c r="H55" t="n">
-        <v>72250</v>
+        <v>71456</v>
       </c>
     </row>
     <row r="56">
@@ -2420,22 +2420,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jul 2019</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>85000</v>
+        <v>99964</v>
       </c>
       <c r="G56" t="n">
-        <v>12750</v>
+        <v>14994</v>
       </c>
       <c r="H56" t="n">
-        <v>72250</v>
+        <v>84970</v>
       </c>
     </row>
     <row r="57">
@@ -2456,22 +2456,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aug 2019</t>
+          <t>Oct 2019</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>85000</v>
+        <v>85003</v>
       </c>
       <c r="G57" t="n">
         <v>12750</v>
       </c>
       <c r="H57" t="n">
-        <v>72250</v>
+        <v>72253</v>
       </c>
     </row>
     <row r="58">
@@ -2492,22 +2492,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sep 2019</t>
+          <t>Nov 2019</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>85000</v>
+        <v>85025</v>
       </c>
       <c r="G58" t="n">
-        <v>12750</v>
+        <v>12753</v>
       </c>
       <c r="H58" t="n">
-        <v>72250</v>
+        <v>72272</v>
       </c>
     </row>
     <row r="59">
@@ -2528,22 +2528,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Oct 2019</t>
+          <t>Dec 2019</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>85000</v>
+        <v>162201</v>
       </c>
       <c r="G59" t="n">
-        <v>12750</v>
+        <v>24330</v>
       </c>
       <c r="H59" t="n">
-        <v>72250</v>
+        <v>137871</v>
       </c>
     </row>
     <row r="60">
@@ -2564,22 +2564,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>85000</v>
+        <v>84266</v>
       </c>
       <c r="G60" t="n">
-        <v>12750</v>
+        <v>12639</v>
       </c>
       <c r="H60" t="n">
-        <v>72250</v>
+        <v>71627</v>
       </c>
     </row>
     <row r="61">
@@ -2600,22 +2600,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Feb 2020</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>89250</v>
+        <v>103284</v>
       </c>
       <c r="G61" t="n">
-        <v>13387</v>
+        <v>15492</v>
       </c>
       <c r="H61" t="n">
-        <v>75863</v>
+        <v>87792</v>
       </c>
     </row>
     <row r="62">
@@ -2636,22 +2636,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>89250</v>
+        <v>83522</v>
       </c>
       <c r="G62" t="n">
-        <v>13387</v>
+        <v>12528</v>
       </c>
       <c r="H62" t="n">
-        <v>75863</v>
+        <v>70994</v>
       </c>
     </row>
     <row r="63">
@@ -2672,22 +2672,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Apr 2020</t>
+          <t>May 2020</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>89250</v>
+        <v>83684</v>
       </c>
       <c r="G63" t="n">
-        <v>13387</v>
+        <v>12552</v>
       </c>
       <c r="H63" t="n">
-        <v>75863</v>
+        <v>71132</v>
       </c>
     </row>
     <row r="64">
@@ -2708,22 +2708,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>89250</v>
+        <v>96427</v>
       </c>
       <c r="G64" t="n">
-        <v>13387</v>
+        <v>14464</v>
       </c>
       <c r="H64" t="n">
-        <v>75863</v>
+        <v>81963</v>
       </c>
     </row>
     <row r="65">
@@ -2744,22 +2744,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>89250</v>
+        <v>84811</v>
       </c>
       <c r="G65" t="n">
-        <v>13387</v>
+        <v>12721</v>
       </c>
       <c r="H65" t="n">
-        <v>75863</v>
+        <v>72090</v>
       </c>
     </row>
     <row r="66">
@@ -2780,22 +2780,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>Aug 2020</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>89250</v>
+        <v>85506</v>
       </c>
       <c r="G66" t="n">
-        <v>13387</v>
+        <v>12825</v>
       </c>
       <c r="H66" t="n">
-        <v>75863</v>
+        <v>72681</v>
       </c>
     </row>
     <row r="67">
@@ -2816,22 +2816,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>Oct 2020</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>89250</v>
+        <v>84437</v>
       </c>
       <c r="G67" t="n">
-        <v>13387</v>
+        <v>12665</v>
       </c>
       <c r="H67" t="n">
-        <v>75863</v>
+        <v>71772</v>
       </c>
     </row>
     <row r="68">
@@ -2852,22 +2852,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Nov 2020</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>89250</v>
+        <v>84429</v>
       </c>
       <c r="G68" t="n">
-        <v>13387</v>
+        <v>12664</v>
       </c>
       <c r="H68" t="n">
-        <v>75863</v>
+        <v>71765</v>
       </c>
     </row>
     <row r="69">
@@ -2888,22 +2888,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oct 2020</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>89250</v>
+        <v>163293</v>
       </c>
       <c r="G69" t="n">
-        <v>13387</v>
+        <v>24493</v>
       </c>
       <c r="H69" t="n">
-        <v>75863</v>
+        <v>138800</v>
       </c>
     </row>
     <row r="70">
@@ -2924,22 +2924,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>Jan 2021</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>89250</v>
+        <v>83681</v>
       </c>
       <c r="G70" t="n">
-        <v>13387</v>
+        <v>12552</v>
       </c>
       <c r="H70" t="n">
-        <v>75863</v>
+        <v>71129</v>
       </c>
     </row>
     <row r="71">
@@ -2960,22 +2960,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jan 2021</t>
+          <t>Feb 2021</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>93712</v>
+        <v>85852</v>
       </c>
       <c r="G71" t="n">
-        <v>14056</v>
+        <v>12877</v>
       </c>
       <c r="H71" t="n">
-        <v>79656</v>
+        <v>72975</v>
       </c>
     </row>
     <row r="72">
@@ -2996,22 +2996,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Feb 2021</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>93712</v>
+        <v>105472</v>
       </c>
       <c r="G72" t="n">
-        <v>14056</v>
+        <v>15820</v>
       </c>
       <c r="H72" t="n">
-        <v>79656</v>
+        <v>89652</v>
       </c>
     </row>
     <row r="73">
@@ -3032,22 +3032,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>Apr 2021</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>93712</v>
+        <v>85195</v>
       </c>
       <c r="G73" t="n">
-        <v>14056</v>
+        <v>12779</v>
       </c>
       <c r="H73" t="n">
-        <v>79656</v>
+        <v>72416</v>
       </c>
     </row>
     <row r="74">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Apr 2021</t>
+          <t>May 2021</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>93712</v>
+        <v>84959</v>
       </c>
       <c r="G74" t="n">
-        <v>14056</v>
+        <v>12743</v>
       </c>
       <c r="H74" t="n">
-        <v>79656</v>
+        <v>72216</v>
       </c>
     </row>
     <row r="75">
@@ -3113,13 +3113,13 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>93712</v>
+        <v>98979</v>
       </c>
       <c r="G75" t="n">
-        <v>14056</v>
+        <v>14846</v>
       </c>
       <c r="H75" t="n">
-        <v>79656</v>
+        <v>84133</v>
       </c>
     </row>
     <row r="76">
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>93712</v>
+        <v>83903</v>
       </c>
       <c r="G76" t="n">
-        <v>14056</v>
+        <v>12585</v>
       </c>
       <c r="H76" t="n">
-        <v>79656</v>
+        <v>71318</v>
       </c>
     </row>
     <row r="77">
@@ -3185,13 +3185,13 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>93712</v>
+        <v>85794</v>
       </c>
       <c r="G77" t="n">
-        <v>14056</v>
+        <v>12869</v>
       </c>
       <c r="H77" t="n">
-        <v>79656</v>
+        <v>72925</v>
       </c>
     </row>
     <row r="78">
@@ -3221,13 +3221,13 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>93712</v>
+        <v>107914</v>
       </c>
       <c r="G78" t="n">
-        <v>14056</v>
+        <v>16187</v>
       </c>
       <c r="H78" t="n">
-        <v>79656</v>
+        <v>91727</v>
       </c>
     </row>
     <row r="79">
@@ -3257,13 +3257,13 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>93712</v>
+        <v>84569</v>
       </c>
       <c r="G79" t="n">
-        <v>14056</v>
+        <v>12685</v>
       </c>
       <c r="H79" t="n">
-        <v>79656</v>
+        <v>71884</v>
       </c>
     </row>
     <row r="80">
@@ -3293,13 +3293,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>93712</v>
+        <v>85778</v>
       </c>
       <c r="G80" t="n">
-        <v>14056</v>
+        <v>12866</v>
       </c>
       <c r="H80" t="n">
-        <v>79656</v>
+        <v>72912</v>
       </c>
     </row>
     <row r="81">
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>93712</v>
+        <v>157603</v>
       </c>
       <c r="G81" t="n">
-        <v>14056</v>
+        <v>23640</v>
       </c>
       <c r="H81" t="n">
-        <v>79656</v>
+        <v>133963</v>
       </c>
     </row>
     <row r="82">
@@ -3365,13 +3365,13 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>98397</v>
+        <v>84273</v>
       </c>
       <c r="G82" t="n">
-        <v>14759</v>
+        <v>12640</v>
       </c>
       <c r="H82" t="n">
-        <v>83638</v>
+        <v>71633</v>
       </c>
     </row>
     <row r="83">
@@ -3401,13 +3401,13 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>98397</v>
+        <v>84827</v>
       </c>
       <c r="G83" t="n">
-        <v>14759</v>
+        <v>12724</v>
       </c>
       <c r="H83" t="n">
-        <v>83638</v>
+        <v>72103</v>
       </c>
     </row>
     <row r="84">
@@ -3437,13 +3437,13 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>98397</v>
+        <v>103709</v>
       </c>
       <c r="G84" t="n">
-        <v>14759</v>
+        <v>15556</v>
       </c>
       <c r="H84" t="n">
-        <v>83638</v>
+        <v>88153</v>
       </c>
     </row>
     <row r="85">
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>98397</v>
+        <v>86328</v>
       </c>
       <c r="G85" t="n">
-        <v>14759</v>
+        <v>12949</v>
       </c>
       <c r="H85" t="n">
-        <v>83638</v>
+        <v>73379</v>
       </c>
     </row>
     <row r="86">
@@ -3500,22 +3500,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>May 2022</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>98397</v>
+        <v>86144</v>
       </c>
       <c r="G86" t="n">
-        <v>14759</v>
+        <v>12921</v>
       </c>
       <c r="H86" t="n">
-        <v>83638</v>
+        <v>73223</v>
       </c>
     </row>
     <row r="87">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jul 2022</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>98397</v>
+        <v>99902</v>
       </c>
       <c r="G87" t="n">
-        <v>14759</v>
+        <v>14985</v>
       </c>
       <c r="H87" t="n">
-        <v>83638</v>
+        <v>84917</v>
       </c>
     </row>
     <row r="88">
@@ -3572,22 +3572,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>Jul 2022</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>98397</v>
+        <v>85865</v>
       </c>
       <c r="G88" t="n">
-        <v>14759</v>
+        <v>12879</v>
       </c>
       <c r="H88" t="n">
-        <v>83638</v>
+        <v>72986</v>
       </c>
     </row>
     <row r="89">
@@ -3608,22 +3608,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Aug 2022</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>98397</v>
+        <v>83773</v>
       </c>
       <c r="G89" t="n">
-        <v>14759</v>
+        <v>12565</v>
       </c>
       <c r="H89" t="n">
-        <v>83638</v>
+        <v>71208</v>
       </c>
     </row>
     <row r="90">
@@ -3644,22 +3644,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>98397</v>
+        <v>96407</v>
       </c>
       <c r="G90" t="n">
-        <v>14759</v>
+        <v>14461</v>
       </c>
       <c r="H90" t="n">
-        <v>83638</v>
+        <v>81946</v>
       </c>
     </row>
     <row r="91">
@@ -3689,13 +3689,13 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>98397</v>
+        <v>85820</v>
       </c>
       <c r="G91" t="n">
-        <v>14759</v>
+        <v>12873</v>
       </c>
       <c r="H91" t="n">
-        <v>83638</v>
+        <v>72947</v>
       </c>
     </row>
     <row r="92">
@@ -3725,13 +3725,13 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>98397</v>
+        <v>164038</v>
       </c>
       <c r="G92" t="n">
-        <v>14759</v>
+        <v>24605</v>
       </c>
       <c r="H92" t="n">
-        <v>83638</v>
+        <v>139433</v>
       </c>
     </row>
     <row r="93">
@@ -3752,22 +3752,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>Jan 2023</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>103316</v>
+        <v>85500</v>
       </c>
       <c r="G93" t="n">
-        <v>15497</v>
+        <v>12825</v>
       </c>
       <c r="H93" t="n">
-        <v>87819</v>
+        <v>72675</v>
       </c>
     </row>
     <row r="94">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Apr 2023</t>
+          <t>Feb 2023</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>103316</v>
+        <v>84609</v>
       </c>
       <c r="G94" t="n">
-        <v>15497</v>
+        <v>12691</v>
       </c>
       <c r="H94" t="n">
-        <v>87819</v>
+        <v>71918</v>
       </c>
     </row>
     <row r="95">
@@ -3824,22 +3824,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>Apr 2023</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>103316</v>
+        <v>85447</v>
       </c>
       <c r="G95" t="n">
-        <v>15497</v>
+        <v>12817</v>
       </c>
       <c r="H95" t="n">
-        <v>87819</v>
+        <v>72630</v>
       </c>
     </row>
     <row r="96">
@@ -3860,22 +3860,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>May 2023</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>103316</v>
+        <v>84775</v>
       </c>
       <c r="G96" t="n">
-        <v>15497</v>
+        <v>12716</v>
       </c>
       <c r="H96" t="n">
-        <v>87819</v>
+        <v>72059</v>
       </c>
     </row>
     <row r="97">
@@ -3896,22 +3896,22 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>103316</v>
+        <v>100323</v>
       </c>
       <c r="G97" t="n">
-        <v>15497</v>
+        <v>15048</v>
       </c>
       <c r="H97" t="n">
-        <v>87819</v>
+        <v>85275</v>
       </c>
     </row>
     <row r="98">
@@ -3932,22 +3932,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>Jul 2023</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>103316</v>
+        <v>86398</v>
       </c>
       <c r="G98" t="n">
-        <v>15497</v>
+        <v>12959</v>
       </c>
       <c r="H98" t="n">
-        <v>87819</v>
+        <v>73439</v>
       </c>
     </row>
     <row r="99">
@@ -3968,22 +3968,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oct 2023</t>
+          <t>Aug 2023</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>103316</v>
+        <v>85119</v>
       </c>
       <c r="G99" t="n">
-        <v>15497</v>
+        <v>12767</v>
       </c>
       <c r="H99" t="n">
-        <v>87819</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="100">
@@ -4004,22 +4004,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Nov 2023</t>
+          <t>Oct 2023</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>103316</v>
+        <v>84591</v>
       </c>
       <c r="G100" t="n">
-        <v>15497</v>
+        <v>12688</v>
       </c>
       <c r="H100" t="n">
-        <v>87819</v>
+        <v>71903</v>
       </c>
     </row>
     <row r="101">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dec 2023</t>
+          <t>Nov 2023</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>103316</v>
+        <v>84065</v>
       </c>
       <c r="G101" t="n">
-        <v>15497</v>
+        <v>12609</v>
       </c>
       <c r="H101" t="n">
-        <v>87819</v>
+        <v>71456</v>
       </c>
     </row>
     <row r="102">
@@ -4076,22 +4076,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Mar 2019</t>
+          <t>Jan 2019</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>50000</v>
+        <v>50083</v>
       </c>
       <c r="G102" t="n">
-        <v>7500</v>
+        <v>7512</v>
       </c>
       <c r="H102" t="n">
-        <v>42500</v>
+        <v>42571</v>
       </c>
     </row>
     <row r="103">
@@ -4112,22 +4112,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Apr 2019</t>
+          <t>Feb 2019</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>50000</v>
+        <v>50996</v>
       </c>
       <c r="G103" t="n">
-        <v>7500</v>
+        <v>7649</v>
       </c>
       <c r="H103" t="n">
-        <v>42500</v>
+        <v>43347</v>
       </c>
     </row>
     <row r="104">
@@ -4148,22 +4148,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>May 2019</t>
+          <t>Mar 2019</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>50000</v>
+        <v>64350</v>
       </c>
       <c r="G104" t="n">
-        <v>7500</v>
+        <v>9652</v>
       </c>
       <c r="H104" t="n">
-        <v>42500</v>
+        <v>54698</v>
       </c>
     </row>
     <row r="105">
@@ -4184,22 +4184,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Jun 2019</t>
+          <t>Apr 2019</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>50000</v>
+        <v>49522</v>
       </c>
       <c r="G105" t="n">
-        <v>7500</v>
+        <v>7428</v>
       </c>
       <c r="H105" t="n">
-        <v>42500</v>
+        <v>42094</v>
       </c>
     </row>
     <row r="106">
@@ -4220,22 +4220,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sep 2019</t>
+          <t>May 2019</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>50000</v>
+        <v>50087</v>
       </c>
       <c r="G106" t="n">
-        <v>7500</v>
+        <v>7513</v>
       </c>
       <c r="H106" t="n">
-        <v>42500</v>
+        <v>42574</v>
       </c>
     </row>
     <row r="107">
@@ -4256,22 +4256,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Oct 2019</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>50000</v>
+        <v>64569</v>
       </c>
       <c r="G107" t="n">
-        <v>7500</v>
+        <v>9685</v>
       </c>
       <c r="H107" t="n">
-        <v>42500</v>
+        <v>54884</v>
       </c>
     </row>
     <row r="108">
@@ -4292,22 +4292,22 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Nov 2019</t>
+          <t>Jul 2019</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>50000</v>
+        <v>50843</v>
       </c>
       <c r="G108" t="n">
-        <v>7500</v>
+        <v>7626</v>
       </c>
       <c r="H108" t="n">
-        <v>42500</v>
+        <v>43217</v>
       </c>
     </row>
     <row r="109">
@@ -4328,22 +4328,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>Aug 2019</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>50000</v>
+        <v>50581</v>
       </c>
       <c r="G109" t="n">
-        <v>7500</v>
+        <v>7587</v>
       </c>
       <c r="H109" t="n">
-        <v>42500</v>
+        <v>42994</v>
       </c>
     </row>
     <row r="110">
@@ -4364,22 +4364,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Jan 2020</t>
+          <t>Nov 2019</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>52500</v>
+        <v>49640</v>
       </c>
       <c r="G110" t="n">
-        <v>7875</v>
+        <v>7446</v>
       </c>
       <c r="H110" t="n">
-        <v>44625</v>
+        <v>42194</v>
       </c>
     </row>
     <row r="111">
@@ -4400,22 +4400,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>60000</v>
+        <v>50026</v>
       </c>
       <c r="G111" t="n">
-        <v>9000</v>
+        <v>7503</v>
       </c>
       <c r="H111" t="n">
-        <v>51000</v>
+        <v>42523</v>
       </c>
     </row>
     <row r="112">
@@ -4436,22 +4436,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Apr 2020</t>
+          <t>Feb 2020</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>50000</v>
+        <v>49849</v>
       </c>
       <c r="G112" t="n">
-        <v>7500</v>
+        <v>7477</v>
       </c>
       <c r="H112" t="n">
-        <v>42500</v>
+        <v>42372</v>
       </c>
     </row>
     <row r="113">
@@ -4472,22 +4472,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>50000</v>
+        <v>61596</v>
       </c>
       <c r="G113" t="n">
-        <v>7500</v>
+        <v>9239</v>
       </c>
       <c r="H113" t="n">
-        <v>42500</v>
+        <v>52357</v>
       </c>
     </row>
     <row r="114">
@@ -4508,22 +4508,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>50000</v>
+        <v>50062</v>
       </c>
       <c r="G114" t="n">
-        <v>7500</v>
+        <v>7509</v>
       </c>
       <c r="H114" t="n">
-        <v>42500</v>
+        <v>42553</v>
       </c>
     </row>
     <row r="115">
@@ -4544,22 +4544,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>May 2020</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>50000</v>
+        <v>49525</v>
       </c>
       <c r="G115" t="n">
-        <v>7500</v>
+        <v>7428</v>
       </c>
       <c r="H115" t="n">
-        <v>42500</v>
+        <v>42097</v>
       </c>
     </row>
     <row r="116">
@@ -4580,22 +4580,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>50000</v>
+        <v>50689</v>
       </c>
       <c r="G116" t="n">
-        <v>7500</v>
+        <v>7603</v>
       </c>
       <c r="H116" t="n">
-        <v>42500</v>
+        <v>43086</v>
       </c>
     </row>
     <row r="117">
@@ -4616,22 +4616,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Aug 2020</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>50000</v>
+        <v>49791</v>
       </c>
       <c r="G117" t="n">
-        <v>7500</v>
+        <v>7468</v>
       </c>
       <c r="H117" t="n">
-        <v>42500</v>
+        <v>42323</v>
       </c>
     </row>
     <row r="118">
@@ -4661,13 +4661,13 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>50000</v>
+        <v>49601</v>
       </c>
       <c r="G118" t="n">
-        <v>7500</v>
+        <v>7440</v>
       </c>
       <c r="H118" t="n">
-        <v>42500</v>
+        <v>42161</v>
       </c>
     </row>
     <row r="119">
@@ -4697,13 +4697,13 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>50000</v>
+        <v>49265</v>
       </c>
       <c r="G119" t="n">
-        <v>7500</v>
+        <v>7389</v>
       </c>
       <c r="H119" t="n">
-        <v>42500</v>
+        <v>41876</v>
       </c>
     </row>
     <row r="120">
@@ -4724,22 +4724,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>Jan 2021</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>50000</v>
+        <v>50914</v>
       </c>
       <c r="G120" t="n">
-        <v>7500</v>
+        <v>7637</v>
       </c>
       <c r="H120" t="n">
-        <v>42500</v>
+        <v>43277</v>
       </c>
     </row>
     <row r="121">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Jan 2021</t>
+          <t>Feb 2021</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>52500</v>
+        <v>50438</v>
       </c>
       <c r="G121" t="n">
-        <v>7875</v>
+        <v>7565</v>
       </c>
       <c r="H121" t="n">
-        <v>44625</v>
+        <v>42873</v>
       </c>
     </row>
     <row r="122">
@@ -4796,22 +4796,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Feb 2021</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>52500</v>
+        <v>58301</v>
       </c>
       <c r="G122" t="n">
-        <v>7875</v>
+        <v>8745</v>
       </c>
       <c r="H122" t="n">
-        <v>44625</v>
+        <v>49556</v>
       </c>
     </row>
     <row r="123">
@@ -4832,22 +4832,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>Apr 2021</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>52500</v>
+        <v>49114</v>
       </c>
       <c r="G123" t="n">
-        <v>7875</v>
+        <v>7367</v>
       </c>
       <c r="H123" t="n">
-        <v>44625</v>
+        <v>41747</v>
       </c>
     </row>
     <row r="124">
@@ -4868,22 +4868,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Apr 2021</t>
+          <t>May 2021</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>52500</v>
+        <v>50554</v>
       </c>
       <c r="G124" t="n">
-        <v>7875</v>
+        <v>7583</v>
       </c>
       <c r="H124" t="n">
-        <v>44625</v>
+        <v>42971</v>
       </c>
     </row>
     <row r="125">
@@ -4913,13 +4913,13 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>52500</v>
+        <v>58780</v>
       </c>
       <c r="G125" t="n">
-        <v>7875</v>
+        <v>8817</v>
       </c>
       <c r="H125" t="n">
-        <v>44625</v>
+        <v>49963</v>
       </c>
     </row>
     <row r="126">
@@ -4949,13 +4949,13 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>52500</v>
+        <v>49381</v>
       </c>
       <c r="G126" t="n">
-        <v>7875</v>
+        <v>7407</v>
       </c>
       <c r="H126" t="n">
-        <v>44625</v>
+        <v>41974</v>
       </c>
     </row>
     <row r="127">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="F127" t="n">
+        <v>61764</v>
+      </c>
+      <c r="G127" t="n">
+        <v>9264</v>
+      </c>
+      <c r="H127" t="n">
         <v>52500</v>
-      </c>
-      <c r="G127" t="n">
-        <v>7875</v>
-      </c>
-      <c r="H127" t="n">
-        <v>44625</v>
       </c>
     </row>
     <row r="128">
@@ -5012,22 +5012,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>52500</v>
+        <v>49117</v>
       </c>
       <c r="G128" t="n">
-        <v>7875</v>
+        <v>7367</v>
       </c>
       <c r="H128" t="n">
-        <v>44625</v>
+        <v>41750</v>
       </c>
     </row>
     <row r="129">
@@ -5048,22 +5048,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>Nov 2021</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>52500</v>
+        <v>49273</v>
       </c>
       <c r="G129" t="n">
-        <v>7875</v>
+        <v>7390</v>
       </c>
       <c r="H129" t="n">
-        <v>44625</v>
+        <v>41883</v>
       </c>
     </row>
     <row r="130">
@@ -5084,22 +5084,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Jan 2022</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>55125</v>
+        <v>83907</v>
       </c>
       <c r="G130" t="n">
-        <v>8268</v>
+        <v>12586</v>
       </c>
       <c r="H130" t="n">
-        <v>46857</v>
+        <v>71321</v>
       </c>
     </row>
     <row r="131">
@@ -5120,22 +5120,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Feb 2022</t>
+          <t>Jan 2022</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>55125</v>
+        <v>50857</v>
       </c>
       <c r="G131" t="n">
-        <v>8268</v>
+        <v>7628</v>
       </c>
       <c r="H131" t="n">
-        <v>46857</v>
+        <v>43229</v>
       </c>
     </row>
     <row r="132">
@@ -5165,13 +5165,13 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>55125</v>
+        <v>58813</v>
       </c>
       <c r="G132" t="n">
-        <v>8268</v>
+        <v>8821</v>
       </c>
       <c r="H132" t="n">
-        <v>46857</v>
+        <v>49992</v>
       </c>
     </row>
     <row r="133">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>55125</v>
+        <v>49636</v>
       </c>
       <c r="G133" t="n">
-        <v>8268</v>
+        <v>7445</v>
       </c>
       <c r="H133" t="n">
-        <v>46857</v>
+        <v>42191</v>
       </c>
     </row>
     <row r="134">
@@ -5228,22 +5228,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>May 2022</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>55125</v>
+        <v>59760</v>
       </c>
       <c r="G134" t="n">
-        <v>8268</v>
+        <v>8964</v>
       </c>
       <c r="H134" t="n">
-        <v>46857</v>
+        <v>50796</v>
       </c>
     </row>
     <row r="135">
@@ -5264,22 +5264,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>Jul 2022</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>55125</v>
+        <v>50142</v>
       </c>
       <c r="G135" t="n">
-        <v>8268</v>
+        <v>7521</v>
       </c>
       <c r="H135" t="n">
-        <v>46857</v>
+        <v>42621</v>
       </c>
     </row>
     <row r="136">
@@ -5300,22 +5300,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Jul 2022</t>
+          <t>Aug 2022</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>65000</v>
+        <v>49078</v>
       </c>
       <c r="G136" t="n">
-        <v>9750</v>
+        <v>7361</v>
       </c>
       <c r="H136" t="n">
-        <v>55250</v>
+        <v>41717</v>
       </c>
     </row>
     <row r="137">
@@ -5336,22 +5336,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>Oct 2022</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>65000</v>
+        <v>49481</v>
       </c>
       <c r="G137" t="n">
-        <v>9750</v>
+        <v>7422</v>
       </c>
       <c r="H137" t="n">
-        <v>55250</v>
+        <v>42059</v>
       </c>
     </row>
     <row r="138">
@@ -5372,22 +5372,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Nov 2022</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>55000</v>
+        <v>49585</v>
       </c>
       <c r="G138" t="n">
-        <v>8250</v>
+        <v>7437</v>
       </c>
       <c r="H138" t="n">
-        <v>46750</v>
+        <v>42148</v>
       </c>
     </row>
     <row r="139">
@@ -5408,22 +5408,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>Dec 2022</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>55000</v>
+        <v>82587</v>
       </c>
       <c r="G139" t="n">
-        <v>8250</v>
+        <v>12388</v>
       </c>
       <c r="H139" t="n">
-        <v>46750</v>
+        <v>70199</v>
       </c>
     </row>
     <row r="140">
@@ -5444,22 +5444,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Nov 2022</t>
+          <t>Jan 2023</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>55000</v>
+        <v>50048</v>
       </c>
       <c r="G140" t="n">
-        <v>8250</v>
+        <v>7507</v>
       </c>
       <c r="H140" t="n">
-        <v>46750</v>
+        <v>42541</v>
       </c>
     </row>
     <row r="141">
@@ -5480,22 +5480,22 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Jan 2023</t>
+          <t>Feb 2023</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>57750</v>
+        <v>49322</v>
       </c>
       <c r="G141" t="n">
-        <v>8662</v>
+        <v>7398</v>
       </c>
       <c r="H141" t="n">
-        <v>49088</v>
+        <v>41924</v>
       </c>
     </row>
     <row r="142">
@@ -5516,22 +5516,22 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>Mar 2023</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>57750</v>
+        <v>64341</v>
       </c>
       <c r="G142" t="n">
-        <v>8662</v>
+        <v>9651</v>
       </c>
       <c r="H142" t="n">
-        <v>49088</v>
+        <v>54690</v>
       </c>
     </row>
     <row r="143">
@@ -5552,22 +5552,22 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mar 2023</t>
+          <t>Apr 2023</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>57750</v>
+        <v>49236</v>
       </c>
       <c r="G143" t="n">
-        <v>8662</v>
+        <v>7385</v>
       </c>
       <c r="H143" t="n">
-        <v>49088</v>
+        <v>41851</v>
       </c>
     </row>
     <row r="144">
@@ -5597,13 +5597,13 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>57750</v>
+        <v>50756</v>
       </c>
       <c r="G144" t="n">
-        <v>8662</v>
+        <v>7613</v>
       </c>
       <c r="H144" t="n">
-        <v>49088</v>
+        <v>43143</v>
       </c>
     </row>
     <row r="145">
@@ -5633,13 +5633,13 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>57750</v>
+        <v>64798</v>
       </c>
       <c r="G145" t="n">
-        <v>8662</v>
+        <v>9719</v>
       </c>
       <c r="H145" t="n">
-        <v>49088</v>
+        <v>55079</v>
       </c>
     </row>
     <row r="146">
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>57750</v>
+        <v>50437</v>
       </c>
       <c r="G146" t="n">
-        <v>8662</v>
+        <v>7565</v>
       </c>
       <c r="H146" t="n">
-        <v>49088</v>
+        <v>42872</v>
       </c>
     </row>
     <row r="147">
@@ -5705,13 +5705,13 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>57750</v>
+        <v>50038</v>
       </c>
       <c r="G147" t="n">
-        <v>8662</v>
+        <v>7505</v>
       </c>
       <c r="H147" t="n">
-        <v>49088</v>
+        <v>42533</v>
       </c>
     </row>
     <row r="148">
@@ -5741,13 +5741,13 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>57750</v>
+        <v>59895</v>
       </c>
       <c r="G148" t="n">
-        <v>8662</v>
+        <v>8984</v>
       </c>
       <c r="H148" t="n">
-        <v>49088</v>
+        <v>50911</v>
       </c>
     </row>
     <row r="149">
@@ -5777,13 +5777,13 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>57750</v>
+        <v>50385</v>
       </c>
       <c r="G149" t="n">
-        <v>8662</v>
+        <v>7557</v>
       </c>
       <c r="H149" t="n">
-        <v>49088</v>
+        <v>42828</v>
       </c>
     </row>
     <row r="150">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>57750</v>
+        <v>49287</v>
       </c>
       <c r="G150" t="n">
-        <v>8662</v>
+        <v>7393</v>
       </c>
       <c r="H150" t="n">
-        <v>49088</v>
+        <v>41894</v>
       </c>
     </row>
     <row r="151">
@@ -5849,13 +5849,13 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>57750</v>
+        <v>80995</v>
       </c>
       <c r="G151" t="n">
-        <v>8662</v>
+        <v>12149</v>
       </c>
       <c r="H151" t="n">
-        <v>49088</v>
+        <v>68846</v>
       </c>
     </row>
   </sheetData>

--- a/Task-1/mock_data/client_summary.xlsx
+++ b/Task-1/mock_data/client_summary.xlsx
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jan 2019</t>
+          <t>Feb 2019</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>63918</v>
+        <v>65337</v>
       </c>
       <c r="H2" t="n">
-        <v>9587</v>
+        <v>9800</v>
       </c>
       <c r="I2" t="n">
-        <v>54331</v>
+        <v>55537</v>
       </c>
     </row>
     <row r="3">
@@ -527,22 +527,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Feb 2019</t>
+          <t>Mar 2019</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>65639</v>
+        <v>80863</v>
       </c>
       <c r="H3" t="n">
-        <v>9845</v>
+        <v>12129</v>
       </c>
       <c r="I3" t="n">
-        <v>55794</v>
+        <v>68734</v>
       </c>
     </row>
     <row r="4">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>66077</v>
+        <v>64173</v>
       </c>
       <c r="H4" t="n">
-        <v>9911</v>
+        <v>9625</v>
       </c>
       <c r="I4" t="n">
-        <v>56166</v>
+        <v>54548</v>
       </c>
     </row>
     <row r="5">
@@ -609,22 +609,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jun 2019</t>
+          <t>May 2019</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>81182</v>
+        <v>65613</v>
       </c>
       <c r="H5" t="n">
-        <v>12177</v>
+        <v>9841</v>
       </c>
       <c r="I5" t="n">
-        <v>69005</v>
+        <v>55772</v>
       </c>
     </row>
     <row r="6">
@@ -650,22 +650,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jul 2019</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>65474</v>
+        <v>77611</v>
       </c>
       <c r="H6" t="n">
-        <v>9821</v>
+        <v>11641</v>
       </c>
       <c r="I6" t="n">
-        <v>55653</v>
+        <v>65970</v>
       </c>
     </row>
     <row r="7">
@@ -691,22 +691,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aug 2019</t>
+          <t>Jul 2019</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>63949</v>
+        <v>64038</v>
       </c>
       <c r="H7" t="n">
-        <v>9592</v>
+        <v>9605</v>
       </c>
       <c r="I7" t="n">
-        <v>54357</v>
+        <v>54433</v>
       </c>
     </row>
     <row r="8">
@@ -732,22 +732,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sep 2019</t>
+          <t>Aug 2019</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>74808</v>
+        <v>65281</v>
       </c>
       <c r="H8" t="n">
-        <v>11221</v>
+        <v>9792</v>
       </c>
       <c r="I8" t="n">
-        <v>63587</v>
+        <v>55489</v>
       </c>
     </row>
     <row r="9">
@@ -773,22 +773,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oct 2019</t>
+          <t>Nov 2019</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>65709</v>
+        <v>64103</v>
       </c>
       <c r="H9" t="n">
-        <v>9856</v>
+        <v>9615</v>
       </c>
       <c r="I9" t="n">
-        <v>55853</v>
+        <v>54488</v>
       </c>
     </row>
     <row r="10">
@@ -814,22 +814,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>124410</v>
+        <v>65213</v>
       </c>
       <c r="H10" t="n">
-        <v>18661</v>
+        <v>9781</v>
       </c>
       <c r="I10" t="n">
-        <v>105749</v>
+        <v>55432</v>
       </c>
     </row>
     <row r="11">
@@ -855,22 +855,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jan 2020</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>64856</v>
+        <v>82245</v>
       </c>
       <c r="H11" t="n">
-        <v>9728</v>
+        <v>12336</v>
       </c>
       <c r="I11" t="n">
-        <v>55128</v>
+        <v>69909</v>
       </c>
     </row>
     <row r="12">
@@ -896,22 +896,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Feb 2020</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>65945</v>
+        <v>64397</v>
       </c>
       <c r="H12" t="n">
-        <v>9891</v>
+        <v>9659</v>
       </c>
       <c r="I12" t="n">
-        <v>56054</v>
+        <v>54738</v>
       </c>
     </row>
     <row r="13">
@@ -937,22 +937,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Apr 2020</t>
+          <t>May 2020</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>64721</v>
+        <v>65461</v>
       </c>
       <c r="H13" t="n">
-        <v>9708</v>
+        <v>9819</v>
       </c>
       <c r="I13" t="n">
-        <v>55013</v>
+        <v>55642</v>
       </c>
     </row>
     <row r="14">
@@ -978,22 +978,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>65153</v>
+        <v>83688</v>
       </c>
       <c r="H14" t="n">
-        <v>9772</v>
+        <v>12553</v>
       </c>
       <c r="I14" t="n">
-        <v>55381</v>
+        <v>71135</v>
       </c>
     </row>
     <row r="15">
@@ -1019,22 +1019,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>84699</v>
+        <v>65983</v>
       </c>
       <c r="H15" t="n">
-        <v>12704</v>
+        <v>9897</v>
       </c>
       <c r="I15" t="n">
-        <v>71995</v>
+        <v>56086</v>
       </c>
     </row>
     <row r="16">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>Aug 2020</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>65616</v>
+        <v>65940</v>
       </c>
       <c r="H16" t="n">
-        <v>9842</v>
+        <v>9891</v>
       </c>
       <c r="I16" t="n">
-        <v>55774</v>
+        <v>56049</v>
       </c>
     </row>
     <row r="17">
@@ -1101,22 +1101,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>65552</v>
+        <v>78813</v>
       </c>
       <c r="H17" t="n">
-        <v>9832</v>
+        <v>11821</v>
       </c>
       <c r="I17" t="n">
-        <v>55720</v>
+        <v>66992</v>
       </c>
     </row>
     <row r="18">
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>64384</v>
+        <v>64879</v>
       </c>
       <c r="H18" t="n">
-        <v>9657</v>
+        <v>9731</v>
       </c>
       <c r="I18" t="n">
-        <v>54727</v>
+        <v>55148</v>
       </c>
     </row>
     <row r="19">
@@ -1183,22 +1183,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nov 2020</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>65221</v>
+        <v>127641</v>
       </c>
       <c r="H19" t="n">
-        <v>9783</v>
+        <v>19146</v>
       </c>
       <c r="I19" t="n">
-        <v>55438</v>
+        <v>108495</v>
       </c>
     </row>
     <row r="20">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>64157</v>
+        <v>65258</v>
       </c>
       <c r="H20" t="n">
-        <v>9623</v>
+        <v>9788</v>
       </c>
       <c r="I20" t="n">
-        <v>54534</v>
+        <v>55470</v>
       </c>
     </row>
     <row r="21">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>65101</v>
+        <v>64716</v>
       </c>
       <c r="H21" t="n">
-        <v>9765</v>
+        <v>9707</v>
       </c>
       <c r="I21" t="n">
-        <v>55336</v>
+        <v>55009</v>
       </c>
     </row>
     <row r="22">
@@ -1315,13 +1315,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>83970</v>
+        <v>84053</v>
       </c>
       <c r="H22" t="n">
-        <v>12595</v>
+        <v>12607</v>
       </c>
       <c r="I22" t="n">
-        <v>71375</v>
+        <v>71446</v>
       </c>
     </row>
     <row r="23">
@@ -1356,13 +1356,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>63845</v>
+        <v>63822</v>
       </c>
       <c r="H23" t="n">
-        <v>9576</v>
+        <v>9573</v>
       </c>
       <c r="I23" t="n">
-        <v>54269</v>
+        <v>54249</v>
       </c>
     </row>
     <row r="24">
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>64549</v>
+        <v>65962</v>
       </c>
       <c r="H24" t="n">
-        <v>9682</v>
+        <v>9894</v>
       </c>
       <c r="I24" t="n">
-        <v>54867</v>
+        <v>56068</v>
       </c>
     </row>
     <row r="25">
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>80810</v>
+        <v>77332</v>
       </c>
       <c r="H25" t="n">
-        <v>12121</v>
+        <v>11599</v>
       </c>
       <c r="I25" t="n">
-        <v>68689</v>
+        <v>65733</v>
       </c>
     </row>
     <row r="26">
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>65697</v>
+        <v>65188</v>
       </c>
       <c r="H26" t="n">
-        <v>9854</v>
+        <v>9778</v>
       </c>
       <c r="I26" t="n">
-        <v>55843</v>
+        <v>55410</v>
       </c>
     </row>
     <row r="27">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>64891</v>
+        <v>65374</v>
       </c>
       <c r="H27" t="n">
-        <v>9733</v>
+        <v>9806</v>
       </c>
       <c r="I27" t="n">
-        <v>55158</v>
+        <v>55568</v>
       </c>
     </row>
     <row r="28">
@@ -1561,13 +1561,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>84116</v>
+        <v>77149</v>
       </c>
       <c r="H28" t="n">
-        <v>12617</v>
+        <v>11572</v>
       </c>
       <c r="I28" t="n">
-        <v>71499</v>
+        <v>65577</v>
       </c>
     </row>
     <row r="29">
@@ -1602,13 +1602,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>64473</v>
+        <v>64815</v>
       </c>
       <c r="H29" t="n">
-        <v>9670</v>
+        <v>9722</v>
       </c>
       <c r="I29" t="n">
-        <v>54803</v>
+        <v>55093</v>
       </c>
     </row>
     <row r="30">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>121915</v>
+        <v>120171</v>
       </c>
       <c r="H30" t="n">
-        <v>18287</v>
+        <v>18025</v>
       </c>
       <c r="I30" t="n">
-        <v>103628</v>
+        <v>102146</v>
       </c>
     </row>
     <row r="31">
@@ -1684,13 +1684,13 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>63748</v>
+        <v>65290</v>
       </c>
       <c r="H31" t="n">
-        <v>9562</v>
+        <v>9793</v>
       </c>
       <c r="I31" t="n">
-        <v>54186</v>
+        <v>55497</v>
       </c>
     </row>
     <row r="32">
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>65158</v>
+        <v>64850</v>
       </c>
       <c r="H32" t="n">
-        <v>9773</v>
+        <v>9727</v>
       </c>
       <c r="I32" t="n">
-        <v>55385</v>
+        <v>55123</v>
       </c>
     </row>
     <row r="33">
@@ -1766,13 +1766,13 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>75982</v>
+        <v>84610</v>
       </c>
       <c r="H33" t="n">
-        <v>11397</v>
+        <v>12691</v>
       </c>
       <c r="I33" t="n">
-        <v>64585</v>
+        <v>71919</v>
       </c>
     </row>
     <row r="34">
@@ -1807,13 +1807,13 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>66150</v>
+        <v>64017</v>
       </c>
       <c r="H34" t="n">
-        <v>9922</v>
+        <v>9602</v>
       </c>
       <c r="I34" t="n">
-        <v>56228</v>
+        <v>54415</v>
       </c>
     </row>
     <row r="35">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>65978</v>
+        <v>66083</v>
       </c>
       <c r="H35" t="n">
-        <v>9896</v>
+        <v>9912</v>
       </c>
       <c r="I35" t="n">
-        <v>56082</v>
+        <v>56171</v>
       </c>
     </row>
     <row r="36">
@@ -1889,13 +1889,13 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>81248</v>
+        <v>84438</v>
       </c>
       <c r="H36" t="n">
-        <v>12187</v>
+        <v>12665</v>
       </c>
       <c r="I36" t="n">
-        <v>69061</v>
+        <v>71773</v>
       </c>
     </row>
     <row r="37">
@@ -1921,22 +1921,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Jul 2022</t>
+          <t>Aug 2022</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>64855</v>
+        <v>66232</v>
       </c>
       <c r="H37" t="n">
-        <v>9728</v>
+        <v>9934</v>
       </c>
       <c r="I37" t="n">
-        <v>55127</v>
+        <v>56298</v>
       </c>
     </row>
     <row r="38">
@@ -1962,22 +1962,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>64370</v>
+        <v>81627</v>
       </c>
       <c r="H38" t="n">
-        <v>9655</v>
+        <v>12244</v>
       </c>
       <c r="I38" t="n">
-        <v>54715</v>
+        <v>69383</v>
       </c>
     </row>
     <row r="39">
@@ -2003,22 +2003,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Oct 2022</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>76100</v>
+        <v>65703</v>
       </c>
       <c r="H39" t="n">
-        <v>11415</v>
+        <v>9855</v>
       </c>
       <c r="I39" t="n">
-        <v>64685</v>
+        <v>55848</v>
       </c>
     </row>
     <row r="40">
@@ -2044,22 +2044,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>Nov 2022</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>64290</v>
+        <v>64388</v>
       </c>
       <c r="H40" t="n">
-        <v>9643</v>
+        <v>9658</v>
       </c>
       <c r="I40" t="n">
-        <v>54647</v>
+        <v>54730</v>
       </c>
     </row>
     <row r="41">
@@ -2085,22 +2085,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nov 2022</t>
+          <t>Dec 2022</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>64597</v>
+        <v>112681</v>
       </c>
       <c r="H41" t="n">
-        <v>9689</v>
+        <v>16902</v>
       </c>
       <c r="I41" t="n">
-        <v>54908</v>
+        <v>95779</v>
       </c>
     </row>
     <row r="42">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dec 2022</t>
+          <t>Feb 2023</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>118186</v>
+        <v>65102</v>
       </c>
       <c r="H42" t="n">
-        <v>17727</v>
+        <v>9765</v>
       </c>
       <c r="I42" t="n">
-        <v>100459</v>
+        <v>55337</v>
       </c>
     </row>
     <row r="43">
@@ -2167,22 +2167,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>Mar 2023</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>64069</v>
+        <v>77282</v>
       </c>
       <c r="H43" t="n">
-        <v>9610</v>
+        <v>11592</v>
       </c>
       <c r="I43" t="n">
-        <v>54459</v>
+        <v>65690</v>
       </c>
     </row>
     <row r="44">
@@ -2208,22 +2208,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mar 2023</t>
+          <t>Apr 2023</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>80855</v>
+        <v>64381</v>
       </c>
       <c r="H44" t="n">
-        <v>12128</v>
+        <v>9657</v>
       </c>
       <c r="I44" t="n">
-        <v>68727</v>
+        <v>54724</v>
       </c>
     </row>
     <row r="45">
@@ -2249,22 +2249,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Apr 2023</t>
+          <t>May 2023</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>64335</v>
+        <v>65307</v>
       </c>
       <c r="H45" t="n">
-        <v>9650</v>
+        <v>9796</v>
       </c>
       <c r="I45" t="n">
-        <v>54685</v>
+        <v>55511</v>
       </c>
     </row>
     <row r="46">
@@ -2290,22 +2290,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>64505</v>
+        <v>81259</v>
       </c>
       <c r="H46" t="n">
-        <v>9675</v>
+        <v>12188</v>
       </c>
       <c r="I46" t="n">
-        <v>54830</v>
+        <v>69071</v>
       </c>
     </row>
     <row r="47">
@@ -2331,22 +2331,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>Jul 2023</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>78359</v>
+        <v>64907</v>
       </c>
       <c r="H47" t="n">
-        <v>11753</v>
+        <v>9736</v>
       </c>
       <c r="I47" t="n">
-        <v>66606</v>
+        <v>55171</v>
       </c>
     </row>
     <row r="48">
@@ -2372,22 +2372,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>Aug 2023</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>64308</v>
+        <v>65691</v>
       </c>
       <c r="H48" t="n">
-        <v>9646</v>
+        <v>9853</v>
       </c>
       <c r="I48" t="n">
-        <v>54662</v>
+        <v>55838</v>
       </c>
     </row>
     <row r="49">
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>82404</v>
+        <v>77408</v>
       </c>
       <c r="H49" t="n">
-        <v>12360</v>
+        <v>11611</v>
       </c>
       <c r="I49" t="n">
-        <v>70044</v>
+        <v>65797</v>
       </c>
     </row>
     <row r="50">
@@ -2463,13 +2463,13 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>64085</v>
+        <v>64462</v>
       </c>
       <c r="H50" t="n">
-        <v>9612</v>
+        <v>9669</v>
       </c>
       <c r="I50" t="n">
-        <v>54473</v>
+        <v>54793</v>
       </c>
     </row>
     <row r="51">
@@ -2495,22 +2495,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nov 2023</t>
+          <t>Dec 2023</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>65438</v>
+        <v>121749</v>
       </c>
       <c r="H51" t="n">
-        <v>9815</v>
+        <v>18262</v>
       </c>
       <c r="I51" t="n">
-        <v>55623</v>
+        <v>103487</v>
       </c>
     </row>
     <row r="52">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Feb 2019</t>
+          <t>Jan 2019</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>May 2019</t>
+          <t>Apr 2019</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jun 2019</t>
+          <t>May 2019</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aug 2019</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sep 2019</t>
+          <t>Jul 2019</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Oct 2019</t>
+          <t>Aug 2019</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nov 2019</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>Oct 2019</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2905,22 +2905,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jan 2020</t>
+          <t>Nov 2019</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>44000</v>
+        <v>40000</v>
       </c>
       <c r="H61" t="n">
-        <v>4400</v>
+        <v>4000</v>
       </c>
       <c r="I61" t="n">
-        <v>39600</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="62">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Feb 2020</t>
+          <t>Dec 2019</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>44000</v>
+        <v>40000</v>
       </c>
       <c r="H62" t="n">
-        <v>4400</v>
+        <v>4000</v>
       </c>
       <c r="I62" t="n">
-        <v>39600</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="63">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Feb 2020</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Apr 2020</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3069,12 +3069,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>May 2020</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Aug 2020</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oct 2020</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nov 2020</t>
+          <t>Oct 2020</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -3356,22 +3356,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Jan 2021</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>48400</v>
+        <v>44000</v>
       </c>
       <c r="H72" t="n">
-        <v>4840</v>
+        <v>4400</v>
       </c>
       <c r="I72" t="n">
-        <v>43560</v>
+        <v>39600</v>
       </c>
     </row>
     <row r="73">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Feb 2021</t>
+          <t>Jan 2021</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Apr 2021</t>
+          <t>May 2021</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>Aug 2021</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>Nov 2021</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jan 2022</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>53240</v>
+        <v>48400</v>
       </c>
       <c r="H82" t="n">
-        <v>5324</v>
+        <v>4840</v>
       </c>
       <c r="I82" t="n">
-        <v>47916</v>
+        <v>43560</v>
       </c>
     </row>
     <row r="83">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Feb 2022</t>
+          <t>Jan 2022</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mar 2022</t>
+          <t>Feb 2022</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Apr 2022</t>
+          <t>Mar 2022</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>Apr 2022</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>May 2022</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nov 2022</t>
+          <t>Jul 2022</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dec 2022</t>
+          <t>Aug 2022</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -4135,22 +4135,22 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Jan 2023</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>58564</v>
+        <v>53240</v>
       </c>
       <c r="H91" t="n">
-        <v>5856</v>
+        <v>5324</v>
       </c>
       <c r="I91" t="n">
-        <v>52708</v>
+        <v>47916</v>
       </c>
     </row>
     <row r="92">
@@ -4176,22 +4176,22 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>Oct 2022</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>58564</v>
+        <v>53240</v>
       </c>
       <c r="H92" t="n">
-        <v>5856</v>
+        <v>5324</v>
       </c>
       <c r="I92" t="n">
-        <v>52708</v>
+        <v>47916</v>
       </c>
     </row>
     <row r="93">
@@ -4217,22 +4217,22 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mar 2023</t>
+          <t>Dec 2022</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>58564</v>
+        <v>53240</v>
       </c>
       <c r="H93" t="n">
-        <v>5856</v>
+        <v>5324</v>
       </c>
       <c r="I93" t="n">
-        <v>52708</v>
+        <v>47916</v>
       </c>
     </row>
     <row r="94">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Apr 2023</t>
+          <t>Feb 2023</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>Mar 2023</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>Apr 2023</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Aug 2023</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>Jul 2023</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Oct 2023</t>
+          <t>Aug 2023</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nov 2023</t>
+          <t>Oct 2023</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -4586,22 +4586,22 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Jun 2019</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>129866</v>
+        <v>139790</v>
       </c>
       <c r="H102" t="n">
-        <v>12986</v>
+        <v>13979</v>
       </c>
       <c r="I102" t="n">
-        <v>116880</v>
+        <v>125811</v>
       </c>
     </row>
     <row r="103">
@@ -4636,13 +4636,13 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>117170</v>
+        <v>109859</v>
       </c>
       <c r="H103" t="n">
-        <v>11717</v>
+        <v>10985</v>
       </c>
       <c r="I103" t="n">
-        <v>105453</v>
+        <v>98874</v>
       </c>
     </row>
     <row r="104">
@@ -4677,13 +4677,13 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>113345</v>
+        <v>131528</v>
       </c>
       <c r="H104" t="n">
-        <v>11334</v>
+        <v>13152</v>
       </c>
       <c r="I104" t="n">
-        <v>102011</v>
+        <v>118376</v>
       </c>
     </row>
     <row r="105">
@@ -4709,22 +4709,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>119477</v>
+        <v>108704</v>
       </c>
       <c r="H105" t="n">
-        <v>11947</v>
+        <v>10870</v>
       </c>
       <c r="I105" t="n">
-        <v>107530</v>
+        <v>97834</v>
       </c>
     </row>
     <row r="106">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>110615</v>
+        <v>108062</v>
       </c>
       <c r="H106" t="n">
-        <v>11061</v>
+        <v>10806</v>
       </c>
       <c r="I106" t="n">
-        <v>99554</v>
+        <v>97256</v>
       </c>
     </row>
     <row r="107">
@@ -4791,22 +4791,22 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>109522</v>
+        <v>140234</v>
       </c>
       <c r="H107" t="n">
-        <v>10952</v>
+        <v>14023</v>
       </c>
       <c r="I107" t="n">
-        <v>98570</v>
+        <v>126211</v>
       </c>
     </row>
     <row r="108">
@@ -4841,13 +4841,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>147961</v>
+        <v>121951</v>
       </c>
       <c r="H108" t="n">
-        <v>14796</v>
+        <v>12195</v>
       </c>
       <c r="I108" t="n">
-        <v>133165</v>
+        <v>109756</v>
       </c>
     </row>
     <row r="109">
@@ -4873,22 +4873,22 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mar 2023</t>
+          <t>Dec 2022</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>121624</v>
+        <v>130520</v>
       </c>
       <c r="H109" t="n">
-        <v>12162</v>
+        <v>13052</v>
       </c>
       <c r="I109" t="n">
-        <v>109462</v>
+        <v>117468</v>
       </c>
     </row>
     <row r="110">
@@ -4923,13 +4923,13 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>138996</v>
+        <v>126471</v>
       </c>
       <c r="H110" t="n">
-        <v>13899</v>
+        <v>12647</v>
       </c>
       <c r="I110" t="n">
-        <v>125097</v>
+        <v>113824</v>
       </c>
     </row>
     <row r="111">
@@ -4955,22 +4955,22 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dec 2023</t>
+          <t>Sep 2023</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>119220</v>
+        <v>148458</v>
       </c>
       <c r="H111" t="n">
-        <v>11922</v>
+        <v>14845</v>
       </c>
       <c r="I111" t="n">
-        <v>107298</v>
+        <v>133613</v>
       </c>
     </row>
     <row r="112">
@@ -4996,22 +4996,22 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Jan 2019</t>
+          <t>Feb 2019</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>86185</v>
+        <v>84963</v>
       </c>
       <c r="H112" t="n">
-        <v>12927</v>
+        <v>12744</v>
       </c>
       <c r="I112" t="n">
-        <v>73258</v>
+        <v>72219</v>
       </c>
     </row>
     <row r="113">
@@ -5037,22 +5037,22 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Feb 2019</t>
+          <t>May 2019</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>83390</v>
+        <v>83746</v>
       </c>
       <c r="H113" t="n">
-        <v>12508</v>
+        <v>12561</v>
       </c>
       <c r="I113" t="n">
-        <v>70882</v>
+        <v>71185</v>
       </c>
     </row>
     <row r="114">
@@ -5078,22 +5078,22 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mar 2019</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>99963</v>
+        <v>108509</v>
       </c>
       <c r="H114" t="n">
-        <v>14994</v>
+        <v>16276</v>
       </c>
       <c r="I114" t="n">
-        <v>84969</v>
+        <v>92233</v>
       </c>
     </row>
     <row r="115">
@@ -5119,22 +5119,22 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Apr 2019</t>
+          <t>Jul 2019</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>84740</v>
+        <v>83404</v>
       </c>
       <c r="H115" t="n">
-        <v>12711</v>
+        <v>12510</v>
       </c>
       <c r="I115" t="n">
-        <v>72029</v>
+        <v>70894</v>
       </c>
     </row>
     <row r="116">
@@ -5160,22 +5160,22 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Jun 2019</t>
+          <t>Aug 2019</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>102348</v>
+        <v>84212</v>
       </c>
       <c r="H116" t="n">
-        <v>15352</v>
+        <v>12631</v>
       </c>
       <c r="I116" t="n">
-        <v>86996</v>
+        <v>71581</v>
       </c>
     </row>
     <row r="117">
@@ -5201,22 +5201,22 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Aug 2019</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>83914</v>
+        <v>109349</v>
       </c>
       <c r="H117" t="n">
-        <v>12587</v>
+        <v>16402</v>
       </c>
       <c r="I117" t="n">
-        <v>71327</v>
+        <v>92947</v>
       </c>
     </row>
     <row r="118">
@@ -5242,22 +5242,22 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sep 2019</t>
+          <t>Oct 2019</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>104038</v>
+        <v>84421</v>
       </c>
       <c r="H118" t="n">
-        <v>15605</v>
+        <v>12663</v>
       </c>
       <c r="I118" t="n">
-        <v>88433</v>
+        <v>71758</v>
       </c>
     </row>
     <row r="119">
@@ -5283,22 +5283,22 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Oct 2019</t>
+          <t>Nov 2019</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>86257</v>
+        <v>84943</v>
       </c>
       <c r="H119" t="n">
-        <v>12938</v>
+        <v>12741</v>
       </c>
       <c r="I119" t="n">
-        <v>73319</v>
+        <v>72202</v>
       </c>
     </row>
     <row r="120">
@@ -5324,22 +5324,22 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nov 2019</t>
+          <t>Dec 2019</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>84030</v>
+        <v>145693</v>
       </c>
       <c r="H120" t="n">
-        <v>12604</v>
+        <v>21853</v>
       </c>
       <c r="I120" t="n">
-        <v>71426</v>
+        <v>123840</v>
       </c>
     </row>
     <row r="121">
@@ -5374,13 +5374,13 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>85997</v>
+        <v>85418</v>
       </c>
       <c r="H121" t="n">
-        <v>12899</v>
+        <v>12812</v>
       </c>
       <c r="I121" t="n">
-        <v>73098</v>
+        <v>72606</v>
       </c>
     </row>
     <row r="122">
@@ -5415,13 +5415,13 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>83384</v>
+        <v>85508</v>
       </c>
       <c r="H122" t="n">
-        <v>12507</v>
+        <v>12826</v>
       </c>
       <c r="I122" t="n">
-        <v>70877</v>
+        <v>72682</v>
       </c>
     </row>
     <row r="123">
@@ -5456,13 +5456,13 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>108586</v>
+        <v>97831</v>
       </c>
       <c r="H123" t="n">
-        <v>16287</v>
+        <v>14674</v>
       </c>
       <c r="I123" t="n">
-        <v>92299</v>
+        <v>83157</v>
       </c>
     </row>
     <row r="124">
@@ -5488,22 +5488,22 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>83889</v>
+        <v>85369</v>
       </c>
       <c r="H124" t="n">
-        <v>12583</v>
+        <v>12805</v>
       </c>
       <c r="I124" t="n">
-        <v>71306</v>
+        <v>72564</v>
       </c>
     </row>
     <row r="125">
@@ -5529,22 +5529,22 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>May 2020</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>103848</v>
+        <v>84686</v>
       </c>
       <c r="H125" t="n">
-        <v>15577</v>
+        <v>12702</v>
       </c>
       <c r="I125" t="n">
-        <v>88271</v>
+        <v>71984</v>
       </c>
     </row>
     <row r="126">
@@ -5570,22 +5570,22 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>85305</v>
+        <v>100515</v>
       </c>
       <c r="H126" t="n">
-        <v>12795</v>
+        <v>15077</v>
       </c>
       <c r="I126" t="n">
-        <v>72510</v>
+        <v>85438</v>
       </c>
     </row>
     <row r="127">
@@ -5611,22 +5611,22 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Aug 2020</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>98148</v>
+        <v>84401</v>
       </c>
       <c r="H127" t="n">
-        <v>14722</v>
+        <v>12660</v>
       </c>
       <c r="I127" t="n">
-        <v>83426</v>
+        <v>71741</v>
       </c>
     </row>
     <row r="128">
@@ -5652,22 +5652,22 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Oct 2020</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>84251</v>
+        <v>108240</v>
       </c>
       <c r="H128" t="n">
-        <v>12637</v>
+        <v>16236</v>
       </c>
       <c r="I128" t="n">
-        <v>71614</v>
+        <v>92004</v>
       </c>
     </row>
     <row r="129">
@@ -5693,22 +5693,22 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Nov 2020</t>
+          <t>Oct 2020</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>86204</v>
+        <v>86396</v>
       </c>
       <c r="H129" t="n">
-        <v>12930</v>
+        <v>12959</v>
       </c>
       <c r="I129" t="n">
-        <v>73274</v>
+        <v>73437</v>
       </c>
     </row>
     <row r="130">
@@ -5734,22 +5734,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>Nov 2020</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>159894</v>
+        <v>84150</v>
       </c>
       <c r="H130" t="n">
-        <v>23984</v>
+        <v>12622</v>
       </c>
       <c r="I130" t="n">
-        <v>135910</v>
+        <v>71528</v>
       </c>
     </row>
     <row r="131">
@@ -5775,22 +5775,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Jan 2021</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>85233</v>
+        <v>167682</v>
       </c>
       <c r="H131" t="n">
-        <v>12784</v>
+        <v>25152</v>
       </c>
       <c r="I131" t="n">
-        <v>72449</v>
+        <v>142530</v>
       </c>
     </row>
     <row r="132">
@@ -5816,22 +5816,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Feb 2021</t>
+          <t>Jan 2021</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>84090</v>
+        <v>86066</v>
       </c>
       <c r="H132" t="n">
-        <v>12613</v>
+        <v>12909</v>
       </c>
       <c r="I132" t="n">
-        <v>71477</v>
+        <v>73157</v>
       </c>
     </row>
     <row r="133">
@@ -5857,22 +5857,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>Feb 2021</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>98946</v>
+        <v>85860</v>
       </c>
       <c r="H133" t="n">
-        <v>14841</v>
+        <v>12879</v>
       </c>
       <c r="I133" t="n">
-        <v>84105</v>
+        <v>72981</v>
       </c>
     </row>
     <row r="134">
@@ -5898,22 +5898,22 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Apr 2021</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>84117</v>
+        <v>106415</v>
       </c>
       <c r="H134" t="n">
-        <v>12617</v>
+        <v>15962</v>
       </c>
       <c r="I134" t="n">
-        <v>71500</v>
+        <v>90453</v>
       </c>
     </row>
     <row r="135">
@@ -5939,22 +5939,22 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>May 2021</t>
+          <t>Apr 2021</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>84597</v>
+        <v>86415</v>
       </c>
       <c r="H135" t="n">
-        <v>12689</v>
+        <v>12962</v>
       </c>
       <c r="I135" t="n">
-        <v>71908</v>
+        <v>73453</v>
       </c>
     </row>
     <row r="136">
@@ -5980,22 +5980,22 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>May 2021</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>102246</v>
+        <v>85400</v>
       </c>
       <c r="H136" t="n">
-        <v>15336</v>
+        <v>12810</v>
       </c>
       <c r="I136" t="n">
-        <v>86910</v>
+        <v>72590</v>
       </c>
     </row>
     <row r="137">
@@ -6021,22 +6021,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Jul 2021</t>
+          <t>Jun 2021</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>85123</v>
+        <v>110736</v>
       </c>
       <c r="H137" t="n">
-        <v>12768</v>
+        <v>16610</v>
       </c>
       <c r="I137" t="n">
-        <v>72355</v>
+        <v>94126</v>
       </c>
     </row>
     <row r="138">
@@ -6062,22 +6062,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Aug 2021</t>
+          <t>Jul 2021</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>86213</v>
+        <v>86475</v>
       </c>
       <c r="H138" t="n">
-        <v>12931</v>
+        <v>12971</v>
       </c>
       <c r="I138" t="n">
-        <v>73282</v>
+        <v>73504</v>
       </c>
     </row>
     <row r="139">
@@ -6103,22 +6103,22 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>Aug 2021</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>105945</v>
+        <v>83589</v>
       </c>
       <c r="H139" t="n">
-        <v>15891</v>
+        <v>12538</v>
       </c>
       <c r="I139" t="n">
-        <v>90054</v>
+        <v>71051</v>
       </c>
     </row>
     <row r="140">
@@ -6144,22 +6144,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>86519</v>
+        <v>98801</v>
       </c>
       <c r="H140" t="n">
-        <v>12977</v>
+        <v>14820</v>
       </c>
       <c r="I140" t="n">
-        <v>73542</v>
+        <v>83981</v>
       </c>
     </row>
     <row r="141">
@@ -6185,22 +6185,22 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Jan 2022</t>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>85176</v>
+        <v>84031</v>
       </c>
       <c r="H141" t="n">
-        <v>12776</v>
+        <v>12604</v>
       </c>
       <c r="I141" t="n">
-        <v>72400</v>
+        <v>71427</v>
       </c>
     </row>
     <row r="142">
@@ -6226,22 +6226,22 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mar 2022</t>
+          <t>Nov 2021</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>108508</v>
+        <v>85219</v>
       </c>
       <c r="H142" t="n">
-        <v>16276</v>
+        <v>12782</v>
       </c>
       <c r="I142" t="n">
-        <v>92232</v>
+        <v>72437</v>
       </c>
     </row>
     <row r="143">
@@ -6267,22 +6267,22 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Apr 2022</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>85244</v>
+        <v>164695</v>
       </c>
       <c r="H143" t="n">
-        <v>12786</v>
+        <v>24704</v>
       </c>
       <c r="I143" t="n">
-        <v>72458</v>
+        <v>139991</v>
       </c>
     </row>
     <row r="144">
@@ -6308,22 +6308,22 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>May 2022</t>
+          <t>Feb 2022</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>83937</v>
+        <v>86253</v>
       </c>
       <c r="H144" t="n">
-        <v>12590</v>
+        <v>12937</v>
       </c>
       <c r="I144" t="n">
-        <v>71347</v>
+        <v>73316</v>
       </c>
     </row>
     <row r="145">
@@ -6349,22 +6349,22 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>May 2022</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>102086</v>
+        <v>84647</v>
       </c>
       <c r="H145" t="n">
-        <v>15312</v>
+        <v>12697</v>
       </c>
       <c r="I145" t="n">
-        <v>86774</v>
+        <v>71950</v>
       </c>
     </row>
     <row r="146">
@@ -6390,22 +6390,22 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Jul 2022</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>86268</v>
+        <v>104153</v>
       </c>
       <c r="H146" t="n">
-        <v>12940</v>
+        <v>15622</v>
       </c>
       <c r="I146" t="n">
-        <v>73328</v>
+        <v>88531</v>
       </c>
     </row>
     <row r="147">
@@ -6431,22 +6431,22 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>Jul 2022</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>85956</v>
+        <v>86498</v>
       </c>
       <c r="H147" t="n">
-        <v>12893</v>
+        <v>12974</v>
       </c>
       <c r="I147" t="n">
-        <v>73063</v>
+        <v>73524</v>
       </c>
     </row>
     <row r="148">
@@ -6472,22 +6472,22 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Nov 2022</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>85467</v>
+        <v>98666</v>
       </c>
       <c r="H148" t="n">
-        <v>12820</v>
+        <v>14799</v>
       </c>
       <c r="I148" t="n">
-        <v>72647</v>
+        <v>83867</v>
       </c>
     </row>
     <row r="149">
@@ -6513,22 +6513,22 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dec 2022</t>
+          <t>Oct 2022</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>169314</v>
+        <v>84335</v>
       </c>
       <c r="H149" t="n">
-        <v>25397</v>
+        <v>12650</v>
       </c>
       <c r="I149" t="n">
-        <v>143917</v>
+        <v>71685</v>
       </c>
     </row>
     <row r="150">
@@ -6554,22 +6554,22 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Jan 2023</t>
+          <t>Nov 2022</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>84421</v>
+        <v>84476</v>
       </c>
       <c r="H150" t="n">
-        <v>12663</v>
+        <v>12671</v>
       </c>
       <c r="I150" t="n">
-        <v>71758</v>
+        <v>71805</v>
       </c>
     </row>
     <row r="151">
@@ -6595,22 +6595,22 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>Dec 2022</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>83654</v>
+        <v>162523</v>
       </c>
       <c r="H151" t="n">
-        <v>12548</v>
+        <v>24378</v>
       </c>
       <c r="I151" t="n">
-        <v>71106</v>
+        <v>138145</v>
       </c>
     </row>
     <row r="152">
@@ -6636,22 +6636,22 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mar 2023</t>
+          <t>Jan 2023</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>104855</v>
+        <v>84989</v>
       </c>
       <c r="H152" t="n">
-        <v>15728</v>
+        <v>12748</v>
       </c>
       <c r="I152" t="n">
-        <v>89127</v>
+        <v>72241</v>
       </c>
     </row>
     <row r="153">
@@ -6677,22 +6677,22 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Apr 2023</t>
+          <t>Feb 2023</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>86392</v>
+        <v>85318</v>
       </c>
       <c r="H153" t="n">
-        <v>12958</v>
+        <v>12797</v>
       </c>
       <c r="I153" t="n">
-        <v>73434</v>
+        <v>72521</v>
       </c>
     </row>
     <row r="154">
@@ -6718,22 +6718,22 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>Mar 2023</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>85704</v>
+        <v>106948</v>
       </c>
       <c r="H154" t="n">
-        <v>12855</v>
+        <v>16042</v>
       </c>
       <c r="I154" t="n">
-        <v>72849</v>
+        <v>90906</v>
       </c>
     </row>
     <row r="155">
@@ -6759,22 +6759,22 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>Apr 2023</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>106596</v>
+        <v>86398</v>
       </c>
       <c r="H155" t="n">
-        <v>15989</v>
+        <v>12959</v>
       </c>
       <c r="I155" t="n">
-        <v>90607</v>
+        <v>73439</v>
       </c>
     </row>
     <row r="156">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>May 2023</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>86313</v>
+        <v>85091</v>
       </c>
       <c r="H156" t="n">
-        <v>12946</v>
+        <v>12763</v>
       </c>
       <c r="I156" t="n">
-        <v>73367</v>
+        <v>72328</v>
       </c>
     </row>
     <row r="157">
@@ -6841,22 +6841,22 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Aug 2023</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="G157" t="n">
-        <v>85231</v>
+        <v>109485</v>
       </c>
       <c r="H157" t="n">
-        <v>12784</v>
+        <v>16422</v>
       </c>
       <c r="I157" t="n">
-        <v>72447</v>
+        <v>93063</v>
       </c>
     </row>
     <row r="158">
@@ -6882,22 +6882,22 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>Jul 2023</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>97882</v>
+        <v>84166</v>
       </c>
       <c r="H158" t="n">
-        <v>14682</v>
+        <v>12624</v>
       </c>
       <c r="I158" t="n">
-        <v>83200</v>
+        <v>71542</v>
       </c>
     </row>
     <row r="159">
@@ -6932,13 +6932,13 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>86647</v>
+        <v>84432</v>
       </c>
       <c r="H159" t="n">
-        <v>12997</v>
+        <v>12664</v>
       </c>
       <c r="I159" t="n">
-        <v>73650</v>
+        <v>71768</v>
       </c>
     </row>
     <row r="160">
@@ -6973,13 +6973,13 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>84822</v>
+        <v>86457</v>
       </c>
       <c r="H160" t="n">
-        <v>12723</v>
+        <v>12968</v>
       </c>
       <c r="I160" t="n">
-        <v>72099</v>
+        <v>73489</v>
       </c>
     </row>
     <row r="161">
@@ -7014,13 +7014,13 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>142435</v>
+        <v>165934</v>
       </c>
       <c r="H161" t="n">
-        <v>21365</v>
+        <v>24890</v>
       </c>
       <c r="I161" t="n">
-        <v>121070</v>
+        <v>141044</v>
       </c>
     </row>
     <row r="162">
@@ -7046,22 +7046,22 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>Mar 2019</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>189864</v>
+        <v>195835</v>
       </c>
       <c r="H162" t="n">
-        <v>18986</v>
+        <v>19583</v>
       </c>
       <c r="I162" t="n">
-        <v>170878</v>
+        <v>176252</v>
       </c>
     </row>
     <row r="163">
@@ -7087,22 +7087,22 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>191730</v>
+        <v>216081</v>
       </c>
       <c r="H163" t="n">
-        <v>19173</v>
+        <v>21608</v>
       </c>
       <c r="I163" t="n">
-        <v>172557</v>
+        <v>194473</v>
       </c>
     </row>
     <row r="164">
@@ -7128,22 +7128,22 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>223043</v>
+        <v>202189</v>
       </c>
       <c r="H164" t="n">
-        <v>22304</v>
+        <v>20218</v>
       </c>
       <c r="I164" t="n">
-        <v>200739</v>
+        <v>181971</v>
       </c>
     </row>
     <row r="165">
@@ -7178,13 +7178,13 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>187893</v>
+        <v>211175</v>
       </c>
       <c r="H165" t="n">
-        <v>18789</v>
+        <v>21117</v>
       </c>
       <c r="I165" t="n">
-        <v>169104</v>
+        <v>190058</v>
       </c>
     </row>
     <row r="166">
@@ -7210,22 +7210,22 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>Jun 2021</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>210165</v>
+        <v>236251</v>
       </c>
       <c r="H166" t="n">
-        <v>21016</v>
+        <v>23625</v>
       </c>
       <c r="I166" t="n">
-        <v>189149</v>
+        <v>212626</v>
       </c>
     </row>
     <row r="167">
@@ -7251,22 +7251,22 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>225242</v>
+        <v>195572</v>
       </c>
       <c r="H167" t="n">
-        <v>22524</v>
+        <v>19557</v>
       </c>
       <c r="I167" t="n">
-        <v>202718</v>
+        <v>176015</v>
       </c>
     </row>
     <row r="168">
@@ -7292,22 +7292,22 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>Mar 2022</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>241562</v>
+        <v>209628</v>
       </c>
       <c r="H168" t="n">
-        <v>24156</v>
+        <v>20962</v>
       </c>
       <c r="I168" t="n">
-        <v>217406</v>
+        <v>188666</v>
       </c>
     </row>
     <row r="169">
@@ -7333,22 +7333,22 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mar 2022</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="G169" t="n">
-        <v>208190</v>
+        <v>198112</v>
       </c>
       <c r="H169" t="n">
-        <v>20819</v>
+        <v>19811</v>
       </c>
       <c r="I169" t="n">
-        <v>187371</v>
+        <v>178301</v>
       </c>
     </row>
     <row r="170">
@@ -7374,22 +7374,22 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>Mar 2023</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>230122</v>
+        <v>243596</v>
       </c>
       <c r="H170" t="n">
-        <v>23012</v>
+        <v>24359</v>
       </c>
       <c r="I170" t="n">
-        <v>207110</v>
+        <v>219237</v>
       </c>
     </row>
     <row r="171">
@@ -7415,22 +7415,22 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dec 2023</t>
+          <t>Sep 2023</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>210566</v>
+        <v>231881</v>
       </c>
       <c r="H171" t="n">
-        <v>21056</v>
+        <v>23188</v>
       </c>
       <c r="I171" t="n">
-        <v>189510</v>
+        <v>208693</v>
       </c>
     </row>
     <row r="172">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -7465,13 +7465,13 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>50899</v>
+        <v>50730</v>
       </c>
       <c r="H172" t="n">
-        <v>7634</v>
+        <v>7609</v>
       </c>
       <c r="I172" t="n">
-        <v>43265</v>
+        <v>43121</v>
       </c>
     </row>
     <row r="173">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>49577</v>
+        <v>50448</v>
       </c>
       <c r="H173" t="n">
-        <v>7436</v>
+        <v>7567</v>
       </c>
       <c r="I173" t="n">
-        <v>42141</v>
+        <v>42881</v>
       </c>
     </row>
     <row r="174">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -7547,13 +7547,13 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>61473</v>
+        <v>61566</v>
       </c>
       <c r="H174" t="n">
-        <v>9220</v>
+        <v>9234</v>
       </c>
       <c r="I174" t="n">
-        <v>52253</v>
+        <v>52332</v>
       </c>
     </row>
     <row r="175">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -7579,22 +7579,22 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Apr 2019</t>
+          <t>May 2019</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>50054</v>
+        <v>49904</v>
       </c>
       <c r="H175" t="n">
-        <v>7508</v>
+        <v>7485</v>
       </c>
       <c r="I175" t="n">
-        <v>42546</v>
+        <v>42419</v>
       </c>
     </row>
     <row r="176">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -7620,22 +7620,22 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>May 2019</t>
+          <t>Jul 2019</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>50494</v>
+        <v>50467</v>
       </c>
       <c r="H176" t="n">
-        <v>7574</v>
+        <v>7570</v>
       </c>
       <c r="I176" t="n">
-        <v>42920</v>
+        <v>42897</v>
       </c>
     </row>
     <row r="177">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -7661,22 +7661,22 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Jul 2019</t>
+          <t>Aug 2019</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>50212</v>
+        <v>50105</v>
       </c>
       <c r="H177" t="n">
-        <v>7531</v>
+        <v>7515</v>
       </c>
       <c r="I177" t="n">
-        <v>42681</v>
+        <v>42590</v>
       </c>
     </row>
     <row r="178">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -7702,22 +7702,22 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Aug 2019</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>49710</v>
+        <v>58783</v>
       </c>
       <c r="H178" t="n">
-        <v>7456</v>
+        <v>8817</v>
       </c>
       <c r="I178" t="n">
-        <v>42254</v>
+        <v>49966</v>
       </c>
     </row>
     <row r="179">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -7752,13 +7752,13 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>50322</v>
+        <v>50795</v>
       </c>
       <c r="H179" t="n">
-        <v>7548</v>
+        <v>7619</v>
       </c>
       <c r="I179" t="n">
-        <v>42774</v>
+        <v>43176</v>
       </c>
     </row>
     <row r="180">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7784,22 +7784,22 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>Nov 2019</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>96648</v>
+        <v>49454</v>
       </c>
       <c r="H180" t="n">
-        <v>14497</v>
+        <v>7418</v>
       </c>
       <c r="I180" t="n">
-        <v>82151</v>
+        <v>42036</v>
       </c>
     </row>
     <row r="181">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -7825,22 +7825,22 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Jan 2020</t>
+          <t>Dec 2019</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>49025</v>
+        <v>98806</v>
       </c>
       <c r="H181" t="n">
-        <v>7353</v>
+        <v>14820</v>
       </c>
       <c r="I181" t="n">
-        <v>41672</v>
+        <v>83986</v>
       </c>
     </row>
     <row r="182">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -7866,22 +7866,22 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Feb 2020</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>49334</v>
+        <v>50499</v>
       </c>
       <c r="H182" t="n">
-        <v>7400</v>
+        <v>7574</v>
       </c>
       <c r="I182" t="n">
-        <v>41934</v>
+        <v>42925</v>
       </c>
     </row>
     <row r="183">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7907,22 +7907,22 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Feb 2020</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>60534</v>
+        <v>50188</v>
       </c>
       <c r="H183" t="n">
-        <v>9080</v>
+        <v>7528</v>
       </c>
       <c r="I183" t="n">
-        <v>51454</v>
+        <v>42660</v>
       </c>
     </row>
     <row r="184">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7948,22 +7948,22 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>49948</v>
+        <v>58850</v>
       </c>
       <c r="H184" t="n">
-        <v>7492</v>
+        <v>8827</v>
       </c>
       <c r="I184" t="n">
-        <v>42456</v>
+        <v>50023</v>
       </c>
     </row>
     <row r="185">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7989,22 +7989,22 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>65612</v>
+        <v>49675</v>
       </c>
       <c r="H185" t="n">
-        <v>9841</v>
+        <v>7451</v>
       </c>
       <c r="I185" t="n">
-        <v>55771</v>
+        <v>42224</v>
       </c>
     </row>
     <row r="186">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8030,22 +8030,22 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>May 2020</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>49052</v>
+        <v>50124</v>
       </c>
       <c r="H186" t="n">
-        <v>7357</v>
+        <v>7518</v>
       </c>
       <c r="I186" t="n">
-        <v>41695</v>
+        <v>42606</v>
       </c>
     </row>
     <row r="187">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8071,22 +8071,22 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>50141</v>
+        <v>65921</v>
       </c>
       <c r="H187" t="n">
-        <v>7521</v>
+        <v>9888</v>
       </c>
       <c r="I187" t="n">
-        <v>42620</v>
+        <v>56033</v>
       </c>
     </row>
     <row r="188">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8112,22 +8112,22 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>62736</v>
+        <v>49268</v>
       </c>
       <c r="H188" t="n">
-        <v>9410</v>
+        <v>7390</v>
       </c>
       <c r="I188" t="n">
-        <v>53326</v>
+        <v>41878</v>
       </c>
     </row>
     <row r="189">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -8153,22 +8153,22 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Oct 2020</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G189" t="n">
-        <v>49997</v>
+        <v>58167</v>
       </c>
       <c r="H189" t="n">
-        <v>7499</v>
+        <v>8725</v>
       </c>
       <c r="I189" t="n">
-        <v>42498</v>
+        <v>49442</v>
       </c>
     </row>
     <row r="190">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -8194,22 +8194,22 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Nov 2020</t>
+          <t>Oct 2020</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>49273</v>
+        <v>50876</v>
       </c>
       <c r="H190" t="n">
-        <v>7390</v>
+        <v>7631</v>
       </c>
       <c r="I190" t="n">
-        <v>41883</v>
+        <v>43245</v>
       </c>
     </row>
     <row r="191">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -8235,22 +8235,22 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>Nov 2020</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>97474</v>
+        <v>50407</v>
       </c>
       <c r="H191" t="n">
-        <v>14621</v>
+        <v>7561</v>
       </c>
       <c r="I191" t="n">
-        <v>82853</v>
+        <v>42846</v>
       </c>
     </row>
     <row r="192">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -8276,22 +8276,22 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Jan 2021</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>50712</v>
+        <v>92270</v>
       </c>
       <c r="H192" t="n">
-        <v>7606</v>
+        <v>13840</v>
       </c>
       <c r="I192" t="n">
-        <v>43106</v>
+        <v>78430</v>
       </c>
     </row>
     <row r="193">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -8317,22 +8317,22 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Feb 2021</t>
+          <t>Jan 2021</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>50039</v>
+        <v>50405</v>
       </c>
       <c r="H193" t="n">
-        <v>7505</v>
+        <v>7560</v>
       </c>
       <c r="I193" t="n">
-        <v>42534</v>
+        <v>42845</v>
       </c>
     </row>
     <row r="194">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -8358,22 +8358,22 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>Feb 2021</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>59375</v>
+        <v>50348</v>
       </c>
       <c r="H194" t="n">
-        <v>8906</v>
+        <v>7552</v>
       </c>
       <c r="I194" t="n">
-        <v>50469</v>
+        <v>42796</v>
       </c>
     </row>
     <row r="195">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -8399,22 +8399,22 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Apr 2021</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>49240</v>
+        <v>61848</v>
       </c>
       <c r="H195" t="n">
-        <v>7386</v>
+        <v>9277</v>
       </c>
       <c r="I195" t="n">
-        <v>41854</v>
+        <v>52571</v>
       </c>
     </row>
     <row r="196">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -8440,22 +8440,22 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>May 2021</t>
+          <t>Apr 2021</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>50153</v>
+        <v>50976</v>
       </c>
       <c r="H196" t="n">
-        <v>7522</v>
+        <v>7646</v>
       </c>
       <c r="I196" t="n">
-        <v>42631</v>
+        <v>43330</v>
       </c>
     </row>
     <row r="197">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -8481,22 +8481,22 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>May 2021</t>
         </is>
       </c>
       <c r="G197" t="n">
-        <v>61406</v>
+        <v>49590</v>
       </c>
       <c r="H197" t="n">
-        <v>9210</v>
+        <v>7438</v>
       </c>
       <c r="I197" t="n">
-        <v>52196</v>
+        <v>42152</v>
       </c>
     </row>
     <row r="198">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -8522,22 +8522,22 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Jul 2021</t>
+          <t>Jun 2021</t>
         </is>
       </c>
       <c r="G198" t="n">
-        <v>49919</v>
+        <v>60491</v>
       </c>
       <c r="H198" t="n">
-        <v>7487</v>
+        <v>9073</v>
       </c>
       <c r="I198" t="n">
-        <v>42432</v>
+        <v>51418</v>
       </c>
     </row>
     <row r="199">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -8563,22 +8563,22 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>Jul 2021</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>57034</v>
+        <v>50431</v>
       </c>
       <c r="H199" t="n">
-        <v>8555</v>
+        <v>7564</v>
       </c>
       <c r="I199" t="n">
-        <v>48479</v>
+        <v>42867</v>
       </c>
     </row>
     <row r="200">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -8604,22 +8604,22 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="G200" t="n">
-        <v>49714</v>
+        <v>63619</v>
       </c>
       <c r="H200" t="n">
-        <v>7457</v>
+        <v>9542</v>
       </c>
       <c r="I200" t="n">
-        <v>42257</v>
+        <v>54077</v>
       </c>
     </row>
     <row r="201">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -8645,22 +8645,22 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>92456</v>
+        <v>49135</v>
       </c>
       <c r="H201" t="n">
-        <v>13868</v>
+        <v>7370</v>
       </c>
       <c r="I201" t="n">
-        <v>78588</v>
+        <v>41765</v>
       </c>
     </row>
     <row r="202">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -8686,22 +8686,22 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Jan 2022</t>
+          <t>Feb 2022</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>50049</v>
+        <v>49098</v>
       </c>
       <c r="H202" t="n">
-        <v>7507</v>
+        <v>7364</v>
       </c>
       <c r="I202" t="n">
-        <v>42542</v>
+        <v>41734</v>
       </c>
     </row>
     <row r="203">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -8727,22 +8727,22 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Feb 2022</t>
+          <t>Mar 2022</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>50206</v>
+        <v>57607</v>
       </c>
       <c r="H203" t="n">
-        <v>7530</v>
+        <v>8641</v>
       </c>
       <c r="I203" t="n">
-        <v>42676</v>
+        <v>48966</v>
       </c>
     </row>
     <row r="204">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -8777,13 +8777,13 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>49960</v>
+        <v>49274</v>
       </c>
       <c r="H204" t="n">
-        <v>7494</v>
+        <v>7391</v>
       </c>
       <c r="I204" t="n">
-        <v>42466</v>
+        <v>41883</v>
       </c>
     </row>
     <row r="205">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -8809,22 +8809,22 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>May 2022</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>50526</v>
+        <v>65250</v>
       </c>
       <c r="H205" t="n">
-        <v>7578</v>
+        <v>9787</v>
       </c>
       <c r="I205" t="n">
-        <v>42948</v>
+        <v>55463</v>
       </c>
     </row>
     <row r="206">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -8850,22 +8850,22 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>Jul 2022</t>
         </is>
       </c>
       <c r="G206" t="n">
-        <v>59820</v>
+        <v>50486</v>
       </c>
       <c r="H206" t="n">
-        <v>8973</v>
+        <v>7572</v>
       </c>
       <c r="I206" t="n">
-        <v>50847</v>
+        <v>42914</v>
       </c>
     </row>
     <row r="207">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -8900,13 +8900,13 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>50684</v>
+        <v>50637</v>
       </c>
       <c r="H207" t="n">
-        <v>7602</v>
+        <v>7595</v>
       </c>
       <c r="I207" t="n">
-        <v>43082</v>
+        <v>43042</v>
       </c>
     </row>
     <row r="208">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -8941,13 +8941,13 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>60112</v>
+        <v>58991</v>
       </c>
       <c r="H208" t="n">
-        <v>9016</v>
+        <v>8848</v>
       </c>
       <c r="I208" t="n">
-        <v>51096</v>
+        <v>50143</v>
       </c>
     </row>
     <row r="209">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -8982,13 +8982,13 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>50399</v>
+        <v>49234</v>
       </c>
       <c r="H209" t="n">
-        <v>7559</v>
+        <v>7385</v>
       </c>
       <c r="I209" t="n">
-        <v>42840</v>
+        <v>41849</v>
       </c>
     </row>
     <row r="210">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9023,13 +9023,13 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>49400</v>
+        <v>49867</v>
       </c>
       <c r="H210" t="n">
-        <v>7410</v>
+        <v>7480</v>
       </c>
       <c r="I210" t="n">
-        <v>41990</v>
+        <v>42387</v>
       </c>
     </row>
     <row r="211">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9064,13 +9064,13 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>79570</v>
+        <v>84678</v>
       </c>
       <c r="H211" t="n">
-        <v>11935</v>
+        <v>12701</v>
       </c>
       <c r="I211" t="n">
-        <v>67635</v>
+        <v>71977</v>
       </c>
     </row>
     <row r="212">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9105,13 +9105,13 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>50179</v>
+        <v>49244</v>
       </c>
       <c r="H212" t="n">
-        <v>7526</v>
+        <v>7386</v>
       </c>
       <c r="I212" t="n">
-        <v>42653</v>
+        <v>41858</v>
       </c>
     </row>
     <row r="213">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9146,13 +9146,13 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>50070</v>
+        <v>50572</v>
       </c>
       <c r="H213" t="n">
-        <v>7510</v>
+        <v>7585</v>
       </c>
       <c r="I213" t="n">
-        <v>42560</v>
+        <v>42987</v>
       </c>
     </row>
     <row r="214">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9187,13 +9187,13 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>61702</v>
+        <v>63386</v>
       </c>
       <c r="H214" t="n">
-        <v>9255</v>
+        <v>9507</v>
       </c>
       <c r="I214" t="n">
-        <v>52447</v>
+        <v>53879</v>
       </c>
     </row>
     <row r="215">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9228,13 +9228,13 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>49659</v>
+        <v>50515</v>
       </c>
       <c r="H215" t="n">
-        <v>7448</v>
+        <v>7577</v>
       </c>
       <c r="I215" t="n">
-        <v>42211</v>
+        <v>42938</v>
       </c>
     </row>
     <row r="216">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9269,13 +9269,13 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>49358</v>
+        <v>50884</v>
       </c>
       <c r="H216" t="n">
-        <v>7403</v>
+        <v>7632</v>
       </c>
       <c r="I216" t="n">
-        <v>41955</v>
+        <v>43252</v>
       </c>
     </row>
     <row r="217">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -9301,22 +9301,22 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>Jul 2023</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>63400</v>
+        <v>50634</v>
       </c>
       <c r="H217" t="n">
-        <v>9510</v>
+        <v>7595</v>
       </c>
       <c r="I217" t="n">
-        <v>53890</v>
+        <v>43039</v>
       </c>
     </row>
     <row r="218">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -9342,22 +9342,22 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>Sep 2023</t>
         </is>
       </c>
       <c r="G218" t="n">
-        <v>49567</v>
+        <v>61578</v>
       </c>
       <c r="H218" t="n">
-        <v>7435</v>
+        <v>9236</v>
       </c>
       <c r="I218" t="n">
-        <v>42132</v>
+        <v>52342</v>
       </c>
     </row>
     <row r="219">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -9383,22 +9383,22 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>Oct 2023</t>
         </is>
       </c>
       <c r="G219" t="n">
-        <v>63751</v>
+        <v>50742</v>
       </c>
       <c r="H219" t="n">
-        <v>9562</v>
+        <v>7611</v>
       </c>
       <c r="I219" t="n">
-        <v>54189</v>
+        <v>43131</v>
       </c>
     </row>
     <row r="220">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -9424,22 +9424,22 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Oct 2023</t>
+          <t>Nov 2023</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>49071</v>
+        <v>50535</v>
       </c>
       <c r="H220" t="n">
-        <v>7360</v>
+        <v>7580</v>
       </c>
       <c r="I220" t="n">
-        <v>41711</v>
+        <v>42955</v>
       </c>
     </row>
     <row r="221">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -9474,13 +9474,13 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>96164</v>
+        <v>84902</v>
       </c>
       <c r="H221" t="n">
-        <v>14424</v>
+        <v>12735</v>
       </c>
       <c r="I221" t="n">
-        <v>81740</v>
+        <v>72167</v>
       </c>
     </row>
     <row r="222">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -9875,22 +9875,22 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Jan 2020</t>
+          <t>Dec 2019</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>27500</v>
+        <v>25000</v>
       </c>
       <c r="H231" t="n">
-        <v>2750</v>
+        <v>2500</v>
       </c>
       <c r="I231" t="n">
-        <v>24750</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="232">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Feb 2020</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -9957,12 +9957,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Feb 2020</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -9998,12 +9998,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -10121,12 +10121,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Oct 2020</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Oct 2020</t>
+          <t>Nov 2020</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -10244,12 +10244,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Nov 2020</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -10285,22 +10285,22 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>Jan 2021</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>27500</v>
+        <v>30250</v>
       </c>
       <c r="H241" t="n">
-        <v>2750</v>
+        <v>3025</v>
       </c>
       <c r="I241" t="n">
-        <v>24750</v>
+        <v>27225</v>
       </c>
     </row>
     <row r="242">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -10326,12 +10326,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Jan 2021</t>
+          <t>Feb 2021</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -10367,12 +10367,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Feb 2021</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Apr 2021</t>
+          <t>May 2021</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>May 2021</t>
+          <t>Jun 2021</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>Jul 2021</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Jul 2021</t>
+          <t>Aug 2021</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -10572,12 +10572,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Aug 2021</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -10654,12 +10654,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>Nov 2021</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -10736,22 +10736,22 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>Jan 2022</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>30250</v>
+        <v>33275</v>
       </c>
       <c r="H252" t="n">
-        <v>3025</v>
+        <v>3327</v>
       </c>
       <c r="I252" t="n">
-        <v>27225</v>
+        <v>29948</v>
       </c>
     </row>
     <row r="253">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Jan 2022</t>
+          <t>Mar 2022</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Mar 2022</t>
+          <t>May 2022</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>May 2022</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>Jul 2022</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Jul 2022</t>
+          <t>Aug 2022</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Nov 2022</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -11064,12 +11064,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>Dec 2022</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -11105,22 +11105,22 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Nov 2022</t>
+          <t>Feb 2023</t>
         </is>
       </c>
       <c r="G261" t="n">
-        <v>33275</v>
+        <v>36602</v>
       </c>
       <c r="H261" t="n">
-        <v>3327</v>
+        <v>3660</v>
       </c>
       <c r="I261" t="n">
-        <v>29948</v>
+        <v>32942</v>
       </c>
     </row>
     <row r="262">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -11146,22 +11146,22 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Dec 2022</t>
+          <t>Mar 2023</t>
         </is>
       </c>
       <c r="G262" t="n">
-        <v>33275</v>
+        <v>36602</v>
       </c>
       <c r="H262" t="n">
-        <v>3327</v>
+        <v>3660</v>
       </c>
       <c r="I262" t="n">
-        <v>29948</v>
+        <v>32942</v>
       </c>
     </row>
     <row r="263">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>Apr 2023</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Mar 2023</t>
+          <t>May 2023</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Apr 2023</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>Jul 2023</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>Aug 2023</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -11392,12 +11392,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Aug 2023</t>
+          <t>Sep 2023</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>Oct 2023</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Vikram Biswas</t>
+          <t>Vikram Seth</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">

--- a/Task-1/mock_data/client_summary.xlsx
+++ b/Task-1/mock_data/client_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I271"/>
+  <dimension ref="A1:I287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Feb 2019</t>
+          <t>Jan 2019</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>65337</v>
+        <v>246562</v>
       </c>
       <c r="H2" t="n">
-        <v>9800</v>
+        <v>36984</v>
       </c>
       <c r="I2" t="n">
-        <v>55537</v>
+        <v>209578</v>
       </c>
     </row>
     <row r="3">
@@ -527,22 +527,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mar 2019</t>
+          <t>Feb 2019</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>80863</v>
+        <v>246643</v>
       </c>
       <c r="H3" t="n">
-        <v>12129</v>
+        <v>36996</v>
       </c>
       <c r="I3" t="n">
-        <v>68734</v>
+        <v>209647</v>
       </c>
     </row>
     <row r="4">
@@ -568,22 +568,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Apr 2019</t>
+          <t>Mar 2019</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>64173</v>
+        <v>285564</v>
       </c>
       <c r="H4" t="n">
-        <v>9625</v>
+        <v>42834</v>
       </c>
       <c r="I4" t="n">
-        <v>54548</v>
+        <v>242730</v>
       </c>
     </row>
     <row r="5">
@@ -609,22 +609,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>May 2019</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>65613</v>
+        <v>322087</v>
       </c>
       <c r="H5" t="n">
-        <v>9841</v>
+        <v>48313</v>
       </c>
       <c r="I5" t="n">
-        <v>55772</v>
+        <v>273774</v>
       </c>
     </row>
     <row r="6">
@@ -650,22 +650,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jun 2019</t>
+          <t>Jul 2019</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>77611</v>
+        <v>251967</v>
       </c>
       <c r="H6" t="n">
-        <v>11641</v>
+        <v>37795</v>
       </c>
       <c r="I6" t="n">
-        <v>65970</v>
+        <v>214172</v>
       </c>
     </row>
     <row r="7">
@@ -691,22 +691,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jul 2019</t>
+          <t>Oct 2019</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>64038</v>
+        <v>251328</v>
       </c>
       <c r="H7" t="n">
-        <v>9605</v>
+        <v>37699</v>
       </c>
       <c r="I7" t="n">
-        <v>54433</v>
+        <v>213629</v>
       </c>
     </row>
     <row r="8">
@@ -732,22 +732,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aug 2019</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>65281</v>
+        <v>249303</v>
       </c>
       <c r="H8" t="n">
-        <v>9792</v>
+        <v>37395</v>
       </c>
       <c r="I8" t="n">
-        <v>55489</v>
+        <v>211908</v>
       </c>
     </row>
     <row r="9">
@@ -773,22 +773,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nov 2019</t>
+          <t>Feb 2020</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>64103</v>
+        <v>252651</v>
       </c>
       <c r="H9" t="n">
-        <v>9615</v>
+        <v>37897</v>
       </c>
       <c r="I9" t="n">
-        <v>54488</v>
+        <v>214754</v>
       </c>
     </row>
     <row r="10">
@@ -814,22 +814,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jan 2020</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>65213</v>
+        <v>318102</v>
       </c>
       <c r="H10" t="n">
-        <v>9781</v>
+        <v>47715</v>
       </c>
       <c r="I10" t="n">
-        <v>55432</v>
+        <v>270387</v>
       </c>
     </row>
     <row r="11">
@@ -855,22 +855,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>82245</v>
+        <v>252822</v>
       </c>
       <c r="H11" t="n">
-        <v>12336</v>
+        <v>37923</v>
       </c>
       <c r="I11" t="n">
-        <v>69909</v>
+        <v>214899</v>
       </c>
     </row>
     <row r="12">
@@ -896,22 +896,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Apr 2020</t>
+          <t>May 2020</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>64397</v>
+        <v>253908</v>
       </c>
       <c r="H12" t="n">
-        <v>9659</v>
+        <v>38086</v>
       </c>
       <c r="I12" t="n">
-        <v>54738</v>
+        <v>215822</v>
       </c>
     </row>
     <row r="13">
@@ -937,22 +937,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>65461</v>
+        <v>298006</v>
       </c>
       <c r="H13" t="n">
-        <v>9819</v>
+        <v>44700</v>
       </c>
       <c r="I13" t="n">
-        <v>55642</v>
+        <v>253306</v>
       </c>
     </row>
     <row r="14">
@@ -978,22 +978,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>83688</v>
+        <v>249165</v>
       </c>
       <c r="H14" t="n">
-        <v>12553</v>
+        <v>37374</v>
       </c>
       <c r="I14" t="n">
-        <v>71135</v>
+        <v>211791</v>
       </c>
     </row>
     <row r="15">
@@ -1019,22 +1019,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>Aug 2020</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>65983</v>
+        <v>250099</v>
       </c>
       <c r="H15" t="n">
-        <v>9897</v>
+        <v>37514</v>
       </c>
       <c r="I15" t="n">
-        <v>56086</v>
+        <v>212585</v>
       </c>
     </row>
     <row r="16">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>65940</v>
+        <v>295913</v>
       </c>
       <c r="H16" t="n">
-        <v>9891</v>
+        <v>44386</v>
       </c>
       <c r="I16" t="n">
-        <v>56049</v>
+        <v>251527</v>
       </c>
     </row>
     <row r="17">
@@ -1101,22 +1101,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Oct 2020</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>78813</v>
+        <v>251865</v>
       </c>
       <c r="H17" t="n">
-        <v>11821</v>
+        <v>37779</v>
       </c>
       <c r="I17" t="n">
-        <v>66992</v>
+        <v>214086</v>
       </c>
     </row>
     <row r="18">
@@ -1142,22 +1142,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oct 2020</t>
+          <t>Nov 2020</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>64879</v>
+        <v>253152</v>
       </c>
       <c r="H18" t="n">
-        <v>9731</v>
+        <v>37972</v>
       </c>
       <c r="I18" t="n">
-        <v>55148</v>
+        <v>215180</v>
       </c>
     </row>
     <row r="19">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>127641</v>
+        <v>431860</v>
       </c>
       <c r="H19" t="n">
-        <v>19146</v>
+        <v>64779</v>
       </c>
       <c r="I19" t="n">
-        <v>108495</v>
+        <v>367081</v>
       </c>
     </row>
     <row r="20">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>65258</v>
+        <v>254671</v>
       </c>
       <c r="H20" t="n">
-        <v>9788</v>
+        <v>38200</v>
       </c>
       <c r="I20" t="n">
-        <v>55470</v>
+        <v>216471</v>
       </c>
     </row>
     <row r="21">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>64716</v>
+        <v>251597</v>
       </c>
       <c r="H21" t="n">
-        <v>9707</v>
+        <v>37739</v>
       </c>
       <c r="I21" t="n">
-        <v>55009</v>
+        <v>213858</v>
       </c>
     </row>
     <row r="22">
@@ -1315,13 +1315,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>84053</v>
+        <v>297364</v>
       </c>
       <c r="H22" t="n">
-        <v>12607</v>
+        <v>44604</v>
       </c>
       <c r="I22" t="n">
-        <v>71446</v>
+        <v>252760</v>
       </c>
     </row>
     <row r="23">
@@ -1356,13 +1356,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>63822</v>
+        <v>246063</v>
       </c>
       <c r="H23" t="n">
-        <v>9573</v>
+        <v>36909</v>
       </c>
       <c r="I23" t="n">
-        <v>54249</v>
+        <v>209154</v>
       </c>
     </row>
     <row r="24">
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>65962</v>
+        <v>253257</v>
       </c>
       <c r="H24" t="n">
-        <v>9894</v>
+        <v>37988</v>
       </c>
       <c r="I24" t="n">
-        <v>56068</v>
+        <v>215269</v>
       </c>
     </row>
     <row r="25">
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>77332</v>
+        <v>302612</v>
       </c>
       <c r="H25" t="n">
-        <v>11599</v>
+        <v>45391</v>
       </c>
       <c r="I25" t="n">
-        <v>65733</v>
+        <v>257221</v>
       </c>
     </row>
     <row r="26">
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>65188</v>
+        <v>281466</v>
       </c>
       <c r="H26" t="n">
-        <v>9778</v>
+        <v>42219</v>
       </c>
       <c r="I26" t="n">
-        <v>55410</v>
+        <v>239247</v>
       </c>
     </row>
     <row r="27">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>65374</v>
+        <v>274657</v>
       </c>
       <c r="H27" t="n">
-        <v>9806</v>
+        <v>41198</v>
       </c>
       <c r="I27" t="n">
-        <v>55568</v>
+        <v>233459</v>
       </c>
     </row>
     <row r="28">
@@ -1561,13 +1561,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>77149</v>
+        <v>351031</v>
       </c>
       <c r="H28" t="n">
-        <v>11572</v>
+        <v>52654</v>
       </c>
       <c r="I28" t="n">
-        <v>65577</v>
+        <v>298377</v>
       </c>
     </row>
     <row r="29">
@@ -1593,22 +1593,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>64815</v>
+        <v>281886</v>
       </c>
       <c r="H29" t="n">
-        <v>9722</v>
+        <v>42282</v>
       </c>
       <c r="I29" t="n">
-        <v>55093</v>
+        <v>239604</v>
       </c>
     </row>
     <row r="30">
@@ -1634,22 +1634,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>Nov 2021</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>120171</v>
+        <v>284614</v>
       </c>
       <c r="H30" t="n">
-        <v>18025</v>
+        <v>42692</v>
       </c>
       <c r="I30" t="n">
-        <v>102146</v>
+        <v>241922</v>
       </c>
     </row>
     <row r="31">
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jan 2022</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>65290</v>
+        <v>451112</v>
       </c>
       <c r="H31" t="n">
-        <v>9793</v>
+        <v>67666</v>
       </c>
       <c r="I31" t="n">
-        <v>55497</v>
+        <v>383446</v>
       </c>
     </row>
     <row r="32">
@@ -1716,22 +1716,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Feb 2022</t>
+          <t>Jan 2022</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>64850</v>
+        <v>277921</v>
       </c>
       <c r="H32" t="n">
-        <v>9727</v>
+        <v>41688</v>
       </c>
       <c r="I32" t="n">
-        <v>55123</v>
+        <v>236233</v>
       </c>
     </row>
     <row r="33">
@@ -1766,13 +1766,13 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>84610</v>
+        <v>340775</v>
       </c>
       <c r="H33" t="n">
-        <v>12691</v>
+        <v>51116</v>
       </c>
       <c r="I33" t="n">
-        <v>71919</v>
+        <v>289659</v>
       </c>
     </row>
     <row r="34">
@@ -1798,22 +1798,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Apr 2022</t>
+          <t>May 2022</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>64017</v>
+        <v>283123</v>
       </c>
       <c r="H34" t="n">
-        <v>9602</v>
+        <v>42468</v>
       </c>
       <c r="I34" t="n">
-        <v>54415</v>
+        <v>240655</v>
       </c>
     </row>
     <row r="35">
@@ -1839,22 +1839,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>May 2022</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>66083</v>
+        <v>325260</v>
       </c>
       <c r="H35" t="n">
-        <v>9912</v>
+        <v>48789</v>
       </c>
       <c r="I35" t="n">
-        <v>56171</v>
+        <v>276471</v>
       </c>
     </row>
     <row r="36">
@@ -1880,22 +1880,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>Jul 2022</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>84438</v>
+        <v>276791</v>
       </c>
       <c r="H36" t="n">
-        <v>12665</v>
+        <v>41518</v>
       </c>
       <c r="I36" t="n">
-        <v>71773</v>
+        <v>235273</v>
       </c>
     </row>
     <row r="37">
@@ -1930,13 +1930,13 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>66232</v>
+        <v>279907</v>
       </c>
       <c r="H37" t="n">
-        <v>9934</v>
+        <v>41986</v>
       </c>
       <c r="I37" t="n">
-        <v>56298</v>
+        <v>237921</v>
       </c>
     </row>
     <row r="38">
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>81627</v>
+        <v>333644</v>
       </c>
       <c r="H38" t="n">
-        <v>12244</v>
+        <v>50046</v>
       </c>
       <c r="I38" t="n">
-        <v>69383</v>
+        <v>283598</v>
       </c>
     </row>
     <row r="39">
@@ -2012,13 +2012,13 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>65703</v>
+        <v>275470</v>
       </c>
       <c r="H39" t="n">
-        <v>9855</v>
+        <v>41320</v>
       </c>
       <c r="I39" t="n">
-        <v>55848</v>
+        <v>234150</v>
       </c>
     </row>
     <row r="40">
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>64388</v>
+        <v>279666</v>
       </c>
       <c r="H40" t="n">
-        <v>9658</v>
+        <v>41949</v>
       </c>
       <c r="I40" t="n">
-        <v>54730</v>
+        <v>237717</v>
       </c>
     </row>
     <row r="41">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>112681</v>
+        <v>555584</v>
       </c>
       <c r="H41" t="n">
-        <v>16902</v>
+        <v>83337</v>
       </c>
       <c r="I41" t="n">
-        <v>95779</v>
+        <v>472247</v>
       </c>
     </row>
     <row r="42">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>65102</v>
+        <v>275963</v>
       </c>
       <c r="H42" t="n">
-        <v>9765</v>
+        <v>41394</v>
       </c>
       <c r="I42" t="n">
-        <v>55337</v>
+        <v>234569</v>
       </c>
     </row>
     <row r="43">
@@ -2167,22 +2167,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mar 2023</t>
+          <t>Apr 2023</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>77282</v>
+        <v>280240</v>
       </c>
       <c r="H43" t="n">
-        <v>11592</v>
+        <v>42036</v>
       </c>
       <c r="I43" t="n">
-        <v>65690</v>
+        <v>238204</v>
       </c>
     </row>
     <row r="44">
@@ -2208,22 +2208,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Apr 2023</t>
+          <t>May 2023</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>64381</v>
+        <v>277692</v>
       </c>
       <c r="H44" t="n">
-        <v>9657</v>
+        <v>41653</v>
       </c>
       <c r="I44" t="n">
-        <v>54724</v>
+        <v>236039</v>
       </c>
     </row>
     <row r="45">
@@ -2249,22 +2249,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>65307</v>
+        <v>352967</v>
       </c>
       <c r="H45" t="n">
-        <v>9796</v>
+        <v>52945</v>
       </c>
       <c r="I45" t="n">
-        <v>55511</v>
+        <v>300022</v>
       </c>
     </row>
     <row r="46">
@@ -2290,22 +2290,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>Jul 2023</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>81259</v>
+        <v>283047</v>
       </c>
       <c r="H46" t="n">
-        <v>12188</v>
+        <v>42457</v>
       </c>
       <c r="I46" t="n">
-        <v>69071</v>
+        <v>240590</v>
       </c>
     </row>
     <row r="47">
@@ -2331,22 +2331,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>Aug 2023</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>64907</v>
+        <v>281900</v>
       </c>
       <c r="H47" t="n">
-        <v>9736</v>
+        <v>42285</v>
       </c>
       <c r="I47" t="n">
-        <v>55171</v>
+        <v>239615</v>
       </c>
     </row>
     <row r="48">
@@ -2372,22 +2372,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aug 2023</t>
+          <t>Sep 2023</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>65691</v>
+        <v>347589</v>
       </c>
       <c r="H48" t="n">
-        <v>9853</v>
+        <v>52138</v>
       </c>
       <c r="I48" t="n">
-        <v>55838</v>
+        <v>295451</v>
       </c>
     </row>
     <row r="49">
@@ -2413,22 +2413,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>Oct 2023</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>77408</v>
+        <v>278058</v>
       </c>
       <c r="H49" t="n">
-        <v>11611</v>
+        <v>41708</v>
       </c>
       <c r="I49" t="n">
-        <v>65797</v>
+        <v>236350</v>
       </c>
     </row>
     <row r="50">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oct 2023</t>
+          <t>Nov 2023</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>64462</v>
+        <v>283234</v>
       </c>
       <c r="H50" t="n">
-        <v>9669</v>
+        <v>42485</v>
       </c>
       <c r="I50" t="n">
-        <v>54793</v>
+        <v>240749</v>
       </c>
     </row>
     <row r="51">
@@ -2504,13 +2504,13 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>121749</v>
+        <v>534026</v>
       </c>
       <c r="H51" t="n">
-        <v>18262</v>
+        <v>80103</v>
       </c>
       <c r="I51" t="n">
-        <v>103487</v>
+        <v>453923</v>
       </c>
     </row>
     <row r="52">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>40000</v>
+        <v>1485120</v>
       </c>
       <c r="H52" t="n">
-        <v>4000</v>
+        <v>148512</v>
       </c>
       <c r="I52" t="n">
-        <v>36000</v>
+        <v>1336608</v>
       </c>
     </row>
     <row r="53">
@@ -2577,22 +2577,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mar 2019</t>
+          <t>Feb 2019</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>40000</v>
+        <v>1485120</v>
       </c>
       <c r="H53" t="n">
-        <v>4000</v>
+        <v>148512</v>
       </c>
       <c r="I53" t="n">
-        <v>36000</v>
+        <v>1336608</v>
       </c>
     </row>
     <row r="54">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Apr 2019</t>
+          <t>Mar 2019</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>40000</v>
+        <v>1485120</v>
       </c>
       <c r="H54" t="n">
-        <v>4000</v>
+        <v>148512</v>
       </c>
       <c r="I54" t="n">
-        <v>36000</v>
+        <v>1336608</v>
       </c>
     </row>
     <row r="55">
@@ -2659,22 +2659,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>May 2019</t>
+          <t>Apr 2019</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>40000</v>
+        <v>1485120</v>
       </c>
       <c r="H55" t="n">
-        <v>4000</v>
+        <v>148512</v>
       </c>
       <c r="I55" t="n">
-        <v>36000</v>
+        <v>1336608</v>
       </c>
     </row>
     <row r="56">
@@ -2700,22 +2700,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Jun 2019</t>
+          <t>May 2019</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>40000</v>
+        <v>1485120</v>
       </c>
       <c r="H56" t="n">
-        <v>4000</v>
+        <v>148512</v>
       </c>
       <c r="I56" t="n">
-        <v>36000</v>
+        <v>1336608</v>
       </c>
     </row>
     <row r="57">
@@ -2741,22 +2741,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jul 2019</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>40000</v>
+        <v>1485120</v>
       </c>
       <c r="H57" t="n">
-        <v>4000</v>
+        <v>148512</v>
       </c>
       <c r="I57" t="n">
-        <v>36000</v>
+        <v>1336608</v>
       </c>
     </row>
     <row r="58">
@@ -2782,22 +2782,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aug 2019</t>
+          <t>Jul 2019</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>40000</v>
+        <v>1485120</v>
       </c>
       <c r="H58" t="n">
-        <v>4000</v>
+        <v>148512</v>
       </c>
       <c r="I58" t="n">
-        <v>36000</v>
+        <v>1336608</v>
       </c>
     </row>
     <row r="59">
@@ -2823,22 +2823,22 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sep 2019</t>
+          <t>Aug 2019</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>40000</v>
+        <v>1485120</v>
       </c>
       <c r="H59" t="n">
-        <v>4000</v>
+        <v>148512</v>
       </c>
       <c r="I59" t="n">
-        <v>36000</v>
+        <v>1336608</v>
       </c>
     </row>
     <row r="60">
@@ -2864,22 +2864,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Oct 2019</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>40000</v>
+        <v>1485120</v>
       </c>
       <c r="H60" t="n">
-        <v>4000</v>
+        <v>148512</v>
       </c>
       <c r="I60" t="n">
-        <v>36000</v>
+        <v>1336608</v>
       </c>
     </row>
     <row r="61">
@@ -2905,22 +2905,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nov 2019</t>
+          <t>Oct 2019</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>40000</v>
+        <v>1485120</v>
       </c>
       <c r="H61" t="n">
-        <v>4000</v>
+        <v>148512</v>
       </c>
       <c r="I61" t="n">
-        <v>36000</v>
+        <v>1336608</v>
       </c>
     </row>
     <row r="62">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>Nov 2019</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>40000</v>
+        <v>1485120</v>
       </c>
       <c r="H62" t="n">
-        <v>4000</v>
+        <v>148512</v>
       </c>
       <c r="I62" t="n">
-        <v>36000</v>
+        <v>1336608</v>
       </c>
     </row>
     <row r="63">
@@ -2987,22 +2987,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Feb 2020</t>
+          <t>Dec 2019</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>44000</v>
+        <v>1485120</v>
       </c>
       <c r="H63" t="n">
-        <v>4400</v>
+        <v>148512</v>
       </c>
       <c r="I63" t="n">
-        <v>39600</v>
+        <v>1336608</v>
       </c>
     </row>
     <row r="64">
@@ -3028,22 +3028,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>44000</v>
+        <v>1633632</v>
       </c>
       <c r="H64" t="n">
-        <v>4400</v>
+        <v>163363</v>
       </c>
       <c r="I64" t="n">
-        <v>39600</v>
+        <v>1470269</v>
       </c>
     </row>
     <row r="65">
@@ -3069,22 +3069,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Apr 2020</t>
+          <t>Feb 2020</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>44000</v>
+        <v>1633632</v>
       </c>
       <c r="H65" t="n">
-        <v>4400</v>
+        <v>163363</v>
       </c>
       <c r="I65" t="n">
-        <v>39600</v>
+        <v>1470269</v>
       </c>
     </row>
     <row r="66">
@@ -3110,22 +3110,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>44000</v>
+        <v>1633632</v>
       </c>
       <c r="H66" t="n">
-        <v>4400</v>
+        <v>163363</v>
       </c>
       <c r="I66" t="n">
-        <v>39600</v>
+        <v>1470269</v>
       </c>
     </row>
     <row r="67">
@@ -3151,22 +3151,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>44000</v>
+        <v>1633632</v>
       </c>
       <c r="H67" t="n">
-        <v>4400</v>
+        <v>163363</v>
       </c>
       <c r="I67" t="n">
-        <v>39600</v>
+        <v>1470269</v>
       </c>
     </row>
     <row r="68">
@@ -3192,22 +3192,22 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>May 2020</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>44000</v>
+        <v>1633632</v>
       </c>
       <c r="H68" t="n">
-        <v>4400</v>
+        <v>163363</v>
       </c>
       <c r="I68" t="n">
-        <v>39600</v>
+        <v>1470269</v>
       </c>
     </row>
     <row r="69">
@@ -3233,22 +3233,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>44000</v>
+        <v>1633632</v>
       </c>
       <c r="H69" t="n">
-        <v>4400</v>
+        <v>163363</v>
       </c>
       <c r="I69" t="n">
-        <v>39600</v>
+        <v>1470269</v>
       </c>
     </row>
     <row r="70">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>44000</v>
+        <v>1633632</v>
       </c>
       <c r="H70" t="n">
-        <v>4400</v>
+        <v>163363</v>
       </c>
       <c r="I70" t="n">
-        <v>39600</v>
+        <v>1470269</v>
       </c>
     </row>
     <row r="71">
@@ -3315,22 +3315,22 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oct 2020</t>
+          <t>Aug 2020</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>44000</v>
+        <v>1633632</v>
       </c>
       <c r="H71" t="n">
-        <v>4400</v>
+        <v>163363</v>
       </c>
       <c r="I71" t="n">
-        <v>39600</v>
+        <v>1470269</v>
       </c>
     </row>
     <row r="72">
@@ -3356,22 +3356,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>44000</v>
+        <v>1633632</v>
       </c>
       <c r="H72" t="n">
-        <v>4400</v>
+        <v>163363</v>
       </c>
       <c r="I72" t="n">
-        <v>39600</v>
+        <v>1470269</v>
       </c>
     </row>
     <row r="73">
@@ -3397,22 +3397,22 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Jan 2021</t>
+          <t>Nov 2020</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>48400</v>
+        <v>1633632</v>
       </c>
       <c r="H73" t="n">
-        <v>4840</v>
+        <v>163363</v>
       </c>
       <c r="I73" t="n">
-        <v>43560</v>
+        <v>1470269</v>
       </c>
     </row>
     <row r="74">
@@ -3438,22 +3438,22 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>48400</v>
+        <v>1633632</v>
       </c>
       <c r="H74" t="n">
-        <v>4840</v>
+        <v>163363</v>
       </c>
       <c r="I74" t="n">
-        <v>43560</v>
+        <v>1470269</v>
       </c>
     </row>
     <row r="75">
@@ -3479,22 +3479,22 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>May 2021</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>48400</v>
+        <v>1796995</v>
       </c>
       <c r="H75" t="n">
-        <v>4840</v>
+        <v>179699</v>
       </c>
       <c r="I75" t="n">
-        <v>43560</v>
+        <v>1617296</v>
       </c>
     </row>
     <row r="76">
@@ -3520,22 +3520,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>Apr 2021</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>48400</v>
+        <v>1796995</v>
       </c>
       <c r="H76" t="n">
-        <v>4840</v>
+        <v>179699</v>
       </c>
       <c r="I76" t="n">
-        <v>43560</v>
+        <v>1617296</v>
       </c>
     </row>
     <row r="77">
@@ -3561,22 +3561,22 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Jul 2021</t>
+          <t>May 2021</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>48400</v>
+        <v>1796995</v>
       </c>
       <c r="H77" t="n">
-        <v>4840</v>
+        <v>179699</v>
       </c>
       <c r="I77" t="n">
-        <v>43560</v>
+        <v>1617296</v>
       </c>
     </row>
     <row r="78">
@@ -3602,22 +3602,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Aug 2021</t>
+          <t>Jun 2021</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>48400</v>
+        <v>1796995</v>
       </c>
       <c r="H78" t="n">
-        <v>4840</v>
+        <v>179699</v>
       </c>
       <c r="I78" t="n">
-        <v>43560</v>
+        <v>1617296</v>
       </c>
     </row>
     <row r="79">
@@ -3643,22 +3643,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>Jul 2021</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>48400</v>
+        <v>1796995</v>
       </c>
       <c r="H79" t="n">
-        <v>4840</v>
+        <v>179699</v>
       </c>
       <c r="I79" t="n">
-        <v>43560</v>
+        <v>1617296</v>
       </c>
     </row>
     <row r="80">
@@ -3684,22 +3684,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>Aug 2021</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>48400</v>
+        <v>1796995</v>
       </c>
       <c r="H80" t="n">
-        <v>4840</v>
+        <v>179699</v>
       </c>
       <c r="I80" t="n">
-        <v>43560</v>
+        <v>1617296</v>
       </c>
     </row>
     <row r="81">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>48400</v>
+        <v>1796995</v>
       </c>
       <c r="H81" t="n">
-        <v>4840</v>
+        <v>179699</v>
       </c>
       <c r="I81" t="n">
-        <v>43560</v>
+        <v>1617296</v>
       </c>
     </row>
     <row r="82">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>48400</v>
+        <v>1796995</v>
       </c>
       <c r="H82" t="n">
-        <v>4840</v>
+        <v>179699</v>
       </c>
       <c r="I82" t="n">
-        <v>43560</v>
+        <v>1617296</v>
       </c>
     </row>
     <row r="83">
@@ -3807,22 +3807,22 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Jan 2022</t>
+          <t>Nov 2021</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>53240</v>
+        <v>1796995</v>
       </c>
       <c r="H83" t="n">
-        <v>5324</v>
+        <v>179699</v>
       </c>
       <c r="I83" t="n">
-        <v>47916</v>
+        <v>1617296</v>
       </c>
     </row>
     <row r="84">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Feb 2022</t>
+          <t>Jan 2022</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>53240</v>
+        <v>1976694</v>
       </c>
       <c r="H84" t="n">
-        <v>5324</v>
+        <v>197669</v>
       </c>
       <c r="I84" t="n">
-        <v>47916</v>
+        <v>1779025</v>
       </c>
     </row>
     <row r="85">
@@ -3889,22 +3889,22 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mar 2022</t>
+          <t>Feb 2022</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>53240</v>
+        <v>1976694</v>
       </c>
       <c r="H85" t="n">
-        <v>5324</v>
+        <v>197669</v>
       </c>
       <c r="I85" t="n">
-        <v>47916</v>
+        <v>1779025</v>
       </c>
     </row>
     <row r="86">
@@ -3930,22 +3930,22 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Apr 2022</t>
+          <t>Mar 2022</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>53240</v>
+        <v>1976694</v>
       </c>
       <c r="H86" t="n">
-        <v>5324</v>
+        <v>197669</v>
       </c>
       <c r="I86" t="n">
-        <v>47916</v>
+        <v>1779025</v>
       </c>
     </row>
     <row r="87">
@@ -3971,22 +3971,22 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>May 2022</t>
+          <t>Apr 2022</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>53240</v>
+        <v>1976694</v>
       </c>
       <c r="H87" t="n">
-        <v>5324</v>
+        <v>197669</v>
       </c>
       <c r="I87" t="n">
-        <v>47916</v>
+        <v>1779025</v>
       </c>
     </row>
     <row r="88">
@@ -4012,22 +4012,22 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>Aug 2022</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>53240</v>
+        <v>1976694</v>
       </c>
       <c r="H88" t="n">
-        <v>5324</v>
+        <v>197669</v>
       </c>
       <c r="I88" t="n">
-        <v>47916</v>
+        <v>1779025</v>
       </c>
     </row>
     <row r="89">
@@ -4053,22 +4053,22 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Jul 2022</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>53240</v>
+        <v>1976694</v>
       </c>
       <c r="H89" t="n">
-        <v>5324</v>
+        <v>197669</v>
       </c>
       <c r="I89" t="n">
-        <v>47916</v>
+        <v>1779025</v>
       </c>
     </row>
     <row r="90">
@@ -4094,22 +4094,22 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>Oct 2022</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>53240</v>
+        <v>1976694</v>
       </c>
       <c r="H90" t="n">
-        <v>5324</v>
+        <v>197669</v>
       </c>
       <c r="I90" t="n">
-        <v>47916</v>
+        <v>1779025</v>
       </c>
     </row>
     <row r="91">
@@ -4135,22 +4135,22 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Nov 2022</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>53240</v>
+        <v>1976694</v>
       </c>
       <c r="H91" t="n">
-        <v>5324</v>
+        <v>197669</v>
       </c>
       <c r="I91" t="n">
-        <v>47916</v>
+        <v>1779025</v>
       </c>
     </row>
     <row r="92">
@@ -4176,22 +4176,22 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>Jan 2023</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>53240</v>
+        <v>2174364</v>
       </c>
       <c r="H92" t="n">
-        <v>5324</v>
+        <v>217436</v>
       </c>
       <c r="I92" t="n">
-        <v>47916</v>
+        <v>1956928</v>
       </c>
     </row>
     <row r="93">
@@ -4217,22 +4217,22 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dec 2022</t>
+          <t>Feb 2023</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>53240</v>
+        <v>2174364</v>
       </c>
       <c r="H93" t="n">
-        <v>5324</v>
+        <v>217436</v>
       </c>
       <c r="I93" t="n">
-        <v>47916</v>
+        <v>1956928</v>
       </c>
     </row>
     <row r="94">
@@ -4258,22 +4258,22 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>Apr 2023</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>58564</v>
+        <v>2174364</v>
       </c>
       <c r="H94" t="n">
-        <v>5856</v>
+        <v>217436</v>
       </c>
       <c r="I94" t="n">
-        <v>52708</v>
+        <v>1956928</v>
       </c>
     </row>
     <row r="95">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mar 2023</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>58564</v>
+        <v>2174364</v>
       </c>
       <c r="H95" t="n">
-        <v>5856</v>
+        <v>217436</v>
       </c>
       <c r="I95" t="n">
-        <v>52708</v>
+        <v>1956928</v>
       </c>
     </row>
     <row r="96">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Apr 2023</t>
+          <t>Jul 2023</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>58564</v>
+        <v>2174364</v>
       </c>
       <c r="H96" t="n">
-        <v>5856</v>
+        <v>217436</v>
       </c>
       <c r="I96" t="n">
-        <v>52708</v>
+        <v>1956928</v>
       </c>
     </row>
     <row r="97">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>Aug 2023</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>58564</v>
+        <v>2174364</v>
       </c>
       <c r="H97" t="n">
-        <v>5856</v>
+        <v>217436</v>
       </c>
       <c r="I97" t="n">
-        <v>52708</v>
+        <v>1956928</v>
       </c>
     </row>
     <row r="98">
@@ -4422,22 +4422,22 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>Sep 2023</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>58564</v>
+        <v>2174364</v>
       </c>
       <c r="H98" t="n">
-        <v>5856</v>
+        <v>217436</v>
       </c>
       <c r="I98" t="n">
-        <v>52708</v>
+        <v>1956928</v>
       </c>
     </row>
     <row r="99">
@@ -4463,22 +4463,22 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Aug 2023</t>
+          <t>Oct 2023</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>58564</v>
+        <v>2174364</v>
       </c>
       <c r="H99" t="n">
-        <v>5856</v>
+        <v>217436</v>
       </c>
       <c r="I99" t="n">
-        <v>52708</v>
+        <v>1956928</v>
       </c>
     </row>
     <row r="100">
@@ -4504,22 +4504,22 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Oct 2023</t>
+          <t>Nov 2023</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>58564</v>
+        <v>2174364</v>
       </c>
       <c r="H100" t="n">
-        <v>5856</v>
+        <v>217436</v>
       </c>
       <c r="I100" t="n">
-        <v>52708</v>
+        <v>1956928</v>
       </c>
     </row>
     <row r="101">
@@ -4554,13 +4554,13 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>58564</v>
+        <v>2174364</v>
       </c>
       <c r="H101" t="n">
-        <v>5856</v>
+        <v>217436</v>
       </c>
       <c r="I101" t="n">
-        <v>52708</v>
+        <v>1956928</v>
       </c>
     </row>
     <row r="102">
@@ -4586,22 +4586,22 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sep 2019</t>
+          <t>Mar 2019</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>139790</v>
+        <v>131303</v>
       </c>
       <c r="H102" t="n">
-        <v>13979</v>
+        <v>13130</v>
       </c>
       <c r="I102" t="n">
-        <v>125811</v>
+        <v>118173</v>
       </c>
     </row>
     <row r="103">
@@ -4627,22 +4627,22 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>109859</v>
+        <v>117348</v>
       </c>
       <c r="H103" t="n">
-        <v>10985</v>
+        <v>11734</v>
       </c>
       <c r="I103" t="n">
-        <v>98874</v>
+        <v>105614</v>
       </c>
     </row>
     <row r="104">
@@ -4668,22 +4668,22 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>131528</v>
+        <v>120825</v>
       </c>
       <c r="H104" t="n">
-        <v>13152</v>
+        <v>12082</v>
       </c>
       <c r="I104" t="n">
-        <v>118376</v>
+        <v>108743</v>
       </c>
     </row>
     <row r="105">
@@ -4709,22 +4709,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Dec 2019</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>108704</v>
+        <v>139269</v>
       </c>
       <c r="H105" t="n">
-        <v>10870</v>
+        <v>13926</v>
       </c>
       <c r="I105" t="n">
-        <v>97834</v>
+        <v>125343</v>
       </c>
     </row>
     <row r="106">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>108062</v>
+        <v>142601</v>
       </c>
       <c r="H106" t="n">
-        <v>10806</v>
+        <v>14260</v>
       </c>
       <c r="I106" t="n">
-        <v>97256</v>
+        <v>128341</v>
       </c>
     </row>
     <row r="107">
@@ -4791,22 +4791,22 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>140234</v>
+        <v>128690</v>
       </c>
       <c r="H107" t="n">
-        <v>14023</v>
+        <v>12869</v>
       </c>
       <c r="I107" t="n">
-        <v>126211</v>
+        <v>115821</v>
       </c>
     </row>
     <row r="108">
@@ -4832,22 +4832,22 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>121951</v>
+        <v>119197</v>
       </c>
       <c r="H108" t="n">
-        <v>12195</v>
+        <v>11919</v>
       </c>
       <c r="I108" t="n">
-        <v>109756</v>
+        <v>107278</v>
       </c>
     </row>
     <row r="109">
@@ -4873,22 +4873,22 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dec 2022</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>130520</v>
+        <v>128803</v>
       </c>
       <c r="H109" t="n">
-        <v>13052</v>
+        <v>12880</v>
       </c>
       <c r="I109" t="n">
-        <v>117468</v>
+        <v>115923</v>
       </c>
     </row>
     <row r="110">
@@ -4914,22 +4914,22 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>126471</v>
+        <v>140235</v>
       </c>
       <c r="H110" t="n">
-        <v>12647</v>
+        <v>14023</v>
       </c>
       <c r="I110" t="n">
-        <v>113824</v>
+        <v>126212</v>
       </c>
     </row>
     <row r="111">
@@ -4955,350 +4955,350 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>148458</v>
+        <v>116823</v>
       </c>
       <c r="H111" t="n">
-        <v>14845</v>
+        <v>11682</v>
       </c>
       <c r="I111" t="n">
-        <v>133613</v>
+        <v>105141</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>C-1002</t>
+          <t>C-1001</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Robert Kramer</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Relationship Manager</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Feb 2019</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>84963</v>
+        <v>111586</v>
       </c>
       <c r="H112" t="n">
-        <v>12744</v>
+        <v>11158</v>
       </c>
       <c r="I112" t="n">
-        <v>72219</v>
+        <v>100428</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>C-1002</t>
+          <t>C-1001</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Robert Kramer</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Relationship Manager</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>May 2019</t>
+          <t>Mar 2022</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>83746</v>
+        <v>131040</v>
       </c>
       <c r="H113" t="n">
-        <v>12561</v>
+        <v>13104</v>
       </c>
       <c r="I113" t="n">
-        <v>71185</v>
+        <v>117936</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>C-1002</t>
+          <t>C-1001</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Robert Kramer</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Relationship Manager</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Jun 2019</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>108509</v>
+        <v>115615</v>
       </c>
       <c r="H114" t="n">
-        <v>16276</v>
+        <v>11561</v>
       </c>
       <c r="I114" t="n">
-        <v>92233</v>
+        <v>104054</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>C-1002</t>
+          <t>C-1001</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Robert Kramer</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Relationship Manager</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Jul 2019</t>
+          <t>Dec 2022</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>83404</v>
+        <v>112111</v>
       </c>
       <c r="H115" t="n">
-        <v>12510</v>
+        <v>11211</v>
       </c>
       <c r="I115" t="n">
-        <v>70894</v>
+        <v>100900</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>C-1002</t>
+          <t>C-1001</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Robert Kramer</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Relationship Manager</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Aug 2019</t>
+          <t>Mar 2023</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>84212</v>
+        <v>113877</v>
       </c>
       <c r="H116" t="n">
-        <v>12631</v>
+        <v>11387</v>
       </c>
       <c r="I116" t="n">
-        <v>71581</v>
+        <v>102490</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>C-1002</t>
+          <t>C-1001</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Robert Kramer</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Relationship Manager</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sep 2019</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>109349</v>
+        <v>137952</v>
       </c>
       <c r="H117" t="n">
-        <v>16402</v>
+        <v>13795</v>
       </c>
       <c r="I117" t="n">
-        <v>92947</v>
+        <v>124157</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>C-1002</t>
+          <t>C-1001</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Robert Kramer</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Relationship Manager</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Oct 2019</t>
+          <t>Sep 2023</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>84421</v>
+        <v>138160</v>
       </c>
       <c r="H118" t="n">
-        <v>12663</v>
+        <v>13816</v>
       </c>
       <c r="I118" t="n">
-        <v>71758</v>
+        <v>124344</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>C-1002</t>
+          <t>C-1001</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Robert Kramer</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Relationship Manager</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nov 2019</t>
+          <t>Dec 2023</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>84943</v>
+        <v>110806</v>
       </c>
       <c r="H119" t="n">
-        <v>12741</v>
+        <v>11080</v>
       </c>
       <c r="I119" t="n">
-        <v>72202</v>
+        <v>99726</v>
       </c>
     </row>
     <row r="120">
@@ -5324,22 +5324,22 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>Jan 2019</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>145693</v>
+        <v>129956</v>
       </c>
       <c r="H120" t="n">
-        <v>21853</v>
+        <v>19493</v>
       </c>
       <c r="I120" t="n">
-        <v>123840</v>
+        <v>110463</v>
       </c>
     </row>
     <row r="121">
@@ -5365,22 +5365,22 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Jan 2020</t>
+          <t>Mar 2019</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>85418</v>
+        <v>155941</v>
       </c>
       <c r="H121" t="n">
-        <v>12812</v>
+        <v>23391</v>
       </c>
       <c r="I121" t="n">
-        <v>72606</v>
+        <v>132550</v>
       </c>
     </row>
     <row r="122">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Feb 2020</t>
+          <t>Apr 2019</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>85508</v>
+        <v>129250</v>
       </c>
       <c r="H122" t="n">
-        <v>12826</v>
+        <v>19387</v>
       </c>
       <c r="I122" t="n">
-        <v>72682</v>
+        <v>109863</v>
       </c>
     </row>
     <row r="123">
@@ -5447,22 +5447,22 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>May 2019</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>97831</v>
+        <v>130630</v>
       </c>
       <c r="H123" t="n">
-        <v>14674</v>
+        <v>19594</v>
       </c>
       <c r="I123" t="n">
-        <v>83157</v>
+        <v>111036</v>
       </c>
     </row>
     <row r="124">
@@ -5488,22 +5488,22 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Apr 2020</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>85369</v>
+        <v>170272</v>
       </c>
       <c r="H124" t="n">
-        <v>12805</v>
+        <v>25540</v>
       </c>
       <c r="I124" t="n">
-        <v>72564</v>
+        <v>144732</v>
       </c>
     </row>
     <row r="125">
@@ -5529,22 +5529,22 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Aug 2019</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>84686</v>
+        <v>130973</v>
       </c>
       <c r="H125" t="n">
-        <v>12702</v>
+        <v>19645</v>
       </c>
       <c r="I125" t="n">
-        <v>71984</v>
+        <v>111328</v>
       </c>
     </row>
     <row r="126">
@@ -5570,22 +5570,22 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>100515</v>
+        <v>157020</v>
       </c>
       <c r="H126" t="n">
-        <v>15077</v>
+        <v>23553</v>
       </c>
       <c r="I126" t="n">
-        <v>85438</v>
+        <v>133467</v>
       </c>
     </row>
     <row r="127">
@@ -5611,22 +5611,22 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>Oct 2019</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>84401</v>
+        <v>130591</v>
       </c>
       <c r="H127" t="n">
-        <v>12660</v>
+        <v>19588</v>
       </c>
       <c r="I127" t="n">
-        <v>71741</v>
+        <v>111003</v>
       </c>
     </row>
     <row r="128">
@@ -5652,22 +5652,22 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Nov 2019</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>108240</v>
+        <v>127600</v>
       </c>
       <c r="H128" t="n">
-        <v>16236</v>
+        <v>19140</v>
       </c>
       <c r="I128" t="n">
-        <v>92004</v>
+        <v>108460</v>
       </c>
     </row>
     <row r="129">
@@ -5693,22 +5693,22 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Oct 2020</t>
+          <t>Dec 2019</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>86396</v>
+        <v>247917</v>
       </c>
       <c r="H129" t="n">
-        <v>12959</v>
+        <v>37187</v>
       </c>
       <c r="I129" t="n">
-        <v>73437</v>
+        <v>210730</v>
       </c>
     </row>
     <row r="130">
@@ -5734,22 +5734,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Nov 2020</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>84150</v>
+        <v>127594</v>
       </c>
       <c r="H130" t="n">
-        <v>12622</v>
+        <v>19139</v>
       </c>
       <c r="I130" t="n">
-        <v>71528</v>
+        <v>108455</v>
       </c>
     </row>
     <row r="131">
@@ -5775,22 +5775,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>167682</v>
+        <v>154351</v>
       </c>
       <c r="H131" t="n">
-        <v>25152</v>
+        <v>23152</v>
       </c>
       <c r="I131" t="n">
-        <v>142530</v>
+        <v>131199</v>
       </c>
     </row>
     <row r="132">
@@ -5816,22 +5816,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Jan 2021</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>86066</v>
+        <v>132451</v>
       </c>
       <c r="H132" t="n">
-        <v>12909</v>
+        <v>19867</v>
       </c>
       <c r="I132" t="n">
-        <v>73157</v>
+        <v>112584</v>
       </c>
     </row>
     <row r="133">
@@ -5857,22 +5857,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Feb 2021</t>
+          <t>May 2020</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>85860</v>
+        <v>127691</v>
       </c>
       <c r="H133" t="n">
-        <v>12879</v>
+        <v>19153</v>
       </c>
       <c r="I133" t="n">
-        <v>72981</v>
+        <v>108538</v>
       </c>
     </row>
     <row r="134">
@@ -5898,22 +5898,22 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>106415</v>
+        <v>153008</v>
       </c>
       <c r="H134" t="n">
-        <v>15962</v>
+        <v>22951</v>
       </c>
       <c r="I134" t="n">
-        <v>90453</v>
+        <v>130057</v>
       </c>
     </row>
     <row r="135">
@@ -5939,22 +5939,22 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Apr 2021</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>86415</v>
+        <v>130775</v>
       </c>
       <c r="H135" t="n">
-        <v>12962</v>
+        <v>19616</v>
       </c>
       <c r="I135" t="n">
-        <v>73453</v>
+        <v>111159</v>
       </c>
     </row>
     <row r="136">
@@ -5980,22 +5980,22 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>May 2021</t>
+          <t>Aug 2020</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>85400</v>
+        <v>131774</v>
       </c>
       <c r="H136" t="n">
-        <v>12810</v>
+        <v>19766</v>
       </c>
       <c r="I136" t="n">
-        <v>72590</v>
+        <v>112008</v>
       </c>
     </row>
     <row r="137">
@@ -6021,22 +6021,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>110736</v>
+        <v>166538</v>
       </c>
       <c r="H137" t="n">
-        <v>16610</v>
+        <v>24980</v>
       </c>
       <c r="I137" t="n">
-        <v>94126</v>
+        <v>141558</v>
       </c>
     </row>
     <row r="138">
@@ -6062,22 +6062,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Jul 2021</t>
+          <t>Oct 2020</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>86475</v>
+        <v>129225</v>
       </c>
       <c r="H138" t="n">
-        <v>12971</v>
+        <v>19383</v>
       </c>
       <c r="I138" t="n">
-        <v>73504</v>
+        <v>109842</v>
       </c>
     </row>
     <row r="139">
@@ -6103,22 +6103,22 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Aug 2021</t>
+          <t>Nov 2020</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>83589</v>
+        <v>129410</v>
       </c>
       <c r="H139" t="n">
-        <v>12538</v>
+        <v>19411</v>
       </c>
       <c r="I139" t="n">
-        <v>71051</v>
+        <v>109999</v>
       </c>
     </row>
     <row r="140">
@@ -6144,22 +6144,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>98801</v>
+        <v>222726</v>
       </c>
       <c r="H140" t="n">
-        <v>14820</v>
+        <v>33408</v>
       </c>
       <c r="I140" t="n">
-        <v>83981</v>
+        <v>189318</v>
       </c>
     </row>
     <row r="141">
@@ -6185,22 +6185,22 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>Jan 2021</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>84031</v>
+        <v>162727</v>
       </c>
       <c r="H141" t="n">
-        <v>12604</v>
+        <v>24409</v>
       </c>
       <c r="I141" t="n">
-        <v>71427</v>
+        <v>138318</v>
       </c>
     </row>
     <row r="142">
@@ -6226,22 +6226,22 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>Feb 2021</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>85219</v>
+        <v>162192</v>
       </c>
       <c r="H142" t="n">
-        <v>12782</v>
+        <v>24328</v>
       </c>
       <c r="I142" t="n">
-        <v>72437</v>
+        <v>137864</v>
       </c>
     </row>
     <row r="143">
@@ -6267,22 +6267,22 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>164695</v>
+        <v>195525</v>
       </c>
       <c r="H143" t="n">
-        <v>24704</v>
+        <v>29328</v>
       </c>
       <c r="I143" t="n">
-        <v>139991</v>
+        <v>166197</v>
       </c>
     </row>
     <row r="144">
@@ -6308,22 +6308,22 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Feb 2022</t>
+          <t>Apr 2021</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>86253</v>
+        <v>162452</v>
       </c>
       <c r="H144" t="n">
-        <v>12937</v>
+        <v>24367</v>
       </c>
       <c r="I144" t="n">
-        <v>73316</v>
+        <v>138085</v>
       </c>
     </row>
     <row r="145">
@@ -6349,22 +6349,22 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>May 2022</t>
+          <t>May 2021</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>84647</v>
+        <v>157062</v>
       </c>
       <c r="H145" t="n">
-        <v>12697</v>
+        <v>23559</v>
       </c>
       <c r="I145" t="n">
-        <v>71950</v>
+        <v>133503</v>
       </c>
     </row>
     <row r="146">
@@ -6390,22 +6390,22 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>Jun 2021</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>104153</v>
+        <v>189662</v>
       </c>
       <c r="H146" t="n">
-        <v>15622</v>
+        <v>28449</v>
       </c>
       <c r="I146" t="n">
-        <v>88531</v>
+        <v>161213</v>
       </c>
     </row>
     <row r="147">
@@ -6431,22 +6431,22 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Jul 2022</t>
+          <t>Jul 2021</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>86498</v>
+        <v>158005</v>
       </c>
       <c r="H147" t="n">
-        <v>12974</v>
+        <v>23700</v>
       </c>
       <c r="I147" t="n">
-        <v>73524</v>
+        <v>134305</v>
       </c>
     </row>
     <row r="148">
@@ -6472,22 +6472,22 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Aug 2021</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>98666</v>
+        <v>159099</v>
       </c>
       <c r="H148" t="n">
-        <v>14799</v>
+        <v>23864</v>
       </c>
       <c r="I148" t="n">
-        <v>83867</v>
+        <v>135235</v>
       </c>
     </row>
     <row r="149">
@@ -6513,22 +6513,22 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>84335</v>
+        <v>192964</v>
       </c>
       <c r="H149" t="n">
-        <v>12650</v>
+        <v>28944</v>
       </c>
       <c r="I149" t="n">
-        <v>71685</v>
+        <v>164020</v>
       </c>
     </row>
     <row r="150">
@@ -6554,22 +6554,22 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Nov 2022</t>
+          <t>Nov 2021</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>84476</v>
+        <v>157044</v>
       </c>
       <c r="H150" t="n">
-        <v>12671</v>
+        <v>23556</v>
       </c>
       <c r="I150" t="n">
-        <v>71805</v>
+        <v>133488</v>
       </c>
     </row>
     <row r="151">
@@ -6595,22 +6595,22 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dec 2022</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>162523</v>
+        <v>289204</v>
       </c>
       <c r="H151" t="n">
-        <v>24378</v>
+        <v>43380</v>
       </c>
       <c r="I151" t="n">
-        <v>138145</v>
+        <v>245824</v>
       </c>
     </row>
     <row r="152">
@@ -6636,22 +6636,22 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Jan 2023</t>
+          <t>Jan 2022</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>84989</v>
+        <v>162748</v>
       </c>
       <c r="H152" t="n">
-        <v>12748</v>
+        <v>24412</v>
       </c>
       <c r="I152" t="n">
-        <v>72241</v>
+        <v>138336</v>
       </c>
     </row>
     <row r="153">
@@ -6677,22 +6677,22 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>Feb 2022</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>85318</v>
+        <v>157873</v>
       </c>
       <c r="H153" t="n">
-        <v>12797</v>
+        <v>23680</v>
       </c>
       <c r="I153" t="n">
-        <v>72521</v>
+        <v>134193</v>
       </c>
     </row>
     <row r="154">
@@ -6718,22 +6718,22 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mar 2023</t>
+          <t>Apr 2022</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>106948</v>
+        <v>157807</v>
       </c>
       <c r="H154" t="n">
-        <v>16042</v>
+        <v>23671</v>
       </c>
       <c r="I154" t="n">
-        <v>90906</v>
+        <v>134136</v>
       </c>
     </row>
     <row r="155">
@@ -6759,22 +6759,22 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Apr 2023</t>
+          <t>May 2022</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>86398</v>
+        <v>162738</v>
       </c>
       <c r="H155" t="n">
-        <v>12959</v>
+        <v>24410</v>
       </c>
       <c r="I155" t="n">
-        <v>73439</v>
+        <v>138328</v>
       </c>
     </row>
     <row r="156">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>85091</v>
+        <v>192490</v>
       </c>
       <c r="H156" t="n">
-        <v>12763</v>
+        <v>28873</v>
       </c>
       <c r="I156" t="n">
-        <v>72328</v>
+        <v>163617</v>
       </c>
     </row>
     <row r="157">
@@ -6841,22 +6841,22 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>Aug 2022</t>
         </is>
       </c>
       <c r="G157" t="n">
-        <v>109485</v>
+        <v>159050</v>
       </c>
       <c r="H157" t="n">
-        <v>16422</v>
+        <v>23857</v>
       </c>
       <c r="I157" t="n">
-        <v>93063</v>
+        <v>135193</v>
       </c>
     </row>
     <row r="158">
@@ -6882,22 +6882,22 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>84166</v>
+        <v>194066</v>
       </c>
       <c r="H158" t="n">
-        <v>12624</v>
+        <v>29109</v>
       </c>
       <c r="I158" t="n">
-        <v>71542</v>
+        <v>164957</v>
       </c>
     </row>
     <row r="159">
@@ -6923,22 +6923,22 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Oct 2023</t>
+          <t>Oct 2022</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>84432</v>
+        <v>161734</v>
       </c>
       <c r="H159" t="n">
-        <v>12664</v>
+        <v>24260</v>
       </c>
       <c r="I159" t="n">
-        <v>71768</v>
+        <v>137474</v>
       </c>
     </row>
     <row r="160">
@@ -6964,22 +6964,22 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Nov 2023</t>
+          <t>Jan 2023</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>86457</v>
+        <v>157555</v>
       </c>
       <c r="H160" t="n">
-        <v>12968</v>
+        <v>23633</v>
       </c>
       <c r="I160" t="n">
-        <v>73489</v>
+        <v>133922</v>
       </c>
     </row>
     <row r="161">
@@ -7005,22 +7005,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Dec 2023</t>
+          <t>Mar 2023</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>165934</v>
+        <v>189449</v>
       </c>
       <c r="H161" t="n">
-        <v>24890</v>
+        <v>28417</v>
       </c>
       <c r="I161" t="n">
-        <v>141044</v>
+        <v>161032</v>
       </c>
     </row>
     <row r="162">
@@ -7036,32 +7036,32 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Shareholder / Director</t>
+          <t>Relationship Manager</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Corporate Equity Liquidation</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mar 2019</t>
+          <t>Apr 2023</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>195835</v>
+        <v>160189</v>
       </c>
       <c r="H162" t="n">
-        <v>19583</v>
+        <v>24028</v>
       </c>
       <c r="I162" t="n">
-        <v>176252</v>
+        <v>136161</v>
       </c>
     </row>
     <row r="163">
@@ -7077,32 +7077,32 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Shareholder / Director</t>
+          <t>Relationship Manager</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Corporate Equity Liquidation</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Jun 2019</t>
+          <t>May 2023</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>216081</v>
+        <v>159330</v>
       </c>
       <c r="H163" t="n">
-        <v>21608</v>
+        <v>23899</v>
       </c>
       <c r="I163" t="n">
-        <v>194473</v>
+        <v>135431</v>
       </c>
     </row>
     <row r="164">
@@ -7118,32 +7118,32 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Shareholder / Director</t>
+          <t>Relationship Manager</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Corporate Equity Liquidation</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sep 2019</t>
+          <t>Jul 2023</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>202189</v>
+        <v>159860</v>
       </c>
       <c r="H164" t="n">
-        <v>20218</v>
+        <v>23979</v>
       </c>
       <c r="I164" t="n">
-        <v>181971</v>
+        <v>135881</v>
       </c>
     </row>
     <row r="165">
@@ -7159,32 +7159,32 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Shareholder / Director</t>
+          <t>Relationship Manager</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Corporate Equity Liquidation</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>Aug 2023</t>
         </is>
       </c>
       <c r="G165" t="n">
-        <v>211175</v>
+        <v>157595</v>
       </c>
       <c r="H165" t="n">
-        <v>21117</v>
+        <v>23639</v>
       </c>
       <c r="I165" t="n">
-        <v>190058</v>
+        <v>133956</v>
       </c>
     </row>
     <row r="166">
@@ -7200,32 +7200,32 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Shareholder / Director</t>
+          <t>Relationship Manager</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Corporate Equity Liquidation</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>Sep 2023</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>236251</v>
+        <v>185258</v>
       </c>
       <c r="H166" t="n">
-        <v>23625</v>
+        <v>27788</v>
       </c>
       <c r="I166" t="n">
-        <v>212626</v>
+        <v>157470</v>
       </c>
     </row>
     <row r="167">
@@ -7241,32 +7241,32 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Shareholder / Director</t>
+          <t>Relationship Manager</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Corporate Equity Liquidation</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>Oct 2023</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>195572</v>
+        <v>161332</v>
       </c>
       <c r="H167" t="n">
-        <v>19557</v>
+        <v>24199</v>
       </c>
       <c r="I167" t="n">
-        <v>176015</v>
+        <v>137133</v>
       </c>
     </row>
     <row r="168">
@@ -7282,32 +7282,32 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Shareholder / Director</t>
+          <t>Relationship Manager</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Corporate Equity Liquidation</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mar 2022</t>
+          <t>Nov 2023</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>209628</v>
+        <v>157381</v>
       </c>
       <c r="H168" t="n">
-        <v>20962</v>
+        <v>23607</v>
       </c>
       <c r="I168" t="n">
-        <v>188666</v>
+        <v>133774</v>
       </c>
     </row>
     <row r="169">
@@ -7323,32 +7323,32 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Shareholder / Director</t>
+          <t>Relationship Manager</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Corporate Equity Liquidation</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Dec 2023</t>
         </is>
       </c>
       <c r="G169" t="n">
-        <v>198112</v>
+        <v>273804</v>
       </c>
       <c r="H169" t="n">
-        <v>19811</v>
+        <v>41070</v>
       </c>
       <c r="I169" t="n">
-        <v>178301</v>
+        <v>232734</v>
       </c>
     </row>
     <row r="170">
@@ -7374,22 +7374,22 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mar 2023</t>
+          <t>Mar 2019</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>243596</v>
+        <v>187575</v>
       </c>
       <c r="H170" t="n">
-        <v>24359</v>
+        <v>18757</v>
       </c>
       <c r="I170" t="n">
-        <v>219237</v>
+        <v>168818</v>
       </c>
     </row>
     <row r="171">
@@ -7415,678 +7415,678 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>231881</v>
+        <v>181416</v>
       </c>
       <c r="H171" t="n">
-        <v>23188</v>
+        <v>18141</v>
       </c>
       <c r="I171" t="n">
-        <v>208693</v>
+        <v>163275</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Jan 2019</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>50730</v>
+        <v>189393</v>
       </c>
       <c r="H172" t="n">
-        <v>7609</v>
+        <v>18939</v>
       </c>
       <c r="I172" t="n">
-        <v>43121</v>
+        <v>170454</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Feb 2019</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>50448</v>
+        <v>235423</v>
       </c>
       <c r="H173" t="n">
-        <v>7567</v>
+        <v>23542</v>
       </c>
       <c r="I173" t="n">
-        <v>42881</v>
+        <v>211881</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mar 2019</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>61566</v>
+        <v>194174</v>
       </c>
       <c r="H174" t="n">
-        <v>9234</v>
+        <v>19417</v>
       </c>
       <c r="I174" t="n">
-        <v>52332</v>
+        <v>174757</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>May 2019</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>49904</v>
+        <v>236912</v>
       </c>
       <c r="H175" t="n">
-        <v>7485</v>
+        <v>23691</v>
       </c>
       <c r="I175" t="n">
-        <v>42419</v>
+        <v>213221</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Jul 2019</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>50467</v>
+        <v>190126</v>
       </c>
       <c r="H176" t="n">
-        <v>7570</v>
+        <v>19012</v>
       </c>
       <c r="I176" t="n">
-        <v>42897</v>
+        <v>171114</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Aug 2019</t>
+          <t>Jun 2021</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>50105</v>
+        <v>221953</v>
       </c>
       <c r="H177" t="n">
-        <v>7515</v>
+        <v>22195</v>
       </c>
       <c r="I177" t="n">
-        <v>42590</v>
+        <v>199758</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sep 2019</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>58783</v>
+        <v>238589</v>
       </c>
       <c r="H178" t="n">
-        <v>8817</v>
+        <v>23858</v>
       </c>
       <c r="I178" t="n">
-        <v>49966</v>
+        <v>214731</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Oct 2019</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>50795</v>
+        <v>235725</v>
       </c>
       <c r="H179" t="n">
-        <v>7619</v>
+        <v>23572</v>
       </c>
       <c r="I179" t="n">
-        <v>43176</v>
+        <v>212153</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Nov 2019</t>
+          <t>Mar 2022</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>49454</v>
+        <v>211250</v>
       </c>
       <c r="H180" t="n">
-        <v>7418</v>
+        <v>21125</v>
       </c>
       <c r="I180" t="n">
-        <v>42036</v>
+        <v>190125</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>98806</v>
+        <v>196444</v>
       </c>
       <c r="H181" t="n">
-        <v>14820</v>
+        <v>19644</v>
       </c>
       <c r="I181" t="n">
-        <v>83986</v>
+        <v>176800</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Jan 2020</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>50499</v>
+        <v>210878</v>
       </c>
       <c r="H182" t="n">
-        <v>7574</v>
+        <v>21087</v>
       </c>
       <c r="I182" t="n">
-        <v>42925</v>
+        <v>189791</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Feb 2020</t>
+          <t>Dec 2022</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>50188</v>
+        <v>237905</v>
       </c>
       <c r="H183" t="n">
-        <v>7528</v>
+        <v>23790</v>
       </c>
       <c r="I183" t="n">
-        <v>42660</v>
+        <v>214115</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Mar 2023</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>58850</v>
+        <v>233822</v>
       </c>
       <c r="H184" t="n">
-        <v>8827</v>
+        <v>23382</v>
       </c>
       <c r="I184" t="n">
-        <v>50023</v>
+        <v>210440</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Apr 2020</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>49675</v>
+        <v>192807</v>
       </c>
       <c r="H185" t="n">
-        <v>7451</v>
+        <v>19280</v>
       </c>
       <c r="I185" t="n">
-        <v>42224</v>
+        <v>173527</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Sep 2023</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>50124</v>
+        <v>184591</v>
       </c>
       <c r="H186" t="n">
-        <v>7518</v>
+        <v>18459</v>
       </c>
       <c r="I186" t="n">
-        <v>42606</v>
+        <v>166132</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>C-1003</t>
+          <t>C-1002</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Vikram Seth</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Shareholder / Director</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Executive Yield (Salary)</t>
+          <t>Corporate Equity Liquidation</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Dec 2023</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>65921</v>
+        <v>196055</v>
       </c>
       <c r="H187" t="n">
-        <v>9888</v>
+        <v>19605</v>
       </c>
       <c r="I187" t="n">
-        <v>56033</v>
+        <v>176450</v>
       </c>
     </row>
     <row r="188">
@@ -8112,22 +8112,22 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>Jan 2019</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>49268</v>
+        <v>151732</v>
       </c>
       <c r="H188" t="n">
-        <v>7390</v>
+        <v>22759</v>
       </c>
       <c r="I188" t="n">
-        <v>41878</v>
+        <v>128973</v>
       </c>
     </row>
     <row r="189">
@@ -8153,22 +8153,22 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Feb 2019</t>
         </is>
       </c>
       <c r="G189" t="n">
-        <v>58167</v>
+        <v>152088</v>
       </c>
       <c r="H189" t="n">
-        <v>8725</v>
+        <v>22813</v>
       </c>
       <c r="I189" t="n">
-        <v>49442</v>
+        <v>129275</v>
       </c>
     </row>
     <row r="190">
@@ -8194,22 +8194,22 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Oct 2020</t>
+          <t>Mar 2019</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>50876</v>
+        <v>190394</v>
       </c>
       <c r="H190" t="n">
-        <v>7631</v>
+        <v>28559</v>
       </c>
       <c r="I190" t="n">
-        <v>43245</v>
+        <v>161835</v>
       </c>
     </row>
     <row r="191">
@@ -8235,22 +8235,22 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Nov 2020</t>
+          <t>Apr 2019</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>50407</v>
+        <v>147226</v>
       </c>
       <c r="H191" t="n">
-        <v>7561</v>
+        <v>22083</v>
       </c>
       <c r="I191" t="n">
-        <v>42846</v>
+        <v>125143</v>
       </c>
     </row>
     <row r="192">
@@ -8276,22 +8276,22 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>May 2019</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>92270</v>
+        <v>147901</v>
       </c>
       <c r="H192" t="n">
-        <v>13840</v>
+        <v>22185</v>
       </c>
       <c r="I192" t="n">
-        <v>78430</v>
+        <v>125716</v>
       </c>
     </row>
     <row r="193">
@@ -8317,22 +8317,22 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Jan 2021</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>50405</v>
+        <v>183891</v>
       </c>
       <c r="H193" t="n">
-        <v>7560</v>
+        <v>27583</v>
       </c>
       <c r="I193" t="n">
-        <v>42845</v>
+        <v>156308</v>
       </c>
     </row>
     <row r="194">
@@ -8358,22 +8358,22 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Feb 2021</t>
+          <t>Jul 2019</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>50348</v>
+        <v>147989</v>
       </c>
       <c r="H194" t="n">
-        <v>7552</v>
+        <v>22198</v>
       </c>
       <c r="I194" t="n">
-        <v>42796</v>
+        <v>125791</v>
       </c>
     </row>
     <row r="195">
@@ -8399,22 +8399,22 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>61848</v>
+        <v>183429</v>
       </c>
       <c r="H195" t="n">
-        <v>9277</v>
+        <v>27514</v>
       </c>
       <c r="I195" t="n">
-        <v>52571</v>
+        <v>155915</v>
       </c>
     </row>
     <row r="196">
@@ -8440,22 +8440,22 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Apr 2021</t>
+          <t>Oct 2019</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>50976</v>
+        <v>148353</v>
       </c>
       <c r="H196" t="n">
-        <v>7646</v>
+        <v>22252</v>
       </c>
       <c r="I196" t="n">
-        <v>43330</v>
+        <v>126101</v>
       </c>
     </row>
     <row r="197">
@@ -8481,22 +8481,22 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>May 2021</t>
+          <t>Nov 2019</t>
         </is>
       </c>
       <c r="G197" t="n">
-        <v>49590</v>
+        <v>147999</v>
       </c>
       <c r="H197" t="n">
-        <v>7438</v>
+        <v>22199</v>
       </c>
       <c r="I197" t="n">
-        <v>42152</v>
+        <v>125800</v>
       </c>
     </row>
     <row r="198">
@@ -8522,22 +8522,22 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="G198" t="n">
-        <v>60491</v>
+        <v>151600</v>
       </c>
       <c r="H198" t="n">
-        <v>9073</v>
+        <v>22740</v>
       </c>
       <c r="I198" t="n">
-        <v>51418</v>
+        <v>128860</v>
       </c>
     </row>
     <row r="199">
@@ -8563,22 +8563,22 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Jul 2021</t>
+          <t>Feb 2020</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>50431</v>
+        <v>148831</v>
       </c>
       <c r="H199" t="n">
-        <v>7564</v>
+        <v>22324</v>
       </c>
       <c r="I199" t="n">
-        <v>42867</v>
+        <v>126507</v>
       </c>
     </row>
     <row r="200">
@@ -8604,22 +8604,22 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="G200" t="n">
-        <v>63619</v>
+        <v>179196</v>
       </c>
       <c r="H200" t="n">
-        <v>9542</v>
+        <v>26879</v>
       </c>
       <c r="I200" t="n">
-        <v>54077</v>
+        <v>152317</v>
       </c>
     </row>
     <row r="201">
@@ -8645,22 +8645,22 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>May 2020</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>49135</v>
+        <v>149593</v>
       </c>
       <c r="H201" t="n">
-        <v>7370</v>
+        <v>22438</v>
       </c>
       <c r="I201" t="n">
-        <v>41765</v>
+        <v>127155</v>
       </c>
     </row>
     <row r="202">
@@ -8686,22 +8686,22 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Feb 2022</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>49098</v>
+        <v>147576</v>
       </c>
       <c r="H202" t="n">
-        <v>7364</v>
+        <v>22136</v>
       </c>
       <c r="I202" t="n">
-        <v>41734</v>
+        <v>125440</v>
       </c>
     </row>
     <row r="203">
@@ -8727,22 +8727,22 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Mar 2022</t>
+          <t>Aug 2020</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>57607</v>
+        <v>152941</v>
       </c>
       <c r="H203" t="n">
-        <v>8641</v>
+        <v>22941</v>
       </c>
       <c r="I203" t="n">
-        <v>48966</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="204">
@@ -8768,22 +8768,22 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Apr 2022</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>49274</v>
+        <v>177567</v>
       </c>
       <c r="H204" t="n">
-        <v>7391</v>
+        <v>26635</v>
       </c>
       <c r="I204" t="n">
-        <v>41883</v>
+        <v>150932</v>
       </c>
     </row>
     <row r="205">
@@ -8809,22 +8809,22 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>Oct 2020</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>65250</v>
+        <v>148591</v>
       </c>
       <c r="H205" t="n">
-        <v>9787</v>
+        <v>22288</v>
       </c>
       <c r="I205" t="n">
-        <v>55463</v>
+        <v>126303</v>
       </c>
     </row>
     <row r="206">
@@ -8850,22 +8850,22 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Jul 2022</t>
+          <t>Nov 2020</t>
         </is>
       </c>
       <c r="G206" t="n">
-        <v>50486</v>
+        <v>150555</v>
       </c>
       <c r="H206" t="n">
-        <v>7572</v>
+        <v>22583</v>
       </c>
       <c r="I206" t="n">
-        <v>42914</v>
+        <v>127972</v>
       </c>
     </row>
     <row r="207">
@@ -8891,22 +8891,22 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>50637</v>
+        <v>243013</v>
       </c>
       <c r="H207" t="n">
-        <v>7595</v>
+        <v>36451</v>
       </c>
       <c r="I207" t="n">
-        <v>43042</v>
+        <v>206562</v>
       </c>
     </row>
     <row r="208">
@@ -8932,22 +8932,22 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Jan 2021</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>58991</v>
+        <v>152068</v>
       </c>
       <c r="H208" t="n">
-        <v>8848</v>
+        <v>22810</v>
       </c>
       <c r="I208" t="n">
-        <v>50143</v>
+        <v>129258</v>
       </c>
     </row>
     <row r="209">
@@ -8973,22 +8973,22 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>Feb 2021</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>49234</v>
+        <v>149663</v>
       </c>
       <c r="H209" t="n">
-        <v>7385</v>
+        <v>22449</v>
       </c>
       <c r="I209" t="n">
-        <v>41849</v>
+        <v>127214</v>
       </c>
     </row>
     <row r="210">
@@ -9014,22 +9014,22 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Nov 2022</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>49867</v>
+        <v>175423</v>
       </c>
       <c r="H210" t="n">
-        <v>7480</v>
+        <v>26313</v>
       </c>
       <c r="I210" t="n">
-        <v>42387</v>
+        <v>149110</v>
       </c>
     </row>
     <row r="211">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dec 2022</t>
+          <t>May 2021</t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>84678</v>
+        <v>148647</v>
       </c>
       <c r="H211" t="n">
-        <v>12701</v>
+        <v>22297</v>
       </c>
       <c r="I211" t="n">
-        <v>71977</v>
+        <v>126350</v>
       </c>
     </row>
     <row r="212">
@@ -9096,22 +9096,22 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Jan 2023</t>
+          <t>Jun 2021</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>49244</v>
+        <v>187308</v>
       </c>
       <c r="H212" t="n">
-        <v>7386</v>
+        <v>28096</v>
       </c>
       <c r="I212" t="n">
-        <v>41858</v>
+        <v>159212</v>
       </c>
     </row>
     <row r="213">
@@ -9137,22 +9137,22 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>Jul 2021</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>50572</v>
+        <v>151903</v>
       </c>
       <c r="H213" t="n">
-        <v>7585</v>
+        <v>22785</v>
       </c>
       <c r="I213" t="n">
-        <v>42987</v>
+        <v>129118</v>
       </c>
     </row>
     <row r="214">
@@ -9178,22 +9178,22 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Mar 2023</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="G214" t="n">
-        <v>63386</v>
+        <v>180490</v>
       </c>
       <c r="H214" t="n">
-        <v>9507</v>
+        <v>27073</v>
       </c>
       <c r="I214" t="n">
-        <v>53879</v>
+        <v>153417</v>
       </c>
     </row>
     <row r="215">
@@ -9219,22 +9219,22 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Apr 2023</t>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>50515</v>
+        <v>150561</v>
       </c>
       <c r="H215" t="n">
-        <v>7577</v>
+        <v>22584</v>
       </c>
       <c r="I215" t="n">
-        <v>42938</v>
+        <v>127977</v>
       </c>
     </row>
     <row r="216">
@@ -9260,22 +9260,22 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>Nov 2021</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>50884</v>
+        <v>150075</v>
       </c>
       <c r="H216" t="n">
-        <v>7632</v>
+        <v>22511</v>
       </c>
       <c r="I216" t="n">
-        <v>43252</v>
+        <v>127564</v>
       </c>
     </row>
     <row r="217">
@@ -9301,22 +9301,22 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>50634</v>
+        <v>257110</v>
       </c>
       <c r="H217" t="n">
-        <v>7595</v>
+        <v>38566</v>
       </c>
       <c r="I217" t="n">
-        <v>43039</v>
+        <v>218544</v>
       </c>
     </row>
     <row r="218">
@@ -9342,22 +9342,22 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>Jan 2022</t>
         </is>
       </c>
       <c r="G218" t="n">
-        <v>61578</v>
+        <v>177569</v>
       </c>
       <c r="H218" t="n">
-        <v>9236</v>
+        <v>26635</v>
       </c>
       <c r="I218" t="n">
-        <v>52342</v>
+        <v>150934</v>
       </c>
     </row>
     <row r="219">
@@ -9383,22 +9383,22 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Oct 2023</t>
+          <t>Feb 2022</t>
         </is>
       </c>
       <c r="G219" t="n">
-        <v>50742</v>
+        <v>177282</v>
       </c>
       <c r="H219" t="n">
-        <v>7611</v>
+        <v>26592</v>
       </c>
       <c r="I219" t="n">
-        <v>43131</v>
+        <v>150690</v>
       </c>
     </row>
     <row r="220">
@@ -9424,22 +9424,22 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Nov 2023</t>
+          <t>Mar 2022</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>50535</v>
+        <v>223217</v>
       </c>
       <c r="H220" t="n">
-        <v>7580</v>
+        <v>33482</v>
       </c>
       <c r="I220" t="n">
-        <v>42955</v>
+        <v>189735</v>
       </c>
     </row>
     <row r="221">
@@ -9465,22 +9465,22 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Dec 2023</t>
+          <t>Apr 2022</t>
         </is>
       </c>
       <c r="G221" t="n">
-        <v>84902</v>
+        <v>183139</v>
       </c>
       <c r="H221" t="n">
-        <v>12735</v>
+        <v>27470</v>
       </c>
       <c r="I221" t="n">
-        <v>72167</v>
+        <v>155669</v>
       </c>
     </row>
     <row r="222">
@@ -9496,32 +9496,32 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Feb 2019</t>
+          <t>May 2022</t>
         </is>
       </c>
       <c r="G222" t="n">
-        <v>25000</v>
+        <v>177682</v>
       </c>
       <c r="H222" t="n">
-        <v>2500</v>
+        <v>26652</v>
       </c>
       <c r="I222" t="n">
-        <v>22500</v>
+        <v>151030</v>
       </c>
     </row>
     <row r="223">
@@ -9537,32 +9537,32 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mar 2019</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>25000</v>
+        <v>222289</v>
       </c>
       <c r="H223" t="n">
-        <v>2500</v>
+        <v>33343</v>
       </c>
       <c r="I223" t="n">
-        <v>22500</v>
+        <v>188946</v>
       </c>
     </row>
     <row r="224">
@@ -9578,32 +9578,32 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Apr 2019</t>
+          <t>Jul 2022</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>25000</v>
+        <v>176747</v>
       </c>
       <c r="H224" t="n">
-        <v>2500</v>
+        <v>26512</v>
       </c>
       <c r="I224" t="n">
-        <v>22500</v>
+        <v>150235</v>
       </c>
     </row>
     <row r="225">
@@ -9619,32 +9619,32 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Jun 2019</t>
+          <t>Aug 2022</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>25000</v>
+        <v>180962</v>
       </c>
       <c r="H225" t="n">
-        <v>2500</v>
+        <v>27144</v>
       </c>
       <c r="I225" t="n">
-        <v>22500</v>
+        <v>153818</v>
       </c>
     </row>
     <row r="226">
@@ -9660,32 +9660,32 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Jul 2019</t>
+          <t>Oct 2022</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>25000</v>
+        <v>183291</v>
       </c>
       <c r="H226" t="n">
-        <v>2500</v>
+        <v>27493</v>
       </c>
       <c r="I226" t="n">
-        <v>22500</v>
+        <v>155798</v>
       </c>
     </row>
     <row r="227">
@@ -9701,32 +9701,32 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Aug 2019</t>
+          <t>Nov 2022</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>25000</v>
+        <v>181966</v>
       </c>
       <c r="H227" t="n">
-        <v>2500</v>
+        <v>27294</v>
       </c>
       <c r="I227" t="n">
-        <v>22500</v>
+        <v>154672</v>
       </c>
     </row>
     <row r="228">
@@ -9742,32 +9742,32 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Sep 2019</t>
+          <t>Dec 2022</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>25000</v>
+        <v>331254</v>
       </c>
       <c r="H228" t="n">
-        <v>2500</v>
+        <v>49688</v>
       </c>
       <c r="I228" t="n">
-        <v>22500</v>
+        <v>281566</v>
       </c>
     </row>
     <row r="229">
@@ -9783,32 +9783,32 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Oct 2019</t>
+          <t>Jan 2023</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>25000</v>
+        <v>177397</v>
       </c>
       <c r="H229" t="n">
-        <v>2500</v>
+        <v>26609</v>
       </c>
       <c r="I229" t="n">
-        <v>22500</v>
+        <v>150788</v>
       </c>
     </row>
     <row r="230">
@@ -9824,32 +9824,32 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Nov 2019</t>
+          <t>Apr 2023</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>25000</v>
+        <v>177779</v>
       </c>
       <c r="H230" t="n">
-        <v>2500</v>
+        <v>26666</v>
       </c>
       <c r="I230" t="n">
-        <v>22500</v>
+        <v>151113</v>
       </c>
     </row>
     <row r="231">
@@ -9865,32 +9865,32 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>May 2023</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>25000</v>
+        <v>180364</v>
       </c>
       <c r="H231" t="n">
-        <v>2500</v>
+        <v>27054</v>
       </c>
       <c r="I231" t="n">
-        <v>22500</v>
+        <v>153310</v>
       </c>
     </row>
     <row r="232">
@@ -9906,32 +9906,32 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Jan 2020</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>27500</v>
+        <v>213330</v>
       </c>
       <c r="H232" t="n">
-        <v>2750</v>
+        <v>31999</v>
       </c>
       <c r="I232" t="n">
-        <v>24750</v>
+        <v>181331</v>
       </c>
     </row>
     <row r="233">
@@ -9947,32 +9947,32 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Feb 2020</t>
+          <t>Jul 2023</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>27500</v>
+        <v>183453</v>
       </c>
       <c r="H233" t="n">
-        <v>2750</v>
+        <v>27517</v>
       </c>
       <c r="I233" t="n">
-        <v>24750</v>
+        <v>155936</v>
       </c>
     </row>
     <row r="234">
@@ -9988,32 +9988,32 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Aug 2023</t>
         </is>
       </c>
       <c r="G234" t="n">
-        <v>27500</v>
+        <v>182830</v>
       </c>
       <c r="H234" t="n">
-        <v>2750</v>
+        <v>27424</v>
       </c>
       <c r="I234" t="n">
-        <v>24750</v>
+        <v>155406</v>
       </c>
     </row>
     <row r="235">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Apr 2020</t>
+          <t>Sep 2023</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>27500</v>
+        <v>224246</v>
       </c>
       <c r="H235" t="n">
-        <v>2750</v>
+        <v>33636</v>
       </c>
       <c r="I235" t="n">
-        <v>24750</v>
+        <v>190610</v>
       </c>
     </row>
     <row r="236">
@@ -10070,32 +10070,32 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Oct 2023</t>
         </is>
       </c>
       <c r="G236" t="n">
-        <v>27500</v>
+        <v>179734</v>
       </c>
       <c r="H236" t="n">
-        <v>2750</v>
+        <v>26960</v>
       </c>
       <c r="I236" t="n">
-        <v>24750</v>
+        <v>152774</v>
       </c>
     </row>
     <row r="237">
@@ -10111,32 +10111,32 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Property Landlord</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Real Estate Yield (Rent)</t>
+          <t>Executive Yield (Salary)</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>Dec 2023</t>
         </is>
       </c>
       <c r="G237" t="n">
-        <v>27500</v>
+        <v>316626</v>
       </c>
       <c r="H237" t="n">
-        <v>2750</v>
+        <v>47493</v>
       </c>
       <c r="I237" t="n">
-        <v>24750</v>
+        <v>269133</v>
       </c>
     </row>
     <row r="238">
@@ -10162,22 +10162,22 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Oct 2020</t>
+          <t>Jan 2019</t>
         </is>
       </c>
       <c r="G238" t="n">
-        <v>27500</v>
+        <v>70000</v>
       </c>
       <c r="H238" t="n">
-        <v>2750</v>
+        <v>7000</v>
       </c>
       <c r="I238" t="n">
-        <v>24750</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="239">
@@ -10203,22 +10203,22 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Nov 2020</t>
+          <t>Mar 2019</t>
         </is>
       </c>
       <c r="G239" t="n">
-        <v>27500</v>
+        <v>70000</v>
       </c>
       <c r="H239" t="n">
-        <v>2750</v>
+        <v>7000</v>
       </c>
       <c r="I239" t="n">
-        <v>24750</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="240">
@@ -10244,22 +10244,22 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>Apr 2019</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>27500</v>
+        <v>70000</v>
       </c>
       <c r="H240" t="n">
-        <v>2750</v>
+        <v>7000</v>
       </c>
       <c r="I240" t="n">
-        <v>24750</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="241">
@@ -10285,22 +10285,22 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Jan 2021</t>
+          <t>May 2019</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>30250</v>
+        <v>70000</v>
       </c>
       <c r="H241" t="n">
-        <v>3025</v>
+        <v>7000</v>
       </c>
       <c r="I241" t="n">
-        <v>27225</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="242">
@@ -10326,22 +10326,22 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Feb 2021</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="G242" t="n">
-        <v>30250</v>
+        <v>70000</v>
       </c>
       <c r="H242" t="n">
-        <v>3025</v>
+        <v>7000</v>
       </c>
       <c r="I242" t="n">
-        <v>27225</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="243">
@@ -10367,22 +10367,22 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>Jul 2019</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>30250</v>
+        <v>70000</v>
       </c>
       <c r="H243" t="n">
-        <v>3025</v>
+        <v>7000</v>
       </c>
       <c r="I243" t="n">
-        <v>27225</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="244">
@@ -10408,22 +10408,22 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>May 2021</t>
+          <t>Aug 2019</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>30250</v>
+        <v>70000</v>
       </c>
       <c r="H244" t="n">
-        <v>3025</v>
+        <v>7000</v>
       </c>
       <c r="I244" t="n">
-        <v>27225</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="245">
@@ -10449,22 +10449,22 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="G245" t="n">
-        <v>30250</v>
+        <v>70000</v>
       </c>
       <c r="H245" t="n">
-        <v>3025</v>
+        <v>7000</v>
       </c>
       <c r="I245" t="n">
-        <v>27225</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="246">
@@ -10490,22 +10490,22 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Jul 2021</t>
+          <t>Oct 2019</t>
         </is>
       </c>
       <c r="G246" t="n">
-        <v>30250</v>
+        <v>70000</v>
       </c>
       <c r="H246" t="n">
-        <v>3025</v>
+        <v>7000</v>
       </c>
       <c r="I246" t="n">
-        <v>27225</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="247">
@@ -10531,22 +10531,22 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Aug 2021</t>
+          <t>Nov 2019</t>
         </is>
       </c>
       <c r="G247" t="n">
-        <v>30250</v>
+        <v>70000</v>
       </c>
       <c r="H247" t="n">
-        <v>3025</v>
+        <v>7000</v>
       </c>
       <c r="I247" t="n">
-        <v>27225</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="248">
@@ -10572,22 +10572,22 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>Dec 2019</t>
         </is>
       </c>
       <c r="G248" t="n">
-        <v>30250</v>
+        <v>70000</v>
       </c>
       <c r="H248" t="n">
-        <v>3025</v>
+        <v>7000</v>
       </c>
       <c r="I248" t="n">
-        <v>27225</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="249">
@@ -10613,22 +10613,22 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="G249" t="n">
-        <v>30250</v>
+        <v>77000</v>
       </c>
       <c r="H249" t="n">
-        <v>3025</v>
+        <v>7700</v>
       </c>
       <c r="I249" t="n">
-        <v>27225</v>
+        <v>69300</v>
       </c>
     </row>
     <row r="250">
@@ -10654,22 +10654,22 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>Feb 2020</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>30250</v>
+        <v>77000</v>
       </c>
       <c r="H250" t="n">
-        <v>3025</v>
+        <v>7700</v>
       </c>
       <c r="I250" t="n">
-        <v>27225</v>
+        <v>69300</v>
       </c>
     </row>
     <row r="251">
@@ -10695,22 +10695,22 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>30250</v>
+        <v>77000</v>
       </c>
       <c r="H251" t="n">
-        <v>3025</v>
+        <v>7700</v>
       </c>
       <c r="I251" t="n">
-        <v>27225</v>
+        <v>69300</v>
       </c>
     </row>
     <row r="252">
@@ -10736,22 +10736,22 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Jan 2022</t>
+          <t>May 2020</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>33275</v>
+        <v>77000</v>
       </c>
       <c r="H252" t="n">
-        <v>3327</v>
+        <v>7700</v>
       </c>
       <c r="I252" t="n">
-        <v>29948</v>
+        <v>69300</v>
       </c>
     </row>
     <row r="253">
@@ -10777,22 +10777,22 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Mar 2022</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>33275</v>
+        <v>77000</v>
       </c>
       <c r="H253" t="n">
-        <v>3327</v>
+        <v>7700</v>
       </c>
       <c r="I253" t="n">
-        <v>29948</v>
+        <v>69300</v>
       </c>
     </row>
     <row r="254">
@@ -10818,22 +10818,22 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>May 2022</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>33275</v>
+        <v>77000</v>
       </c>
       <c r="H254" t="n">
-        <v>3327</v>
+        <v>7700</v>
       </c>
       <c r="I254" t="n">
-        <v>29948</v>
+        <v>69300</v>
       </c>
     </row>
     <row r="255">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>Aug 2020</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>33275</v>
+        <v>77000</v>
       </c>
       <c r="H255" t="n">
-        <v>3327</v>
+        <v>7700</v>
       </c>
       <c r="I255" t="n">
-        <v>29948</v>
+        <v>69300</v>
       </c>
     </row>
     <row r="256">
@@ -10900,22 +10900,22 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Jul 2022</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>33275</v>
+        <v>77000</v>
       </c>
       <c r="H256" t="n">
-        <v>3327</v>
+        <v>7700</v>
       </c>
       <c r="I256" t="n">
-        <v>29948</v>
+        <v>69300</v>
       </c>
     </row>
     <row r="257">
@@ -10941,22 +10941,22 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>Oct 2020</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>33275</v>
+        <v>77000</v>
       </c>
       <c r="H257" t="n">
-        <v>3327</v>
+        <v>7700</v>
       </c>
       <c r="I257" t="n">
-        <v>29948</v>
+        <v>69300</v>
       </c>
     </row>
     <row r="258">
@@ -10982,22 +10982,22 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Nov 2020</t>
         </is>
       </c>
       <c r="G258" t="n">
-        <v>33275</v>
+        <v>77000</v>
       </c>
       <c r="H258" t="n">
-        <v>3327</v>
+        <v>7700</v>
       </c>
       <c r="I258" t="n">
-        <v>29948</v>
+        <v>69300</v>
       </c>
     </row>
     <row r="259">
@@ -11023,22 +11023,22 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Nov 2022</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G259" t="n">
-        <v>33275</v>
+        <v>77000</v>
       </c>
       <c r="H259" t="n">
-        <v>3327</v>
+        <v>7700</v>
       </c>
       <c r="I259" t="n">
-        <v>29948</v>
+        <v>69300</v>
       </c>
     </row>
     <row r="260">
@@ -11064,22 +11064,22 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Dec 2022</t>
+          <t>Jan 2021</t>
         </is>
       </c>
       <c r="G260" t="n">
-        <v>33275</v>
+        <v>84700</v>
       </c>
       <c r="H260" t="n">
-        <v>3327</v>
+        <v>8470</v>
       </c>
       <c r="I260" t="n">
-        <v>29948</v>
+        <v>76230</v>
       </c>
     </row>
     <row r="261">
@@ -11105,22 +11105,22 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>Feb 2021</t>
         </is>
       </c>
       <c r="G261" t="n">
-        <v>36602</v>
+        <v>84700</v>
       </c>
       <c r="H261" t="n">
-        <v>3660</v>
+        <v>8470</v>
       </c>
       <c r="I261" t="n">
-        <v>32942</v>
+        <v>76230</v>
       </c>
     </row>
     <row r="262">
@@ -11146,22 +11146,22 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Mar 2023</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="G262" t="n">
-        <v>36602</v>
+        <v>84700</v>
       </c>
       <c r="H262" t="n">
-        <v>3660</v>
+        <v>8470</v>
       </c>
       <c r="I262" t="n">
-        <v>32942</v>
+        <v>76230</v>
       </c>
     </row>
     <row r="263">
@@ -11187,22 +11187,22 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Apr 2023</t>
+          <t>Apr 2021</t>
         </is>
       </c>
       <c r="G263" t="n">
-        <v>36602</v>
+        <v>84700</v>
       </c>
       <c r="H263" t="n">
-        <v>3660</v>
+        <v>8470</v>
       </c>
       <c r="I263" t="n">
-        <v>32942</v>
+        <v>76230</v>
       </c>
     </row>
     <row r="264">
@@ -11228,22 +11228,22 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>May 2021</t>
         </is>
       </c>
       <c r="G264" t="n">
-        <v>36602</v>
+        <v>84700</v>
       </c>
       <c r="H264" t="n">
-        <v>3660</v>
+        <v>8470</v>
       </c>
       <c r="I264" t="n">
-        <v>32942</v>
+        <v>76230</v>
       </c>
     </row>
     <row r="265">
@@ -11269,22 +11269,22 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>Jun 2021</t>
         </is>
       </c>
       <c r="G265" t="n">
-        <v>36602</v>
+        <v>84700</v>
       </c>
       <c r="H265" t="n">
-        <v>3660</v>
+        <v>8470</v>
       </c>
       <c r="I265" t="n">
-        <v>32942</v>
+        <v>76230</v>
       </c>
     </row>
     <row r="266">
@@ -11310,22 +11310,22 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>Jul 2021</t>
         </is>
       </c>
       <c r="G266" t="n">
-        <v>36602</v>
+        <v>84700</v>
       </c>
       <c r="H266" t="n">
-        <v>3660</v>
+        <v>8470</v>
       </c>
       <c r="I266" t="n">
-        <v>32942</v>
+        <v>76230</v>
       </c>
     </row>
     <row r="267">
@@ -11351,22 +11351,22 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Aug 2023</t>
+          <t>Aug 2021</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>36602</v>
+        <v>84700</v>
       </c>
       <c r="H267" t="n">
-        <v>3660</v>
+        <v>8470</v>
       </c>
       <c r="I267" t="n">
-        <v>32942</v>
+        <v>76230</v>
       </c>
     </row>
     <row r="268">
@@ -11392,22 +11392,22 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>36602</v>
+        <v>84700</v>
       </c>
       <c r="H268" t="n">
-        <v>3660</v>
+        <v>8470</v>
       </c>
       <c r="I268" t="n">
-        <v>32942</v>
+        <v>76230</v>
       </c>
     </row>
     <row r="269">
@@ -11433,22 +11433,22 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Oct 2023</t>
+          <t>Jan 2022</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>36602</v>
+        <v>93170</v>
       </c>
       <c r="H269" t="n">
-        <v>3660</v>
+        <v>9317</v>
       </c>
       <c r="I269" t="n">
-        <v>32942</v>
+        <v>83853</v>
       </c>
     </row>
     <row r="270">
@@ -11474,22 +11474,22 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Nov 2023</t>
+          <t>Feb 2022</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>36602</v>
+        <v>93170</v>
       </c>
       <c r="H270" t="n">
-        <v>3660</v>
+        <v>9317</v>
       </c>
       <c r="I270" t="n">
-        <v>32942</v>
+        <v>83853</v>
       </c>
     </row>
     <row r="271">
@@ -11515,22 +11515,678 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Mar 2022</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>93170</v>
+      </c>
+      <c r="H271" t="n">
+        <v>9317</v>
+      </c>
+      <c r="I271" t="n">
+        <v>83853</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>May 2022</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>93170</v>
+      </c>
+      <c r="H272" t="n">
+        <v>9317</v>
+      </c>
+      <c r="I272" t="n">
+        <v>83853</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Jun 2022</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>93170</v>
+      </c>
+      <c r="H273" t="n">
+        <v>9317</v>
+      </c>
+      <c r="I273" t="n">
+        <v>83853</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Jul 2022</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>93170</v>
+      </c>
+      <c r="H274" t="n">
+        <v>9317</v>
+      </c>
+      <c r="I274" t="n">
+        <v>83853</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Sep 2022</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>93170</v>
+      </c>
+      <c r="H275" t="n">
+        <v>9317</v>
+      </c>
+      <c r="I275" t="n">
+        <v>83853</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Oct 2022</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>93170</v>
+      </c>
+      <c r="H276" t="n">
+        <v>9317</v>
+      </c>
+      <c r="I276" t="n">
+        <v>83853</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Nov 2022</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>93170</v>
+      </c>
+      <c r="H277" t="n">
+        <v>9317</v>
+      </c>
+      <c r="I277" t="n">
+        <v>83853</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Dec 2022</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>93170</v>
+      </c>
+      <c r="H278" t="n">
+        <v>9317</v>
+      </c>
+      <c r="I278" t="n">
+        <v>83853</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Feb 2023</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>102487</v>
+      </c>
+      <c r="H279" t="n">
+        <v>10248</v>
+      </c>
+      <c r="I279" t="n">
+        <v>92239</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Apr 2023</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>102487</v>
+      </c>
+      <c r="H280" t="n">
+        <v>10248</v>
+      </c>
+      <c r="I280" t="n">
+        <v>92239</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>May 2023</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>102487</v>
+      </c>
+      <c r="H281" t="n">
+        <v>10248</v>
+      </c>
+      <c r="I281" t="n">
+        <v>92239</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Jun 2023</t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>102487</v>
+      </c>
+      <c r="H282" t="n">
+        <v>10248</v>
+      </c>
+      <c r="I282" t="n">
+        <v>92239</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Jul 2023</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>102487</v>
+      </c>
+      <c r="H283" t="n">
+        <v>10248</v>
+      </c>
+      <c r="I283" t="n">
+        <v>92239</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Aug 2023</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>102487</v>
+      </c>
+      <c r="H284" t="n">
+        <v>10248</v>
+      </c>
+      <c r="I284" t="n">
+        <v>92239</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Oct 2023</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>102487</v>
+      </c>
+      <c r="H285" t="n">
+        <v>10248</v>
+      </c>
+      <c r="I285" t="n">
+        <v>92239</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Nov 2023</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>102487</v>
+      </c>
+      <c r="H286" t="n">
+        <v>10248</v>
+      </c>
+      <c r="I286" t="n">
+        <v>92239</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>C-1003</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Property Landlord</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Real Estate Yield (Rent)</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
           <t>2023-12-01</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
+      <c r="F287" t="inlineStr">
         <is>
           <t>Dec 2023</t>
         </is>
       </c>
-      <c r="G271" t="n">
-        <v>36602</v>
-      </c>
-      <c r="H271" t="n">
-        <v>3660</v>
-      </c>
-      <c r="I271" t="n">
-        <v>32942</v>
+      <c r="G287" t="n">
+        <v>102487</v>
+      </c>
+      <c r="H287" t="n">
+        <v>10248</v>
+      </c>
+      <c r="I287" t="n">
+        <v>92239</v>
       </c>
     </row>
   </sheetData>

--- a/Task-1/mock_data/client_summary.xlsx
+++ b/Task-1/mock_data/client_summary.xlsx
@@ -495,13 +495,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>246562</v>
+        <v>251158</v>
       </c>
       <c r="H2" t="n">
-        <v>36984</v>
+        <v>37673</v>
       </c>
       <c r="I2" t="n">
-        <v>209578</v>
+        <v>213485</v>
       </c>
     </row>
     <row r="3">
@@ -527,22 +527,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Feb 2019</t>
+          <t>Mar 2019</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>246643</v>
+        <v>304955</v>
       </c>
       <c r="H3" t="n">
-        <v>36996</v>
+        <v>45743</v>
       </c>
       <c r="I3" t="n">
-        <v>209647</v>
+        <v>259212</v>
       </c>
     </row>
     <row r="4">
@@ -568,22 +568,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mar 2019</t>
+          <t>Apr 2019</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>285564</v>
+        <v>250241</v>
       </c>
       <c r="H4" t="n">
-        <v>42834</v>
+        <v>37536</v>
       </c>
       <c r="I4" t="n">
-        <v>242730</v>
+        <v>212705</v>
       </c>
     </row>
     <row r="5">
@@ -618,13 +618,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>322087</v>
+        <v>308862</v>
       </c>
       <c r="H5" t="n">
-        <v>48313</v>
+        <v>46329</v>
       </c>
       <c r="I5" t="n">
-        <v>273774</v>
+        <v>262533</v>
       </c>
     </row>
     <row r="6">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>251967</v>
+        <v>254210</v>
       </c>
       <c r="H6" t="n">
-        <v>37795</v>
+        <v>38131</v>
       </c>
       <c r="I6" t="n">
-        <v>214172</v>
+        <v>216079</v>
       </c>
     </row>
     <row r="7">
@@ -691,22 +691,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oct 2019</t>
+          <t>Aug 2019</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>251328</v>
+        <v>253565</v>
       </c>
       <c r="H7" t="n">
-        <v>37699</v>
+        <v>38034</v>
       </c>
       <c r="I7" t="n">
-        <v>213629</v>
+        <v>215531</v>
       </c>
     </row>
     <row r="8">
@@ -732,22 +732,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jan 2020</t>
+          <t>Oct 2019</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>249303</v>
+        <v>252531</v>
       </c>
       <c r="H8" t="n">
-        <v>37395</v>
+        <v>37879</v>
       </c>
       <c r="I8" t="n">
-        <v>211908</v>
+        <v>214652</v>
       </c>
     </row>
     <row r="9">
@@ -773,22 +773,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Feb 2020</t>
+          <t>Nov 2019</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>252651</v>
+        <v>251284</v>
       </c>
       <c r="H9" t="n">
-        <v>37897</v>
+        <v>37692</v>
       </c>
       <c r="I9" t="n">
-        <v>214754</v>
+        <v>213592</v>
       </c>
     </row>
     <row r="10">
@@ -814,22 +814,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Dec 2019</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>318102</v>
+        <v>470630</v>
       </c>
       <c r="H10" t="n">
-        <v>47715</v>
+        <v>70594</v>
       </c>
       <c r="I10" t="n">
-        <v>270387</v>
+        <v>400036</v>
       </c>
     </row>
     <row r="11">
@@ -855,22 +855,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Apr 2020</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>252822</v>
+        <v>247650</v>
       </c>
       <c r="H11" t="n">
-        <v>37923</v>
+        <v>37147</v>
       </c>
       <c r="I11" t="n">
-        <v>214899</v>
+        <v>210503</v>
       </c>
     </row>
     <row r="12">
@@ -896,22 +896,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Feb 2020</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>253908</v>
+        <v>248656</v>
       </c>
       <c r="H12" t="n">
-        <v>38086</v>
+        <v>37298</v>
       </c>
       <c r="I12" t="n">
-        <v>215822</v>
+        <v>211358</v>
       </c>
     </row>
     <row r="13">
@@ -937,22 +937,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>298006</v>
+        <v>313641</v>
       </c>
       <c r="H13" t="n">
-        <v>44700</v>
+        <v>47046</v>
       </c>
       <c r="I13" t="n">
-        <v>253306</v>
+        <v>266595</v>
       </c>
     </row>
     <row r="14">
@@ -978,22 +978,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>249165</v>
+        <v>250184</v>
       </c>
       <c r="H14" t="n">
-        <v>37374</v>
+        <v>37527</v>
       </c>
       <c r="I14" t="n">
-        <v>211791</v>
+        <v>212657</v>
       </c>
     </row>
     <row r="15">
@@ -1019,22 +1019,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>May 2020</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>250099</v>
+        <v>246898</v>
       </c>
       <c r="H15" t="n">
-        <v>37514</v>
+        <v>37034</v>
       </c>
       <c r="I15" t="n">
-        <v>212585</v>
+        <v>209864</v>
       </c>
     </row>
     <row r="16">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>295913</v>
+        <v>318588</v>
       </c>
       <c r="H16" t="n">
-        <v>44386</v>
+        <v>47788</v>
       </c>
       <c r="I16" t="n">
-        <v>251527</v>
+        <v>270800</v>
       </c>
     </row>
     <row r="17">
@@ -1101,22 +1101,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oct 2020</t>
+          <t>Aug 2020</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>251865</v>
+        <v>253466</v>
       </c>
       <c r="H17" t="n">
-        <v>37779</v>
+        <v>38019</v>
       </c>
       <c r="I17" t="n">
-        <v>214086</v>
+        <v>215447</v>
       </c>
     </row>
     <row r="18">
@@ -1142,22 +1142,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nov 2020</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>253152</v>
+        <v>298650</v>
       </c>
       <c r="H18" t="n">
-        <v>37972</v>
+        <v>44797</v>
       </c>
       <c r="I18" t="n">
-        <v>215180</v>
+        <v>253853</v>
       </c>
     </row>
     <row r="19">
@@ -1183,22 +1183,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>Oct 2020</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>431860</v>
+        <v>246670</v>
       </c>
       <c r="H19" t="n">
-        <v>64779</v>
+        <v>37000</v>
       </c>
       <c r="I19" t="n">
-        <v>367081</v>
+        <v>209670</v>
       </c>
     </row>
     <row r="20">
@@ -1224,22 +1224,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jan 2021</t>
+          <t>Nov 2020</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>254671</v>
+        <v>246999</v>
       </c>
       <c r="H20" t="n">
-        <v>38200</v>
+        <v>37049</v>
       </c>
       <c r="I20" t="n">
-        <v>216471</v>
+        <v>209950</v>
       </c>
     </row>
     <row r="21">
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Feb 2021</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>251597</v>
+        <v>465753</v>
       </c>
       <c r="H21" t="n">
-        <v>37739</v>
+        <v>69862</v>
       </c>
       <c r="I21" t="n">
-        <v>213858</v>
+        <v>395891</v>
       </c>
     </row>
     <row r="22">
@@ -1306,22 +1306,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>Jan 2021</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>297364</v>
+        <v>252722</v>
       </c>
       <c r="H22" t="n">
-        <v>44604</v>
+        <v>37908</v>
       </c>
       <c r="I22" t="n">
-        <v>252760</v>
+        <v>214814</v>
       </c>
     </row>
     <row r="23">
@@ -1347,22 +1347,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Apr 2021</t>
+          <t>Feb 2021</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>246063</v>
+        <v>251904</v>
       </c>
       <c r="H23" t="n">
-        <v>36909</v>
+        <v>37785</v>
       </c>
       <c r="I23" t="n">
-        <v>209154</v>
+        <v>214119</v>
       </c>
     </row>
     <row r="24">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>May 2021</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>253257</v>
+        <v>317251</v>
       </c>
       <c r="H24" t="n">
-        <v>37988</v>
+        <v>47587</v>
       </c>
       <c r="I24" t="n">
-        <v>215269</v>
+        <v>269664</v>
       </c>
     </row>
     <row r="25">
@@ -1429,22 +1429,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>Apr 2021</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>302612</v>
+        <v>245750</v>
       </c>
       <c r="H25" t="n">
-        <v>45391</v>
+        <v>36862</v>
       </c>
       <c r="I25" t="n">
-        <v>257221</v>
+        <v>208888</v>
       </c>
     </row>
     <row r="26">
@@ -1470,22 +1470,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jul 2021</t>
+          <t>May 2021</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>281466</v>
+        <v>246489</v>
       </c>
       <c r="H26" t="n">
-        <v>42219</v>
+        <v>36973</v>
       </c>
       <c r="I26" t="n">
-        <v>239247</v>
+        <v>209516</v>
       </c>
     </row>
     <row r="27">
@@ -1511,22 +1511,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aug 2021</t>
+          <t>Jun 2021</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>274657</v>
+        <v>321996</v>
       </c>
       <c r="H27" t="n">
-        <v>41198</v>
+        <v>48299</v>
       </c>
       <c r="I27" t="n">
-        <v>233459</v>
+        <v>273697</v>
       </c>
     </row>
     <row r="28">
@@ -1552,22 +1552,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>Jul 2021</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>351031</v>
+        <v>281291</v>
       </c>
       <c r="H28" t="n">
-        <v>52654</v>
+        <v>42193</v>
       </c>
       <c r="I28" t="n">
-        <v>298377</v>
+        <v>239098</v>
       </c>
     </row>
     <row r="29">
@@ -1593,22 +1593,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>Aug 2021</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>281886</v>
+        <v>283041</v>
       </c>
       <c r="H29" t="n">
-        <v>42282</v>
+        <v>42456</v>
       </c>
       <c r="I29" t="n">
-        <v>239604</v>
+        <v>240585</v>
       </c>
     </row>
     <row r="30">
@@ -1634,22 +1634,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>284614</v>
+        <v>343796</v>
       </c>
       <c r="H30" t="n">
-        <v>42692</v>
+        <v>51569</v>
       </c>
       <c r="I30" t="n">
-        <v>241922</v>
+        <v>292227</v>
       </c>
     </row>
     <row r="31">
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>451112</v>
+        <v>280214</v>
       </c>
       <c r="H31" t="n">
-        <v>67666</v>
+        <v>42032</v>
       </c>
       <c r="I31" t="n">
-        <v>383446</v>
+        <v>238182</v>
       </c>
     </row>
     <row r="32">
@@ -1716,22 +1716,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jan 2022</t>
+          <t>Nov 2021</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>277921</v>
+        <v>279801</v>
       </c>
       <c r="H32" t="n">
-        <v>41688</v>
+        <v>41970</v>
       </c>
       <c r="I32" t="n">
-        <v>236233</v>
+        <v>237831</v>
       </c>
     </row>
     <row r="33">
@@ -1757,22 +1757,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mar 2022</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>340775</v>
+        <v>544493</v>
       </c>
       <c r="H33" t="n">
-        <v>51116</v>
+        <v>81673</v>
       </c>
       <c r="I33" t="n">
-        <v>289659</v>
+        <v>462820</v>
       </c>
     </row>
     <row r="34">
@@ -1798,22 +1798,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>May 2022</t>
+          <t>Feb 2022</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>283123</v>
+        <v>276648</v>
       </c>
       <c r="H34" t="n">
-        <v>42468</v>
+        <v>41497</v>
       </c>
       <c r="I34" t="n">
-        <v>240655</v>
+        <v>235151</v>
       </c>
     </row>
     <row r="35">
@@ -1839,22 +1839,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>Apr 2022</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>325260</v>
+        <v>282671</v>
       </c>
       <c r="H35" t="n">
-        <v>48789</v>
+        <v>42400</v>
       </c>
       <c r="I35" t="n">
-        <v>276471</v>
+        <v>240271</v>
       </c>
     </row>
     <row r="36">
@@ -1880,22 +1880,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jul 2022</t>
+          <t>May 2022</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>276791</v>
+        <v>283270</v>
       </c>
       <c r="H36" t="n">
-        <v>41518</v>
+        <v>42490</v>
       </c>
       <c r="I36" t="n">
-        <v>235273</v>
+        <v>240780</v>
       </c>
     </row>
     <row r="37">
@@ -1921,22 +1921,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>279907</v>
+        <v>360704</v>
       </c>
       <c r="H37" t="n">
-        <v>41986</v>
+        <v>54105</v>
       </c>
       <c r="I37" t="n">
-        <v>237921</v>
+        <v>306599</v>
       </c>
     </row>
     <row r="38">
@@ -1962,22 +1962,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Jul 2022</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>333644</v>
+        <v>280066</v>
       </c>
       <c r="H38" t="n">
-        <v>50046</v>
+        <v>42009</v>
       </c>
       <c r="I38" t="n">
-        <v>283598</v>
+        <v>238057</v>
       </c>
     </row>
     <row r="39">
@@ -2003,22 +2003,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>275470</v>
+        <v>320631</v>
       </c>
       <c r="H39" t="n">
-        <v>41320</v>
+        <v>48094</v>
       </c>
       <c r="I39" t="n">
-        <v>234150</v>
+        <v>272537</v>
       </c>
     </row>
     <row r="40">
@@ -2044,22 +2044,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nov 2022</t>
+          <t>Oct 2022</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>279666</v>
+        <v>278647</v>
       </c>
       <c r="H40" t="n">
-        <v>41949</v>
+        <v>41797</v>
       </c>
       <c r="I40" t="n">
-        <v>237717</v>
+        <v>236850</v>
       </c>
     </row>
     <row r="41">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>555584</v>
+        <v>522915</v>
       </c>
       <c r="H41" t="n">
-        <v>83337</v>
+        <v>78437</v>
       </c>
       <c r="I41" t="n">
-        <v>472247</v>
+        <v>444478</v>
       </c>
     </row>
     <row r="42">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>Jan 2023</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>275963</v>
+        <v>284588</v>
       </c>
       <c r="H42" t="n">
-        <v>41394</v>
+        <v>42688</v>
       </c>
       <c r="I42" t="n">
-        <v>234569</v>
+        <v>241900</v>
       </c>
     </row>
     <row r="43">
@@ -2167,22 +2167,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Apr 2023</t>
+          <t>Feb 2023</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>280240</v>
+        <v>279920</v>
       </c>
       <c r="H43" t="n">
-        <v>42036</v>
+        <v>41988</v>
       </c>
       <c r="I43" t="n">
-        <v>238204</v>
+        <v>237932</v>
       </c>
     </row>
     <row r="44">
@@ -2208,22 +2208,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>Mar 2023</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>277692</v>
+        <v>357031</v>
       </c>
       <c r="H44" t="n">
-        <v>41653</v>
+        <v>53554</v>
       </c>
       <c r="I44" t="n">
-        <v>236039</v>
+        <v>303477</v>
       </c>
     </row>
     <row r="45">
@@ -2249,22 +2249,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>Apr 2023</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>352967</v>
+        <v>276950</v>
       </c>
       <c r="H45" t="n">
-        <v>52945</v>
+        <v>41542</v>
       </c>
       <c r="I45" t="n">
-        <v>300022</v>
+        <v>235408</v>
       </c>
     </row>
     <row r="46">
@@ -2290,22 +2290,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>May 2023</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>283047</v>
+        <v>284508</v>
       </c>
       <c r="H46" t="n">
-        <v>42457</v>
+        <v>42676</v>
       </c>
       <c r="I46" t="n">
-        <v>240590</v>
+        <v>241832</v>
       </c>
     </row>
     <row r="47">
@@ -2331,22 +2331,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aug 2023</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>281900</v>
+        <v>333894</v>
       </c>
       <c r="H47" t="n">
-        <v>42285</v>
+        <v>50084</v>
       </c>
       <c r="I47" t="n">
-        <v>239615</v>
+        <v>283810</v>
       </c>
     </row>
     <row r="48">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>347589</v>
+        <v>323287</v>
       </c>
       <c r="H48" t="n">
-        <v>52138</v>
+        <v>48493</v>
       </c>
       <c r="I48" t="n">
-        <v>295451</v>
+        <v>274794</v>
       </c>
     </row>
     <row r="49">
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>278058</v>
+        <v>279425</v>
       </c>
       <c r="H49" t="n">
-        <v>41708</v>
+        <v>41913</v>
       </c>
       <c r="I49" t="n">
-        <v>236350</v>
+        <v>237512</v>
       </c>
     </row>
     <row r="50">
@@ -2463,13 +2463,13 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>283234</v>
+        <v>283748</v>
       </c>
       <c r="H50" t="n">
-        <v>42485</v>
+        <v>42562</v>
       </c>
       <c r="I50" t="n">
-        <v>240749</v>
+        <v>241186</v>
       </c>
     </row>
     <row r="51">
@@ -2504,13 +2504,13 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>534026</v>
+        <v>507124</v>
       </c>
       <c r="H51" t="n">
-        <v>80103</v>
+        <v>76068</v>
       </c>
       <c r="I51" t="n">
-        <v>453923</v>
+        <v>431056</v>
       </c>
     </row>
     <row r="52">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Apr 2019</t>
+          <t>May 2019</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>May 2019</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jun 2019</t>
+          <t>Jul 2019</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jul 2019</t>
+          <t>Aug 2019</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aug 2019</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sep 2019</t>
+          <t>Oct 2019</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oct 2019</t>
+          <t>Nov 2019</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nov 2019</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1485120</v>
+        <v>1633632</v>
       </c>
       <c r="H62" t="n">
-        <v>148512</v>
+        <v>163363</v>
       </c>
       <c r="I62" t="n">
-        <v>1336608</v>
+        <v>1470269</v>
       </c>
     </row>
     <row r="63">
@@ -2987,22 +2987,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1485120</v>
+        <v>1633632</v>
       </c>
       <c r="H63" t="n">
-        <v>148512</v>
+        <v>163363</v>
       </c>
       <c r="I63" t="n">
-        <v>1336608</v>
+        <v>1470269</v>
       </c>
     </row>
     <row r="64">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jan 2020</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3069,12 +3069,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Feb 2020</t>
+          <t>May 2020</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Apr 2020</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Aug 2020</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>Oct 2020</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -3356,22 +3356,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Jan 2021</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1633632</v>
+        <v>1796995</v>
       </c>
       <c r="H72" t="n">
-        <v>163363</v>
+        <v>179699</v>
       </c>
       <c r="I72" t="n">
-        <v>1470269</v>
+        <v>1617296</v>
       </c>
     </row>
     <row r="73">
@@ -3397,22 +3397,22 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nov 2020</t>
+          <t>Feb 2021</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1633632</v>
+        <v>1796995</v>
       </c>
       <c r="H73" t="n">
-        <v>163363</v>
+        <v>179699</v>
       </c>
       <c r="I73" t="n">
-        <v>1470269</v>
+        <v>1617296</v>
       </c>
     </row>
     <row r="74">
@@ -3438,22 +3438,22 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1633632</v>
+        <v>1796995</v>
       </c>
       <c r="H74" t="n">
-        <v>163363</v>
+        <v>179699</v>
       </c>
       <c r="I74" t="n">
-        <v>1470269</v>
+        <v>1617296</v>
       </c>
     </row>
     <row r="75">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>May 2021</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Apr 2021</t>
+          <t>Jun 2021</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>May 2021</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Jul 2021</t>
+          <t>Nov 2021</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aug 2021</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>Jan 2022</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1796995</v>
+        <v>1976694</v>
       </c>
       <c r="H81" t="n">
-        <v>179699</v>
+        <v>197669</v>
       </c>
       <c r="I81" t="n">
-        <v>1617296</v>
+        <v>1779025</v>
       </c>
     </row>
     <row r="82">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>Feb 2022</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1796995</v>
+        <v>1976694</v>
       </c>
       <c r="H82" t="n">
-        <v>179699</v>
+        <v>197669</v>
       </c>
       <c r="I82" t="n">
-        <v>1617296</v>
+        <v>1779025</v>
       </c>
     </row>
     <row r="83">
@@ -3807,22 +3807,22 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>Mar 2022</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1796995</v>
+        <v>1976694</v>
       </c>
       <c r="H83" t="n">
-        <v>179699</v>
+        <v>197669</v>
       </c>
       <c r="I83" t="n">
-        <v>1617296</v>
+        <v>1779025</v>
       </c>
     </row>
     <row r="84">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jan 2022</t>
+          <t>Apr 2022</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Feb 2022</t>
+          <t>May 2022</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mar 2022</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Apr 2022</t>
+          <t>Aug 2022</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>Oct 2022</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Nov 2022</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>Dec 2022</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -4135,22 +4135,22 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nov 2022</t>
+          <t>Jan 2023</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>1976694</v>
+        <v>2174364</v>
       </c>
       <c r="H91" t="n">
-        <v>197669</v>
+        <v>217436</v>
       </c>
       <c r="I91" t="n">
-        <v>1779025</v>
+        <v>1956928</v>
       </c>
     </row>
     <row r="92">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Jan 2023</t>
+          <t>Feb 2023</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>Mar 2023</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>May 2023</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Aug 2023</t>
+          <t>Jul 2023</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>Aug 2023</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Oct 2023</t>
+          <t>Sep 2023</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nov 2023</t>
+          <t>Oct 2023</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dec 2023</t>
+          <t>Nov 2023</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>131303</v>
+        <v>138724</v>
       </c>
       <c r="H102" t="n">
-        <v>13130</v>
+        <v>13872</v>
       </c>
       <c r="I102" t="n">
-        <v>118173</v>
+        <v>124852</v>
       </c>
     </row>
     <row r="103">
@@ -4636,13 +4636,13 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>117348</v>
+        <v>140318</v>
       </c>
       <c r="H103" t="n">
-        <v>11734</v>
+        <v>14031</v>
       </c>
       <c r="I103" t="n">
-        <v>105614</v>
+        <v>126287</v>
       </c>
     </row>
     <row r="104">
@@ -4668,22 +4668,22 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sep 2019</t>
+          <t>Dec 2019</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>120825</v>
+        <v>139518</v>
       </c>
       <c r="H104" t="n">
-        <v>12082</v>
+        <v>13951</v>
       </c>
       <c r="I104" t="n">
-        <v>108743</v>
+        <v>125567</v>
       </c>
     </row>
     <row r="105">
@@ -4709,22 +4709,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>139269</v>
+        <v>135777</v>
       </c>
       <c r="H105" t="n">
-        <v>13926</v>
+        <v>13577</v>
       </c>
       <c r="I105" t="n">
-        <v>125343</v>
+        <v>122200</v>
       </c>
     </row>
     <row r="106">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>142601</v>
+        <v>131141</v>
       </c>
       <c r="H106" t="n">
-        <v>14260</v>
+        <v>13114</v>
       </c>
       <c r="I106" t="n">
-        <v>128341</v>
+        <v>118027</v>
       </c>
     </row>
     <row r="107">
@@ -4791,22 +4791,22 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>128690</v>
+        <v>114921</v>
       </c>
       <c r="H107" t="n">
-        <v>12869</v>
+        <v>11492</v>
       </c>
       <c r="I107" t="n">
-        <v>115821</v>
+        <v>103429</v>
       </c>
     </row>
     <row r="108">
@@ -4832,22 +4832,22 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>119197</v>
+        <v>130196</v>
       </c>
       <c r="H108" t="n">
-        <v>11919</v>
+        <v>13019</v>
       </c>
       <c r="I108" t="n">
-        <v>107278</v>
+        <v>117177</v>
       </c>
     </row>
     <row r="109">
@@ -4873,22 +4873,22 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>128803</v>
+        <v>136848</v>
       </c>
       <c r="H109" t="n">
-        <v>12880</v>
+        <v>13684</v>
       </c>
       <c r="I109" t="n">
-        <v>115923</v>
+        <v>123164</v>
       </c>
     </row>
     <row r="110">
@@ -4914,22 +4914,22 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>Jun 2021</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>140235</v>
+        <v>124276</v>
       </c>
       <c r="H110" t="n">
-        <v>14023</v>
+        <v>12427</v>
       </c>
       <c r="I110" t="n">
-        <v>126212</v>
+        <v>111849</v>
       </c>
     </row>
     <row r="111">
@@ -4964,13 +4964,13 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>116823</v>
+        <v>110853</v>
       </c>
       <c r="H111" t="n">
-        <v>11682</v>
+        <v>11085</v>
       </c>
       <c r="I111" t="n">
-        <v>105141</v>
+        <v>99768</v>
       </c>
     </row>
     <row r="112">
@@ -5005,13 +5005,13 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>111586</v>
+        <v>110709</v>
       </c>
       <c r="H112" t="n">
-        <v>11158</v>
+        <v>11070</v>
       </c>
       <c r="I112" t="n">
-        <v>100428</v>
+        <v>99639</v>
       </c>
     </row>
     <row r="113">
@@ -5046,13 +5046,13 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>131040</v>
+        <v>137569</v>
       </c>
       <c r="H113" t="n">
-        <v>13104</v>
+        <v>13756</v>
       </c>
       <c r="I113" t="n">
-        <v>117936</v>
+        <v>123813</v>
       </c>
     </row>
     <row r="114">
@@ -5078,22 +5078,22 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>115615</v>
+        <v>141993</v>
       </c>
       <c r="H114" t="n">
-        <v>11561</v>
+        <v>14199</v>
       </c>
       <c r="I114" t="n">
-        <v>104054</v>
+        <v>127794</v>
       </c>
     </row>
     <row r="115">
@@ -5128,13 +5128,13 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>112111</v>
+        <v>113918</v>
       </c>
       <c r="H115" t="n">
-        <v>11211</v>
+        <v>11391</v>
       </c>
       <c r="I115" t="n">
-        <v>100900</v>
+        <v>102527</v>
       </c>
     </row>
     <row r="116">
@@ -5169,13 +5169,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>113877</v>
+        <v>115403</v>
       </c>
       <c r="H116" t="n">
-        <v>11387</v>
+        <v>11540</v>
       </c>
       <c r="I116" t="n">
-        <v>102490</v>
+        <v>103863</v>
       </c>
     </row>
     <row r="117">
@@ -5210,13 +5210,13 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>137952</v>
+        <v>132303</v>
       </c>
       <c r="H117" t="n">
-        <v>13795</v>
+        <v>13230</v>
       </c>
       <c r="I117" t="n">
-        <v>124157</v>
+        <v>119073</v>
       </c>
     </row>
     <row r="118">
@@ -5251,13 +5251,13 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>138160</v>
+        <v>138288</v>
       </c>
       <c r="H118" t="n">
-        <v>13816</v>
+        <v>13828</v>
       </c>
       <c r="I118" t="n">
-        <v>124344</v>
+        <v>124460</v>
       </c>
     </row>
     <row r="119">
@@ -5292,13 +5292,13 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>110806</v>
+        <v>133715</v>
       </c>
       <c r="H119" t="n">
-        <v>11080</v>
+        <v>13371</v>
       </c>
       <c r="I119" t="n">
-        <v>99726</v>
+        <v>120344</v>
       </c>
     </row>
     <row r="120">
@@ -5333,13 +5333,13 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>129956</v>
+        <v>129874</v>
       </c>
       <c r="H120" t="n">
-        <v>19493</v>
+        <v>19481</v>
       </c>
       <c r="I120" t="n">
-        <v>110463</v>
+        <v>110393</v>
       </c>
     </row>
     <row r="121">
@@ -5365,22 +5365,22 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mar 2019</t>
+          <t>Feb 2019</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>155941</v>
+        <v>128442</v>
       </c>
       <c r="H121" t="n">
-        <v>23391</v>
+        <v>19266</v>
       </c>
       <c r="I121" t="n">
-        <v>132550</v>
+        <v>109176</v>
       </c>
     </row>
     <row r="122">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Apr 2019</t>
+          <t>May 2019</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>129250</v>
+        <v>127977</v>
       </c>
       <c r="H122" t="n">
-        <v>19387</v>
+        <v>19196</v>
       </c>
       <c r="I122" t="n">
-        <v>109863</v>
+        <v>108781</v>
       </c>
     </row>
     <row r="123">
@@ -5447,22 +5447,22 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>May 2019</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>130630</v>
+        <v>150922</v>
       </c>
       <c r="H123" t="n">
-        <v>19594</v>
+        <v>22638</v>
       </c>
       <c r="I123" t="n">
-        <v>111036</v>
+        <v>128284</v>
       </c>
     </row>
     <row r="124">
@@ -5488,22 +5488,22 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Jun 2019</t>
+          <t>Aug 2019</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>170272</v>
+        <v>127942</v>
       </c>
       <c r="H124" t="n">
-        <v>25540</v>
+        <v>19191</v>
       </c>
       <c r="I124" t="n">
-        <v>144732</v>
+        <v>108751</v>
       </c>
     </row>
     <row r="125">
@@ -5529,22 +5529,22 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Aug 2019</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>130973</v>
+        <v>157473</v>
       </c>
       <c r="H125" t="n">
-        <v>19645</v>
+        <v>23620</v>
       </c>
       <c r="I125" t="n">
-        <v>111328</v>
+        <v>133853</v>
       </c>
     </row>
     <row r="126">
@@ -5570,22 +5570,22 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sep 2019</t>
+          <t>Oct 2019</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>157020</v>
+        <v>130779</v>
       </c>
       <c r="H126" t="n">
-        <v>23553</v>
+        <v>19616</v>
       </c>
       <c r="I126" t="n">
-        <v>133467</v>
+        <v>111163</v>
       </c>
     </row>
     <row r="127">
@@ -5611,22 +5611,22 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Oct 2019</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>130591</v>
+        <v>129823</v>
       </c>
       <c r="H127" t="n">
-        <v>19588</v>
+        <v>19473</v>
       </c>
       <c r="I127" t="n">
-        <v>111003</v>
+        <v>110350</v>
       </c>
     </row>
     <row r="128">
@@ -5652,22 +5652,22 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Nov 2019</t>
+          <t>Feb 2020</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>127600</v>
+        <v>132185</v>
       </c>
       <c r="H128" t="n">
-        <v>19140</v>
+        <v>19827</v>
       </c>
       <c r="I128" t="n">
-        <v>108460</v>
+        <v>112358</v>
       </c>
     </row>
     <row r="129">
@@ -5693,22 +5693,22 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>247917</v>
+        <v>129468</v>
       </c>
       <c r="H129" t="n">
-        <v>37187</v>
+        <v>19420</v>
       </c>
       <c r="I129" t="n">
-        <v>210730</v>
+        <v>110048</v>
       </c>
     </row>
     <row r="130">
@@ -5734,22 +5734,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Jan 2020</t>
+          <t>May 2020</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>127594</v>
+        <v>130177</v>
       </c>
       <c r="H130" t="n">
-        <v>19139</v>
+        <v>19526</v>
       </c>
       <c r="I130" t="n">
-        <v>108455</v>
+        <v>110651</v>
       </c>
     </row>
     <row r="131">
@@ -5775,22 +5775,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>154351</v>
+        <v>152489</v>
       </c>
       <c r="H131" t="n">
-        <v>23152</v>
+        <v>22873</v>
       </c>
       <c r="I131" t="n">
-        <v>131199</v>
+        <v>129616</v>
       </c>
     </row>
     <row r="132">
@@ -5816,22 +5816,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Apr 2020</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>132451</v>
+        <v>129633</v>
       </c>
       <c r="H132" t="n">
-        <v>19867</v>
+        <v>19444</v>
       </c>
       <c r="I132" t="n">
-        <v>112584</v>
+        <v>110189</v>
       </c>
     </row>
     <row r="133">
@@ -5857,22 +5857,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>127691</v>
+        <v>154923</v>
       </c>
       <c r="H133" t="n">
-        <v>19153</v>
+        <v>23238</v>
       </c>
       <c r="I133" t="n">
-        <v>108538</v>
+        <v>131685</v>
       </c>
     </row>
     <row r="134">
@@ -5898,22 +5898,22 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Oct 2020</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>153008</v>
+        <v>128525</v>
       </c>
       <c r="H134" t="n">
-        <v>22951</v>
+        <v>19278</v>
       </c>
       <c r="I134" t="n">
-        <v>130057</v>
+        <v>109247</v>
       </c>
     </row>
     <row r="135">
@@ -5939,22 +5939,22 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>Nov 2020</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>130775</v>
+        <v>130367</v>
       </c>
       <c r="H135" t="n">
-        <v>19616</v>
+        <v>19555</v>
       </c>
       <c r="I135" t="n">
-        <v>111159</v>
+        <v>110812</v>
       </c>
     </row>
     <row r="136">
@@ -5980,22 +5980,22 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>131774</v>
+        <v>219521</v>
       </c>
       <c r="H136" t="n">
-        <v>19766</v>
+        <v>32928</v>
       </c>
       <c r="I136" t="n">
-        <v>112008</v>
+        <v>186593</v>
       </c>
     </row>
     <row r="137">
@@ -6021,22 +6021,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Feb 2021</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>166538</v>
+        <v>159971</v>
       </c>
       <c r="H137" t="n">
-        <v>24980</v>
+        <v>23995</v>
       </c>
       <c r="I137" t="n">
-        <v>141558</v>
+        <v>135976</v>
       </c>
     </row>
     <row r="138">
@@ -6062,22 +6062,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Oct 2020</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>129225</v>
+        <v>202258</v>
       </c>
       <c r="H138" t="n">
-        <v>19383</v>
+        <v>30338</v>
       </c>
       <c r="I138" t="n">
-        <v>109842</v>
+        <v>171920</v>
       </c>
     </row>
     <row r="139">
@@ -6103,22 +6103,22 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Nov 2020</t>
+          <t>Apr 2021</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>129410</v>
+        <v>158643</v>
       </c>
       <c r="H139" t="n">
-        <v>19411</v>
+        <v>23796</v>
       </c>
       <c r="I139" t="n">
-        <v>109999</v>
+        <v>134847</v>
       </c>
     </row>
     <row r="140">
@@ -6144,22 +6144,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>May 2021</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>222726</v>
+        <v>162293</v>
       </c>
       <c r="H140" t="n">
-        <v>33408</v>
+        <v>24343</v>
       </c>
       <c r="I140" t="n">
-        <v>189318</v>
+        <v>137950</v>
       </c>
     </row>
     <row r="141">
@@ -6185,22 +6185,22 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Jan 2021</t>
+          <t>Jun 2021</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>162727</v>
+        <v>200427</v>
       </c>
       <c r="H141" t="n">
-        <v>24409</v>
+        <v>30064</v>
       </c>
       <c r="I141" t="n">
-        <v>138318</v>
+        <v>170363</v>
       </c>
     </row>
     <row r="142">
@@ -6226,22 +6226,22 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Feb 2021</t>
+          <t>Jul 2021</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>162192</v>
+        <v>162576</v>
       </c>
       <c r="H142" t="n">
-        <v>24328</v>
+        <v>24386</v>
       </c>
       <c r="I142" t="n">
-        <v>137864</v>
+        <v>138190</v>
       </c>
     </row>
     <row r="143">
@@ -6267,22 +6267,22 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>Aug 2021</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>195525</v>
+        <v>162319</v>
       </c>
       <c r="H143" t="n">
-        <v>29328</v>
+        <v>24347</v>
       </c>
       <c r="I143" t="n">
-        <v>166197</v>
+        <v>137972</v>
       </c>
     </row>
     <row r="144">
@@ -6308,22 +6308,22 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Apr 2021</t>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>162452</v>
+        <v>160571</v>
       </c>
       <c r="H144" t="n">
-        <v>24367</v>
+        <v>24085</v>
       </c>
       <c r="I144" t="n">
-        <v>138085</v>
+        <v>136486</v>
       </c>
     </row>
     <row r="145">
@@ -6349,22 +6349,22 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>May 2021</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>157062</v>
+        <v>295443</v>
       </c>
       <c r="H145" t="n">
-        <v>23559</v>
+        <v>44316</v>
       </c>
       <c r="I145" t="n">
-        <v>133503</v>
+        <v>251127</v>
       </c>
     </row>
     <row r="146">
@@ -6390,22 +6390,22 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>Jan 2022</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>189662</v>
+        <v>157842</v>
       </c>
       <c r="H146" t="n">
-        <v>28449</v>
+        <v>23676</v>
       </c>
       <c r="I146" t="n">
-        <v>161213</v>
+        <v>134166</v>
       </c>
     </row>
     <row r="147">
@@ -6431,22 +6431,22 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Jul 2021</t>
+          <t>Feb 2022</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>158005</v>
+        <v>156977</v>
       </c>
       <c r="H147" t="n">
-        <v>23700</v>
+        <v>23546</v>
       </c>
       <c r="I147" t="n">
-        <v>134305</v>
+        <v>133431</v>
       </c>
     </row>
     <row r="148">
@@ -6472,22 +6472,22 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Aug 2021</t>
+          <t>Mar 2022</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>159099</v>
+        <v>201552</v>
       </c>
       <c r="H148" t="n">
-        <v>23864</v>
+        <v>30232</v>
       </c>
       <c r="I148" t="n">
-        <v>135235</v>
+        <v>171320</v>
       </c>
     </row>
     <row r="149">
@@ -6513,22 +6513,22 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>Apr 2022</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>192964</v>
+        <v>160034</v>
       </c>
       <c r="H149" t="n">
-        <v>28944</v>
+        <v>24005</v>
       </c>
       <c r="I149" t="n">
-        <v>164020</v>
+        <v>136029</v>
       </c>
     </row>
     <row r="150">
@@ -6554,22 +6554,22 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>May 2022</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>157044</v>
+        <v>157189</v>
       </c>
       <c r="H150" t="n">
-        <v>23556</v>
+        <v>23578</v>
       </c>
       <c r="I150" t="n">
-        <v>133488</v>
+        <v>133611</v>
       </c>
     </row>
     <row r="151">
@@ -6595,22 +6595,22 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>289204</v>
+        <v>199381</v>
       </c>
       <c r="H151" t="n">
-        <v>43380</v>
+        <v>29907</v>
       </c>
       <c r="I151" t="n">
-        <v>245824</v>
+        <v>169474</v>
       </c>
     </row>
     <row r="152">
@@ -6636,22 +6636,22 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Jan 2022</t>
+          <t>Jul 2022</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>162748</v>
+        <v>156946</v>
       </c>
       <c r="H152" t="n">
-        <v>24412</v>
+        <v>23541</v>
       </c>
       <c r="I152" t="n">
-        <v>138336</v>
+        <v>133405</v>
       </c>
     </row>
     <row r="153">
@@ -6677,22 +6677,22 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Feb 2022</t>
+          <t>Aug 2022</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>157873</v>
+        <v>160933</v>
       </c>
       <c r="H153" t="n">
-        <v>23680</v>
+        <v>24139</v>
       </c>
       <c r="I153" t="n">
-        <v>134193</v>
+        <v>136794</v>
       </c>
     </row>
     <row r="154">
@@ -6718,22 +6718,22 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Apr 2022</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>157807</v>
+        <v>187689</v>
       </c>
       <c r="H154" t="n">
-        <v>23671</v>
+        <v>28153</v>
       </c>
       <c r="I154" t="n">
-        <v>134136</v>
+        <v>159536</v>
       </c>
     </row>
     <row r="155">
@@ -6759,22 +6759,22 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>May 2022</t>
+          <t>Oct 2022</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>162738</v>
+        <v>156926</v>
       </c>
       <c r="H155" t="n">
-        <v>24410</v>
+        <v>23538</v>
       </c>
       <c r="I155" t="n">
-        <v>138328</v>
+        <v>133388</v>
       </c>
     </row>
     <row r="156">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>Nov 2022</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>192490</v>
+        <v>162133</v>
       </c>
       <c r="H156" t="n">
-        <v>28873</v>
+        <v>24319</v>
       </c>
       <c r="I156" t="n">
-        <v>163617</v>
+        <v>137814</v>
       </c>
     </row>
     <row r="157">
@@ -6841,22 +6841,22 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>Dec 2022</t>
         </is>
       </c>
       <c r="G157" t="n">
-        <v>159050</v>
+        <v>284082</v>
       </c>
       <c r="H157" t="n">
-        <v>23857</v>
+        <v>42612</v>
       </c>
       <c r="I157" t="n">
-        <v>135193</v>
+        <v>241470</v>
       </c>
     </row>
     <row r="158">
@@ -6882,22 +6882,22 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Jan 2023</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>194066</v>
+        <v>160880</v>
       </c>
       <c r="H158" t="n">
-        <v>29109</v>
+        <v>24132</v>
       </c>
       <c r="I158" t="n">
-        <v>164957</v>
+        <v>136748</v>
       </c>
     </row>
     <row r="159">
@@ -6923,22 +6923,22 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>Feb 2023</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>161734</v>
+        <v>161857</v>
       </c>
       <c r="H159" t="n">
-        <v>24260</v>
+        <v>24278</v>
       </c>
       <c r="I159" t="n">
-        <v>137474</v>
+        <v>137579</v>
       </c>
     </row>
     <row r="160">
@@ -6964,22 +6964,22 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Jan 2023</t>
+          <t>Mar 2023</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>157555</v>
+        <v>206217</v>
       </c>
       <c r="H160" t="n">
-        <v>23633</v>
+        <v>30932</v>
       </c>
       <c r="I160" t="n">
-        <v>133922</v>
+        <v>175285</v>
       </c>
     </row>
     <row r="161">
@@ -7005,22 +7005,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mar 2023</t>
+          <t>Apr 2023</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>189449</v>
+        <v>163185</v>
       </c>
       <c r="H161" t="n">
-        <v>28417</v>
+        <v>24477</v>
       </c>
       <c r="I161" t="n">
-        <v>161032</v>
+        <v>138708</v>
       </c>
     </row>
     <row r="162">
@@ -7046,22 +7046,22 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Apr 2023</t>
+          <t>May 2023</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>160189</v>
+        <v>158499</v>
       </c>
       <c r="H162" t="n">
-        <v>24028</v>
+        <v>23774</v>
       </c>
       <c r="I162" t="n">
-        <v>136161</v>
+        <v>134725</v>
       </c>
     </row>
     <row r="163">
@@ -7087,22 +7087,22 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>159330</v>
+        <v>206550</v>
       </c>
       <c r="H163" t="n">
-        <v>23899</v>
+        <v>30982</v>
       </c>
       <c r="I163" t="n">
-        <v>135431</v>
+        <v>175568</v>
       </c>
     </row>
     <row r="164">
@@ -7137,13 +7137,13 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>159860</v>
+        <v>160301</v>
       </c>
       <c r="H164" t="n">
-        <v>23979</v>
+        <v>24045</v>
       </c>
       <c r="I164" t="n">
-        <v>135881</v>
+        <v>136256</v>
       </c>
     </row>
     <row r="165">
@@ -7178,13 +7178,13 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>157595</v>
+        <v>162901</v>
       </c>
       <c r="H165" t="n">
-        <v>23639</v>
+        <v>24435</v>
       </c>
       <c r="I165" t="n">
-        <v>133956</v>
+        <v>138466</v>
       </c>
     </row>
     <row r="166">
@@ -7219,13 +7219,13 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>185258</v>
+        <v>186728</v>
       </c>
       <c r="H166" t="n">
-        <v>27788</v>
+        <v>28009</v>
       </c>
       <c r="I166" t="n">
-        <v>157470</v>
+        <v>158719</v>
       </c>
     </row>
     <row r="167">
@@ -7260,13 +7260,13 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>161332</v>
+        <v>158631</v>
       </c>
       <c r="H167" t="n">
-        <v>24199</v>
+        <v>23794</v>
       </c>
       <c r="I167" t="n">
-        <v>137133</v>
+        <v>134837</v>
       </c>
     </row>
     <row r="168">
@@ -7301,13 +7301,13 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>157381</v>
+        <v>160540</v>
       </c>
       <c r="H168" t="n">
-        <v>23607</v>
+        <v>24081</v>
       </c>
       <c r="I168" t="n">
-        <v>133774</v>
+        <v>136459</v>
       </c>
     </row>
     <row r="169">
@@ -7342,13 +7342,13 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>273804</v>
+        <v>286374</v>
       </c>
       <c r="H169" t="n">
-        <v>41070</v>
+        <v>42956</v>
       </c>
       <c r="I169" t="n">
-        <v>232734</v>
+        <v>243418</v>
       </c>
     </row>
     <row r="170">
@@ -7383,13 +7383,13 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>187575</v>
+        <v>194285</v>
       </c>
       <c r="H170" t="n">
-        <v>18757</v>
+        <v>19428</v>
       </c>
       <c r="I170" t="n">
-        <v>168818</v>
+        <v>174857</v>
       </c>
     </row>
     <row r="171">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>181416</v>
+        <v>212445</v>
       </c>
       <c r="H171" t="n">
-        <v>18141</v>
+        <v>21244</v>
       </c>
       <c r="I171" t="n">
-        <v>163275</v>
+        <v>191201</v>
       </c>
     </row>
     <row r="172">
@@ -7456,22 +7456,22 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mar 2020</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>189393</v>
+        <v>242962</v>
       </c>
       <c r="H172" t="n">
-        <v>18939</v>
+        <v>24296</v>
       </c>
       <c r="I172" t="n">
-        <v>170454</v>
+        <v>218666</v>
       </c>
     </row>
     <row r="173">
@@ -7497,22 +7497,22 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Dec 2019</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>235423</v>
+        <v>219237</v>
       </c>
       <c r="H173" t="n">
-        <v>23542</v>
+        <v>21923</v>
       </c>
       <c r="I173" t="n">
-        <v>211881</v>
+        <v>197314</v>
       </c>
     </row>
     <row r="174">
@@ -7538,22 +7538,22 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>194174</v>
+        <v>216601</v>
       </c>
       <c r="H174" t="n">
-        <v>19417</v>
+        <v>21660</v>
       </c>
       <c r="I174" t="n">
-        <v>174757</v>
+        <v>194941</v>
       </c>
     </row>
     <row r="175">
@@ -7579,22 +7579,22 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>236912</v>
+        <v>209572</v>
       </c>
       <c r="H175" t="n">
-        <v>23691</v>
+        <v>20957</v>
       </c>
       <c r="I175" t="n">
-        <v>213221</v>
+        <v>188615</v>
       </c>
     </row>
     <row r="176">
@@ -7620,22 +7620,22 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>190126</v>
+        <v>201431</v>
       </c>
       <c r="H176" t="n">
-        <v>19012</v>
+        <v>20143</v>
       </c>
       <c r="I176" t="n">
-        <v>171114</v>
+        <v>181288</v>
       </c>
     </row>
     <row r="177">
@@ -7661,22 +7661,22 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>221953</v>
+        <v>228268</v>
       </c>
       <c r="H177" t="n">
-        <v>22195</v>
+        <v>22826</v>
       </c>
       <c r="I177" t="n">
-        <v>199758</v>
+        <v>205442</v>
       </c>
     </row>
     <row r="178">
@@ -7702,22 +7702,22 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>Jun 2021</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>238589</v>
+        <v>238934</v>
       </c>
       <c r="H178" t="n">
-        <v>23858</v>
+        <v>23893</v>
       </c>
       <c r="I178" t="n">
-        <v>214731</v>
+        <v>215041</v>
       </c>
     </row>
     <row r="179">
@@ -7743,22 +7743,22 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>235725</v>
+        <v>207920</v>
       </c>
       <c r="H179" t="n">
-        <v>23572</v>
+        <v>20792</v>
       </c>
       <c r="I179" t="n">
-        <v>212153</v>
+        <v>187128</v>
       </c>
     </row>
     <row r="180">
@@ -7784,22 +7784,22 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mar 2022</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>211250</v>
+        <v>196089</v>
       </c>
       <c r="H180" t="n">
-        <v>21125</v>
+        <v>19608</v>
       </c>
       <c r="I180" t="n">
-        <v>190125</v>
+        <v>176481</v>
       </c>
     </row>
     <row r="181">
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>196444</v>
+        <v>220574</v>
       </c>
       <c r="H181" t="n">
-        <v>19644</v>
+        <v>22057</v>
       </c>
       <c r="I181" t="n">
-        <v>176800</v>
+        <v>198517</v>
       </c>
     </row>
     <row r="182">
@@ -7875,13 +7875,13 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>210878</v>
+        <v>210849</v>
       </c>
       <c r="H182" t="n">
-        <v>21087</v>
+        <v>21084</v>
       </c>
       <c r="I182" t="n">
-        <v>189791</v>
+        <v>189765</v>
       </c>
     </row>
     <row r="183">
@@ -7916,13 +7916,13 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>237905</v>
+        <v>192803</v>
       </c>
       <c r="H183" t="n">
-        <v>23790</v>
+        <v>19280</v>
       </c>
       <c r="I183" t="n">
-        <v>214115</v>
+        <v>173523</v>
       </c>
     </row>
     <row r="184">
@@ -7957,13 +7957,13 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>233822</v>
+        <v>240373</v>
       </c>
       <c r="H184" t="n">
-        <v>23382</v>
+        <v>24037</v>
       </c>
       <c r="I184" t="n">
-        <v>210440</v>
+        <v>216336</v>
       </c>
     </row>
     <row r="185">
@@ -7998,13 +7998,13 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>192807</v>
+        <v>187031</v>
       </c>
       <c r="H185" t="n">
-        <v>19280</v>
+        <v>18703</v>
       </c>
       <c r="I185" t="n">
-        <v>173527</v>
+        <v>168328</v>
       </c>
     </row>
     <row r="186">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>184591</v>
+        <v>211621</v>
       </c>
       <c r="H186" t="n">
-        <v>18459</v>
+        <v>21162</v>
       </c>
       <c r="I186" t="n">
-        <v>166132</v>
+        <v>190459</v>
       </c>
     </row>
     <row r="187">
@@ -8080,13 +8080,13 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>196055</v>
+        <v>229549</v>
       </c>
       <c r="H187" t="n">
-        <v>19605</v>
+        <v>22954</v>
       </c>
       <c r="I187" t="n">
-        <v>176450</v>
+        <v>206595</v>
       </c>
     </row>
     <row r="188">
@@ -8121,13 +8121,13 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>151732</v>
+        <v>149309</v>
       </c>
       <c r="H188" t="n">
-        <v>22759</v>
+        <v>22396</v>
       </c>
       <c r="I188" t="n">
-        <v>128973</v>
+        <v>126913</v>
       </c>
     </row>
     <row r="189">
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>152088</v>
+        <v>151068</v>
       </c>
       <c r="H189" t="n">
-        <v>22813</v>
+        <v>22660</v>
       </c>
       <c r="I189" t="n">
-        <v>129275</v>
+        <v>128408</v>
       </c>
     </row>
     <row r="190">
@@ -8203,13 +8203,13 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>190394</v>
+        <v>187828</v>
       </c>
       <c r="H190" t="n">
-        <v>28559</v>
+        <v>28174</v>
       </c>
       <c r="I190" t="n">
-        <v>161835</v>
+        <v>159654</v>
       </c>
     </row>
     <row r="191">
@@ -8244,13 +8244,13 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>147226</v>
+        <v>147892</v>
       </c>
       <c r="H191" t="n">
-        <v>22083</v>
+        <v>22183</v>
       </c>
       <c r="I191" t="n">
-        <v>125143</v>
+        <v>125709</v>
       </c>
     </row>
     <row r="192">
@@ -8285,13 +8285,13 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>147901</v>
+        <v>150390</v>
       </c>
       <c r="H192" t="n">
-        <v>22185</v>
+        <v>22558</v>
       </c>
       <c r="I192" t="n">
-        <v>125716</v>
+        <v>127832</v>
       </c>
     </row>
     <row r="193">
@@ -8326,13 +8326,13 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>183891</v>
+        <v>190468</v>
       </c>
       <c r="H193" t="n">
-        <v>27583</v>
+        <v>28570</v>
       </c>
       <c r="I193" t="n">
-        <v>156308</v>
+        <v>161898</v>
       </c>
     </row>
     <row r="194">
@@ -8367,13 +8367,13 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>147989</v>
+        <v>151145</v>
       </c>
       <c r="H194" t="n">
-        <v>22198</v>
+        <v>22671</v>
       </c>
       <c r="I194" t="n">
-        <v>125791</v>
+        <v>128474</v>
       </c>
     </row>
     <row r="195">
@@ -8408,13 +8408,13 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>183429</v>
+        <v>177117</v>
       </c>
       <c r="H195" t="n">
-        <v>27514</v>
+        <v>26567</v>
       </c>
       <c r="I195" t="n">
-        <v>155915</v>
+        <v>150550</v>
       </c>
     </row>
     <row r="196">
@@ -8449,13 +8449,13 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>148353</v>
+        <v>152925</v>
       </c>
       <c r="H196" t="n">
-        <v>22252</v>
+        <v>22938</v>
       </c>
       <c r="I196" t="n">
-        <v>126101</v>
+        <v>129987</v>
       </c>
     </row>
     <row r="197">
@@ -8490,13 +8490,13 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>147999</v>
+        <v>147062</v>
       </c>
       <c r="H197" t="n">
-        <v>22199</v>
+        <v>22059</v>
       </c>
       <c r="I197" t="n">
-        <v>125800</v>
+        <v>125003</v>
       </c>
     </row>
     <row r="198">
@@ -8522,22 +8522,22 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Jan 2020</t>
+          <t>Dec 2019</t>
         </is>
       </c>
       <c r="G198" t="n">
-        <v>151600</v>
+        <v>270166</v>
       </c>
       <c r="H198" t="n">
-        <v>22740</v>
+        <v>40524</v>
       </c>
       <c r="I198" t="n">
-        <v>128860</v>
+        <v>229642</v>
       </c>
     </row>
     <row r="199">
@@ -8563,22 +8563,22 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Feb 2020</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>148831</v>
+        <v>151046</v>
       </c>
       <c r="H199" t="n">
-        <v>22324</v>
+        <v>22656</v>
       </c>
       <c r="I199" t="n">
-        <v>126507</v>
+        <v>128390</v>
       </c>
     </row>
     <row r="200">
@@ -8613,13 +8613,13 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>179196</v>
+        <v>180959</v>
       </c>
       <c r="H200" t="n">
-        <v>26879</v>
+        <v>27143</v>
       </c>
       <c r="I200" t="n">
-        <v>152317</v>
+        <v>153816</v>
       </c>
     </row>
     <row r="201">
@@ -8645,22 +8645,22 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>149593</v>
+        <v>149757</v>
       </c>
       <c r="H201" t="n">
-        <v>22438</v>
+        <v>22463</v>
       </c>
       <c r="I201" t="n">
-        <v>127155</v>
+        <v>127294</v>
       </c>
     </row>
     <row r="202">
@@ -8686,22 +8686,22 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>147576</v>
+        <v>178474</v>
       </c>
       <c r="H202" t="n">
-        <v>22136</v>
+        <v>26771</v>
       </c>
       <c r="I202" t="n">
-        <v>125440</v>
+        <v>151703</v>
       </c>
     </row>
     <row r="203">
@@ -8727,22 +8727,22 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>152941</v>
+        <v>147985</v>
       </c>
       <c r="H203" t="n">
-        <v>22941</v>
+        <v>22197</v>
       </c>
       <c r="I203" t="n">
-        <v>130000</v>
+        <v>125788</v>
       </c>
     </row>
     <row r="204">
@@ -8768,22 +8768,22 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Aug 2020</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>177567</v>
+        <v>151901</v>
       </c>
       <c r="H204" t="n">
-        <v>26635</v>
+        <v>22785</v>
       </c>
       <c r="I204" t="n">
-        <v>150932</v>
+        <v>129116</v>
       </c>
     </row>
     <row r="205">
@@ -8809,22 +8809,22 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Oct 2020</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>148591</v>
+        <v>178868</v>
       </c>
       <c r="H205" t="n">
-        <v>22288</v>
+        <v>26830</v>
       </c>
       <c r="I205" t="n">
-        <v>126303</v>
+        <v>152038</v>
       </c>
     </row>
     <row r="206">
@@ -8850,22 +8850,22 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Nov 2020</t>
+          <t>Oct 2020</t>
         </is>
       </c>
       <c r="G206" t="n">
-        <v>150555</v>
+        <v>148086</v>
       </c>
       <c r="H206" t="n">
-        <v>22583</v>
+        <v>22212</v>
       </c>
       <c r="I206" t="n">
-        <v>127972</v>
+        <v>125874</v>
       </c>
     </row>
     <row r="207">
@@ -8891,22 +8891,22 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Dec 2020</t>
+          <t>Nov 2020</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>243013</v>
+        <v>148076</v>
       </c>
       <c r="H207" t="n">
-        <v>36451</v>
+        <v>22211</v>
       </c>
       <c r="I207" t="n">
-        <v>206562</v>
+        <v>125865</v>
       </c>
     </row>
     <row r="208">
@@ -8932,22 +8932,22 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Jan 2021</t>
+          <t>Dec 2020</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>152068</v>
+        <v>300305</v>
       </c>
       <c r="H208" t="n">
-        <v>22810</v>
+        <v>45045</v>
       </c>
       <c r="I208" t="n">
-        <v>129258</v>
+        <v>255260</v>
       </c>
     </row>
     <row r="209">
@@ -8973,22 +8973,22 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Feb 2021</t>
+          <t>Jan 2021</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>149663</v>
+        <v>149246</v>
       </c>
       <c r="H209" t="n">
-        <v>22449</v>
+        <v>22386</v>
       </c>
       <c r="I209" t="n">
-        <v>127214</v>
+        <v>126860</v>
       </c>
     </row>
     <row r="210">
@@ -9014,22 +9014,22 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>Feb 2021</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>175423</v>
+        <v>147402</v>
       </c>
       <c r="H210" t="n">
-        <v>26313</v>
+        <v>22110</v>
       </c>
       <c r="I210" t="n">
-        <v>149110</v>
+        <v>125292</v>
       </c>
     </row>
     <row r="211">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>May 2021</t>
+          <t>Mar 2021</t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>148647</v>
+        <v>175679</v>
       </c>
       <c r="H211" t="n">
-        <v>22297</v>
+        <v>26351</v>
       </c>
       <c r="I211" t="n">
-        <v>126350</v>
+        <v>149328</v>
       </c>
     </row>
     <row r="212">
@@ -9096,22 +9096,22 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>Apr 2021</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>187308</v>
+        <v>151109</v>
       </c>
       <c r="H212" t="n">
-        <v>28096</v>
+        <v>22666</v>
       </c>
       <c r="I212" t="n">
-        <v>159212</v>
+        <v>128443</v>
       </c>
     </row>
     <row r="213">
@@ -9137,22 +9137,22 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Jul 2021</t>
+          <t>May 2021</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>151903</v>
+        <v>147426</v>
       </c>
       <c r="H213" t="n">
-        <v>22785</v>
+        <v>22113</v>
       </c>
       <c r="I213" t="n">
-        <v>129118</v>
+        <v>125313</v>
       </c>
     </row>
     <row r="214">
@@ -9178,22 +9178,22 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>Jul 2021</t>
         </is>
       </c>
       <c r="G214" t="n">
-        <v>180490</v>
+        <v>149287</v>
       </c>
       <c r="H214" t="n">
-        <v>27073</v>
+        <v>22393</v>
       </c>
       <c r="I214" t="n">
-        <v>153417</v>
+        <v>126894</v>
       </c>
     </row>
     <row r="215">
@@ -9219,22 +9219,22 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>Aug 2021</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>150561</v>
+        <v>149442</v>
       </c>
       <c r="H215" t="n">
-        <v>22584</v>
+        <v>22416</v>
       </c>
       <c r="I215" t="n">
-        <v>127977</v>
+        <v>127026</v>
       </c>
     </row>
     <row r="216">
@@ -9260,22 +9260,22 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>150075</v>
+        <v>188121</v>
       </c>
       <c r="H216" t="n">
-        <v>22511</v>
+        <v>28218</v>
       </c>
       <c r="I216" t="n">
-        <v>127564</v>
+        <v>159903</v>
       </c>
     </row>
     <row r="217">
@@ -9301,22 +9301,22 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>257110</v>
+        <v>147169</v>
       </c>
       <c r="H217" t="n">
-        <v>38566</v>
+        <v>22075</v>
       </c>
       <c r="I217" t="n">
-        <v>218544</v>
+        <v>125094</v>
       </c>
     </row>
     <row r="218">
@@ -9342,22 +9342,22 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Jan 2022</t>
+          <t>Nov 2021</t>
         </is>
       </c>
       <c r="G218" t="n">
-        <v>177569</v>
+        <v>149603</v>
       </c>
       <c r="H218" t="n">
-        <v>26635</v>
+        <v>22440</v>
       </c>
       <c r="I218" t="n">
-        <v>150934</v>
+        <v>127163</v>
       </c>
     </row>
     <row r="219">
@@ -9383,22 +9383,22 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Feb 2022</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G219" t="n">
-        <v>177282</v>
+        <v>281412</v>
       </c>
       <c r="H219" t="n">
-        <v>26592</v>
+        <v>42211</v>
       </c>
       <c r="I219" t="n">
-        <v>150690</v>
+        <v>239201</v>
       </c>
     </row>
     <row r="220">
@@ -9424,22 +9424,22 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Mar 2022</t>
+          <t>Jan 2022</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>223217</v>
+        <v>181866</v>
       </c>
       <c r="H220" t="n">
-        <v>33482</v>
+        <v>27279</v>
       </c>
       <c r="I220" t="n">
-        <v>189735</v>
+        <v>154587</v>
       </c>
     </row>
     <row r="221">
@@ -9465,22 +9465,22 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Apr 2022</t>
+          <t>Feb 2022</t>
         </is>
       </c>
       <c r="G221" t="n">
-        <v>183139</v>
+        <v>176497</v>
       </c>
       <c r="H221" t="n">
-        <v>27470</v>
+        <v>26474</v>
       </c>
       <c r="I221" t="n">
-        <v>155669</v>
+        <v>150023</v>
       </c>
     </row>
     <row r="222">
@@ -9506,22 +9506,22 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>May 2022</t>
+          <t>Mar 2022</t>
         </is>
       </c>
       <c r="G222" t="n">
-        <v>177682</v>
+        <v>225922</v>
       </c>
       <c r="H222" t="n">
-        <v>26652</v>
+        <v>33888</v>
       </c>
       <c r="I222" t="n">
-        <v>151030</v>
+        <v>192034</v>
       </c>
     </row>
     <row r="223">
@@ -9547,22 +9547,22 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>Apr 2022</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>222289</v>
+        <v>182969</v>
       </c>
       <c r="H223" t="n">
-        <v>33343</v>
+        <v>27445</v>
       </c>
       <c r="I223" t="n">
-        <v>188946</v>
+        <v>155524</v>
       </c>
     </row>
     <row r="224">
@@ -9588,22 +9588,22 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Jul 2022</t>
+          <t>Jun 2022</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>176747</v>
+        <v>218076</v>
       </c>
       <c r="H224" t="n">
-        <v>26512</v>
+        <v>32711</v>
       </c>
       <c r="I224" t="n">
-        <v>150235</v>
+        <v>185365</v>
       </c>
     </row>
     <row r="225">
@@ -9629,22 +9629,22 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>Jul 2022</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>180962</v>
+        <v>178227</v>
       </c>
       <c r="H225" t="n">
-        <v>27144</v>
+        <v>26734</v>
       </c>
       <c r="I225" t="n">
-        <v>153818</v>
+        <v>151493</v>
       </c>
     </row>
     <row r="226">
@@ -9670,22 +9670,22 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>183291</v>
+        <v>211049</v>
       </c>
       <c r="H226" t="n">
-        <v>27493</v>
+        <v>31657</v>
       </c>
       <c r="I226" t="n">
-        <v>155798</v>
+        <v>179392</v>
       </c>
     </row>
     <row r="227">
@@ -9711,22 +9711,22 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Nov 2022</t>
+          <t>Oct 2022</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>181966</v>
+        <v>176899</v>
       </c>
       <c r="H227" t="n">
-        <v>27294</v>
+        <v>26534</v>
       </c>
       <c r="I227" t="n">
-        <v>154672</v>
+        <v>150365</v>
       </c>
     </row>
     <row r="228">
@@ -9752,22 +9752,22 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Dec 2022</t>
+          <t>Nov 2022</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>331254</v>
+        <v>176512</v>
       </c>
       <c r="H228" t="n">
-        <v>49688</v>
+        <v>26476</v>
       </c>
       <c r="I228" t="n">
-        <v>281566</v>
+        <v>150036</v>
       </c>
     </row>
     <row r="229">
@@ -9793,22 +9793,22 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Jan 2023</t>
+          <t>Dec 2022</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>177397</v>
+        <v>333525</v>
       </c>
       <c r="H229" t="n">
-        <v>26609</v>
+        <v>50028</v>
       </c>
       <c r="I229" t="n">
-        <v>150788</v>
+        <v>283497</v>
       </c>
     </row>
     <row r="230">
@@ -9834,22 +9834,22 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Apr 2023</t>
+          <t>Jan 2023</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>177779</v>
+        <v>181514</v>
       </c>
       <c r="H230" t="n">
-        <v>26666</v>
+        <v>27227</v>
       </c>
       <c r="I230" t="n">
-        <v>151113</v>
+        <v>154287</v>
       </c>
     </row>
     <row r="231">
@@ -9875,22 +9875,22 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>Apr 2023</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>180364</v>
+        <v>183566</v>
       </c>
       <c r="H231" t="n">
-        <v>27054</v>
+        <v>27534</v>
       </c>
       <c r="I231" t="n">
-        <v>153310</v>
+        <v>156032</v>
       </c>
     </row>
     <row r="232">
@@ -9916,22 +9916,22 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>May 2023</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>213330</v>
+        <v>183308</v>
       </c>
       <c r="H232" t="n">
-        <v>31999</v>
+        <v>27496</v>
       </c>
       <c r="I232" t="n">
-        <v>181331</v>
+        <v>155812</v>
       </c>
     </row>
     <row r="233">
@@ -9957,22 +9957,22 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>183453</v>
+        <v>228439</v>
       </c>
       <c r="H233" t="n">
-        <v>27517</v>
+        <v>34265</v>
       </c>
       <c r="I233" t="n">
-        <v>155936</v>
+        <v>194174</v>
       </c>
     </row>
     <row r="234">
@@ -9998,22 +9998,22 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Aug 2023</t>
+          <t>Jul 2023</t>
         </is>
       </c>
       <c r="G234" t="n">
-        <v>182830</v>
+        <v>178490</v>
       </c>
       <c r="H234" t="n">
-        <v>27424</v>
+        <v>26773</v>
       </c>
       <c r="I234" t="n">
-        <v>155406</v>
+        <v>151717</v>
       </c>
     </row>
     <row r="235">
@@ -10039,22 +10039,22 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>Aug 2023</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>224246</v>
+        <v>179579</v>
       </c>
       <c r="H235" t="n">
-        <v>33636</v>
+        <v>26936</v>
       </c>
       <c r="I235" t="n">
-        <v>190610</v>
+        <v>152643</v>
       </c>
     </row>
     <row r="236">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>179734</v>
+        <v>181542</v>
       </c>
       <c r="H236" t="n">
-        <v>26960</v>
+        <v>27231</v>
       </c>
       <c r="I236" t="n">
-        <v>152774</v>
+        <v>154311</v>
       </c>
     </row>
     <row r="237">
@@ -10121,22 +10121,22 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Dec 2023</t>
+          <t>Nov 2023</t>
         </is>
       </c>
       <c r="G237" t="n">
-        <v>316626</v>
+        <v>179738</v>
       </c>
       <c r="H237" t="n">
-        <v>47493</v>
+        <v>26960</v>
       </c>
       <c r="I237" t="n">
-        <v>269133</v>
+        <v>152778</v>
       </c>
     </row>
     <row r="238">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Mar 2019</t>
+          <t>Feb 2019</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -10244,12 +10244,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Apr 2019</t>
+          <t>Mar 2019</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>May 2019</t>
+          <t>Apr 2019</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -10326,12 +10326,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Jun 2019</t>
+          <t>May 2019</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -10367,12 +10367,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Jul 2019</t>
+          <t>Jun 2019</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Aug 2019</t>
+          <t>Jul 2019</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Sep 2019</t>
+          <t>Aug 2019</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Oct 2019</t>
+          <t>Sep 2019</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Nov 2019</t>
+          <t>Oct 2019</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -10572,12 +10572,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Dec 2019</t>
+          <t>Nov 2019</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -10613,22 +10613,22 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Jan 2020</t>
+          <t>Dec 2019</t>
         </is>
       </c>
       <c r="G249" t="n">
-        <v>77000</v>
+        <v>70000</v>
       </c>
       <c r="H249" t="n">
-        <v>7700</v>
+        <v>7000</v>
       </c>
       <c r="I249" t="n">
-        <v>69300</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="250">
@@ -10654,12 +10654,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Feb 2020</t>
+          <t>Jan 2020</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Apr 2020</t>
+          <t>Feb 2020</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -10736,12 +10736,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>May 2020</t>
+          <t>Mar 2020</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Jun 2020</t>
+          <t>Apr 2020</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Jul 2020</t>
+          <t>Jun 2020</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Aug 2020</t>
+          <t>Jul 2020</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>Aug 2020</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Oct 2020</t>
+          <t>Sep 2020</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Nov 2020</t>
+          <t>Oct 2020</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -11064,12 +11064,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Jan 2021</t>
+          <t>Feb 2021</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Feb 2021</t>
+          <t>Apr 2021</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Mar 2021</t>
+          <t>May 2021</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Apr 2021</t>
+          <t>Jun 2021</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>May 2021</t>
+          <t>Jul 2021</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Jun 2021</t>
+          <t>Aug 2021</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Jul 2021</t>
+          <t>Sep 2021</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Aug 2021</t>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -11392,12 +11392,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>Nov 2021</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -11433,22 +11433,22 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Jan 2022</t>
+          <t>Dec 2021</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>93170</v>
+        <v>84700</v>
       </c>
       <c r="H269" t="n">
-        <v>9317</v>
+        <v>8470</v>
       </c>
       <c r="I269" t="n">
-        <v>83853</v>
+        <v>76230</v>
       </c>
     </row>
     <row r="270">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Feb 2022</t>
+          <t>Jan 2022</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Mar 2022</t>
+          <t>Feb 2022</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -11556,12 +11556,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>May 2022</t>
+          <t>Mar 2022</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -11597,12 +11597,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Jun 2022</t>
+          <t>Apr 2022</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -11638,12 +11638,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Jul 2022</t>
+          <t>May 2022</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -11679,12 +11679,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Jul 2022</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>Aug 2022</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Nov 2022</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Dec 2022</t>
+          <t>Nov 2022</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -11843,22 +11843,22 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>Dec 2022</t>
         </is>
       </c>
       <c r="G279" t="n">
-        <v>102487</v>
+        <v>93170</v>
       </c>
       <c r="H279" t="n">
-        <v>10248</v>
+        <v>9317</v>
       </c>
       <c r="I279" t="n">
-        <v>92239</v>
+        <v>83853</v>
       </c>
     </row>
     <row r="280">
@@ -11884,12 +11884,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Apr 2023</t>
+          <t>Jan 2023</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -11925,12 +11925,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>Feb 2023</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -11966,12 +11966,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>Mar 2023</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>Apr 2023</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Aug 2023</t>
+          <t>May 2023</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Oct 2023</t>
+          <t>Aug 2023</t>
         </is>
       </c>
       <c r="G285" t="n">
